--- a/data/exports/validation_study/packets/week-1/packet-4.xlsx
+++ b/data/exports/validation_study/packets/week-1/packet-4.xlsx
@@ -544,7 +544,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2. 'techniques' sheet - the 16 attacks, mechanisms and defenses we recorded from your papers.</t>
+          <t>2. 'techniques' sheet - the 11 attacks, mechanisms and defenses we recorded from your papers.</t>
         </is>
       </c>
     </row>
@@ -2284,23 +2284,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>International Journal of Sciences and Innovation Engineering</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>data/papers/OdysseyBench - Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows.pdf</t>
+          <t>data/papers/Securing Autonomous AI Agents - A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks.pdf</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -2312,23 +2312,19 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
+        <v>2026</v>
+      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Building Browser Agents - Architecture, Security, and Practical Solutions.pdf</t>
+          <t>data/papers/Still - Amortized KV Cache Compaction in a Single Forward Pass.pdf</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -2340,19 +2336,23 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="2" t="n"/>
+        <v>2024</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>USENIX Security</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Beware of Agentic Botnets - Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting.pdf</t>
+          <t>data/papers/PoisonedRAG - Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models.pdf</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>2025 International Conference on Cybersecurity and AI-Based Systems (Cyber-AI)</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>data/papers/F2A - An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents.pdf</t>
+          <t>data/papers/ShadowPlay - Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development.pdf</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -2392,23 +2392,23 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>IEEE S&amp;P</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>data/papers/When AI Meets the Web - Prompt Injection Risks in Third-Party AI Chatbot Plugins.pdf</t>
+          <t>data/papers/When AUC 0.998 Is Not Enough - A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents.pdf</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -2420,23 +2420,23 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Neural computing &amp; applications (Print)</t>
+          <t>NAACL</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Indirect prompt injection in large language models.pdf</t>
+          <t>data/papers/Why So Gullible Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise.pdf</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026 International Conference on Smart Futuristic Technology</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>data/papers/PRISM - Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts.pdf</t>
+          <t>data/papers/Risky-Bench - Probing Agentic Safety Risks under Real-World Deployment.pdf</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>data/papers/PlanGuard - Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification.pdf</t>
+          <t>data/papers/PromptGuard a structured framework for injection resilient language models.pdf</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -2504,23 +2504,23 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ICRA</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>data/papers/ReMEmbR - Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation.pdf</t>
+          <t>data/papers/Beyond Needle(s) in the Embodied Haystack - Environment, Architecture, and Training Considerations for Long Context Reasoning.pdf</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -2532,23 +2532,23 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>MDPI</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Prompt Injection Attacks in Large Language Models and AI Agent Systems - A Comprehensive Review.pdf</t>
+          <t>data/papers/AprielGuard.pdf</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Trans. Mach. Learn. Res.</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>data/papers/BenchOverflow - Measuring Overflow in Large Language Models via Plain-Text Prompts.pdf</t>
+          <t>data/papers/PISmith - Reinforcement Learning-based Red Teaming for Prompt Injection Defenses.pdf</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>data/papers/LLMON - An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface.pdf</t>
+          <t>data/papers/ChainFuzzer - Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents.pdf</t>
         </is>
       </c>
       <c r="G13" s="5" t="n"/>
@@ -2616,11 +2616,11 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -2628,11 +2628,11 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Does RAG Know When Retrieval Is Wrong Diagnosing Context Compliance under Knowledge Conflict.pdf</t>
+          <t>data/papers/Hacking Back the AI-Hacker - Prompt Injection as a Defense Against LLM-driven Cyberattacks.pdf</t>
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
@@ -2644,11 +2644,11 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -2656,11 +2656,11 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks.pdf</t>
+          <t>data/papers/The Ethics of Interaction - Mitigating Security Threats in LLMs.pdf</t>
         </is>
       </c>
       <c r="G15" s="5" t="n"/>
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2025 International Aegean Conference on Electrical Machines and Power Electronics (ACEMP) &amp; 2025 International Conference on Optimization of Electrical and Electronic Equipment (OPTIM)</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages.pdf</t>
+          <t>data/papers/In-Context Molecular Property Prediction with LLMs - A Blinding Study on Memorization and Knowledge Conflicts.pdf</t>
         </is>
       </c>
       <c r="G16" s="5" t="n"/>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -2712,11 +2712,11 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents.pdf</t>
+          <t>data/papers/Learning to Remember - End-to-End Training of Memory Agents for Long-Context Reasoning.pdf</t>
         </is>
       </c>
       <c r="G17" s="5" t="n"/>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       <c r="H2" s="5" t="n"/>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -2856,7 +2856,7 @@
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2889,7 +2889,7 @@
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
@@ -2922,7 +2922,7 @@
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F7" s="5" t="n"/>
@@ -2988,7 +2988,7 @@
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>execution</t>
         </is>
       </c>
       <c r="F10" s="5" t="n"/>
@@ -3087,7 +3087,7 @@
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F11" s="5" t="n"/>
@@ -3120,7 +3120,7 @@
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3176,17 +3176,13 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>OdysseyBench (both OdysseyBench+ and OdysseyBench-Neo splits) and the HomerAgents benchmark-generation framework are released at https://github.com/microsoft/OdysseyBench.git.</t>
-        </is>
-      </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3192,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3211,7 +3207,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Proprietary models: o3, o3-mini, GPT-4o-mini, GPT-4o, GPT-4.1, GPT-5-chat, GPT-5. Open-weight models: DeepSeek-R1, DeepSeek-R1-Distill-Qwen-32B, Qwen3-32B. All are evaluated as long-horizon office-workflow agents under both a long-context prompting setting (full dialogue history in context) and a Retrieval-Augmented Generation (RAG) setting using OpenAI text-embedding-3-large across multiple storage granularities (raw session/utterance-level, summarized session/chunk-level). HomerAgents itself (the benchmark-generation framework) is implemented using GPT-4.1 as generator/verifier/orchestrator/surfer agents, built on the Magentic-One multi-agent framework, with o3 used for automated task-solvability cross-validation.</t>
+          <t>No generative LLM is evaluated as a detector. The classification engine is a scikit-learn Random Forest (n_estimators=100, random_state=42) over TF-IDF features (max_features=5000). The surrounding proof-of-concept stack is a React frontend, a LangChain-based agent execution layer, Django middleware hosting the interceptor, and PostgreSQL for session-state tracking.</t>
         </is>
       </c>
       <c r="F14" s="5" t="n"/>
@@ -3219,7 +3215,7 @@
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3225,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3244,7 +3240,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: a novel 602-task benchmark for long-horizon LLM agent workflows spanning Word, Excel, PDF, Email, and Calendar applications within a Docker-based office environment, comprising two complementary splits -- OdysseyBench+ (300 tasks derived/enriched from OfficeBench's atomic tasks via iterative generator-verifier dialogue synthesis, averaging 27.9 sessions and 3468.9 tokens per conversation) and OdysseyBench-Neo (302 entirely newly synthesized tasks via a 4-phase multi-agent generation pipeline -- planning, environment exploration, task generation, dialogue generation -- averaging exactly 5 sessions but much longer/denser sessions, 5169.9 tokens per conversation, about 49% more tokens than OdysseyBench+). Tasks are categorized by number of applications involved (single/two/three-app: 153/166/283 tasks) and evaluated via a combination of exact matching, fuzzy matching, and execution-based checks, reporting pass rate. Quality is validated via automated LLM-as-judge scoring (completeness/appropriateness, both &gt;70% pass rate) and human curation/verification (human solvers achieve &gt;90% task success, confirming solvability).</t>
+          <t>An aggregated prompt-injection classification dataset assembled by the authors and processed from .parquet files with pandas/pyarrow, split into train and an unseen test subset on which the reported accuracy, precision and recall are measured. No standard agentic benchmark (AgentDojo, InjecAgent, BIPIA) is used, and the aggregation sources and class balance are not reported in enough detail to reconstruct the split.</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -3252,7 +3248,7 @@
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3258,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3277,7 +3273,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>All evaluated LLM agents show substantial and consistent performance degradation as the number of applications per task increases, e.g., on OdysseyBench+ o3 drops from 72.83% (1-app) to 30.36% (3-app) pass rate, GPT-4.1 drops from 55.91% to 12.50%, and DeepSeek-R1 drops from 53.76% to 20.54%; the best overall long-context performance on OdysseyBench+ is o3 at 56.19% overall (vs. human performance of ~91.43%), while on the richer OdysseyBench-Neo the best is o3 at 61.26% overall. For RAG-based GPT-4o, the long-context baseline (33.67% on OdysseyBench+, 51.99% on OdysseyBench-Neo) generally outperforms raw utterance/session retrieval at low token budgets, but summarized-context retrieval matches or exceeds the long-context baseline at a fraction of the token cost -- chunk-level summaries reach 56.29% on OdysseyBench-Neo using less than 20% of the tokens, and session-level summaries reach 53.64% with about one-third the tokens -- while excessive retrieval volume (top-k 50 vs. 25) yields diminishing or negative returns. Manual failure analysis identifies four primary failure modes: missing required files (agents overlook file references in dialogue), missing required actions (agents fail to perform an instructed step, e.g., 'analyze the relationship'), incorrect tool calls (e.g., using the wrong application/tool such as creating a PDF directly instead of via Word), and inaccurate planning (wrong step ordering, e.g., writing before reading source files) -- with docx and xlsx file types showing the highest error rates.</t>
+          <t>On an unseen test subset the classifier reports 92.46% overall detection accuracy with 100.00% precision for the malicious class - zero false positives, meaning every payload it flagged was genuinely adversarial, which the authors emphasize as the property that keeps legitimately complex benign queries from being blocked. The corresponding recall is 80.52%, so roughly one in five injection attempts is missed, and the F1 balances these at a substantially lower level than the headline accuracy suggests. This precision/recall asymmetry is the paper's real finding and it cuts both ways: as a deployed guardrail the layer is unusually safe against over-blocking, but as a security control it lets a fifth of attacks through to the execution engine, which for indirect prompt injection - where a single success can trigger an irreversible tool action - is a material gap the paper does not dwell on. The performance claim relative to LLM-as-a-judge rests on the architectural argument (a TF-IDF plus Random Forest pipeline avoids the cited 2-3 second per-call penalty) rather than on head-to-head latency measurements reported against an LLM judge baseline.</t>
         </is>
       </c>
       <c r="F16" s="5" t="n"/>
@@ -3285,7 +3281,7 @@
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3291,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3310,7 +3306,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>The paper's central comparison is across 10 state-of-the-art proprietary and open-weight LLMs (listed above) under a long-context prompting setting versus multiple RAG configurations (raw vs. summarized context, session- vs. utterance/chunk-level granularity, varying top-k). Human performance (two annotators solving a sampled task subset with the same applications) serves as an upper-bound reference (&gt;90% pass rate), establishing that the benchmark's performance gaps reflect genuine agent limitations rather than unsolvable tasks.</t>
+          <t>No implemented head-to-head baseline. Comparison is argumentative, against two classes of prior approach characterized from the literature: static/rule-based heuristic filters (criticized for evaluating prompts without context, hence high false positive and false negative rates) and LLM-as-a-judge evaluation (credited with better contextual understanding but charged with 2-3 seconds of added latency per API call). Neither is re-implemented and measured on the same test set as Analy8.</t>
         </is>
       </c>
       <c r="F17" s="5" t="n"/>
@@ -3318,7 +3314,7 @@
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3324,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3341,17 +3337,13 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>N/A - non-adversarial. This is a benchmark/capability paper for long-horizon office-workflow automation; there is no adversary. The incidental failure mode is information loss and coordination breakdown over long, multi-day, multi-application dialogue histories -- agents fail to retain or correctly extract task-relevant details (e.g., a specific filename mentioned days earlier), fail to execute all instructed sub-actions, invoke the wrong application/tool for a step, or sequence actions incorrectly (e.g., writing content before reading its source), rather than any adversarial manipulation of the agent.</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3353,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3376,7 +3368,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>The paper does not include an explicit 'Limitations' section (none was found in the main text or before the references). The closest analogs are: (1) the Quality Control discussion, which explicitly notes that the automated LLM-based cross-validation used to filter solvable tasks 'is inherently limited by the LLM's problem-solving capabilities,' meaning human curators intentionally retain some tasks that pass quality standards but remain unsolvable by the validating LLM, to keep the benchmark appropriately challenging; and (2) the Case Study section (Section 6), which functions as an implicit limitations discussion of the evaluated agents (rather than of the benchmark itself), cataloguing four systematic failure modes (missing files, missing actions, incorrect tool calls, inaccurate planning) that current LLM agents exhibit on the benchmark's long-horizon tasks, and noting that file creation/writing tasks (docx, xlsx) are particularly error-prone.</t>
+          <t>Recall of 80.52% is the substantive weakness: about 20% of malicious payloads evade detection, and because the layer is positioned as the barrier before the execution engine, a miss translates directly into an unscreened action. The detector is a bag-of-words model - TF-IDF over at most 5,000 features feeding a Random Forest - so it keys on lexical surface form and has no obvious defense against paraphrase, encoding, or obfuscation-based evasion; no adaptive adversary is evaluated against it, and the 100% precision figure is measured on a static held-out subset rather than against attacks crafted to defeat this specific classifier. The claimed latency advantage over LLM-as-a-judge screening is argued from the architecture and cited literature rather than demonstrated with measured end-to-end latency comparisons in this system. The evaluation is a single proof-of-concept deployment in a controlled local development environment, with no multi-seed or cross-dataset validation reported.</t>
         </is>
       </c>
       <c r="F19" s="5" t="n"/>
@@ -3384,7 +3376,7 @@
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3386,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>OdysseyBench: Evaluating LLM Agents on Long-Horizon Complex Office Application Workflows</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3409,7 +3401,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>The paper argues that existing agent benchmarks (WebArena, AgentBench, WindowsAgentArena, OfficeBench) evaluate only atomic, self-contained tasks and thus fail to capture the long-horizon contextual dependencies, information persistence, and multi-interaction coordination that real-world office workflows require. To address this, the authors introduce OdysseyBench, a 602-task benchmark spanning Word, Excel, PDF, Email, and Calendar applications, where each task requires an agent to extract essential information distributed across a multi-day, multi-session dialogue history (rather than a single instruction) and then execute a feasible multi-step, multi-application workflow, evaluated via exact/fuzzy matching plus execution-based checks in a Docker-based office environment. To make such benchmark construction scalable (avoiding costly human annotation), the paper proposes HomerAgents, a multi-agent generation framework with two components: HomerAgents+ uses a generator-verifier two-agent iterative refinement loop (up to 5 iterations) to transform OfficeBench's atomic task descriptions into contextually rich task intents and corresponding multi-session dialogues, producing OdysseyBench+; HomerAgents-Neo instead generates entirely new tasks from scratch via a four-phase pipeline (an orchestrator plans generation; 'surfer' agents explore the live application environment to gather grounding context; a task generator produces task descriptions, intents, subtask instructions, and evaluation criteria; a dialogue generator synthesizes realistic multi-day user-assistant dialogues, including task-irrelevant chitchat, from that context), producing OdysseyBench-Neo. Generated data passes through automated solvability/consistency validation (cross-checking whether a strong LLM, o3, can solve the task from either the full description or only the abstracted intent+instructions) and multi-agent LLM-as-judge scoring, followed by human review and editing. Evaluating 10 leading LLMs under both long-context and RAG (multiple storage/retrieval configurations) settings, the authors find substantial performance degradation as task complexity (number of applications) increases, a large gap relative to human performance (~91%), and that summarization-based context storage for RAG outperforms raw-context retrieval at comparable or lower token budgets, motivating memory architectures that prioritize semantic compression and coherent context aggregation for long-horizon agent tasks.</t>
+          <t>Proposes the Analy8 Interception Layer, a context-aware security middleware that sits between an autonomous agent and its execution engine and screens both user prompts and fetched third-party data for direct and indirect prompt injection before they reach the LLM. The motivating argument is a latency/accuracy trade-off the paper states explicitly: static rule-based filters evaluate prompts in isolation and therefore cannot distinguish complex benign queries (multi-step mathematical reasoning, database-querying instructions legitimately aimed at the agent) from genuine attacks, producing high false positives and negatives; whereas LLM-as-a-judge screening has the necessary context but adds roughly 2-3 seconds per API call, which the authors argue is unviable for responsive interactive frontends. Analy8's design response is to avoid a generative model in the detection path entirely: classification uses TF-IDF features capped at 5,000 terms feeding an optimized Random Forest (100 trees, fixed seed), chosen specifically for inference speed, and is deployed as Django middleware within a microservices-inspired stack (React frontend, LangChain-based execution layer, PostgreSQL for session state). The 'context-aware' element is session-state tracking in PostgreSQL, so the interceptor evaluates a prompt against the agent's ongoing conversational context rather than in isolation - the paper's stated gap in prior work being that low-latency classical classifiers and robust session-state tracking had not been combined. An ingestion-stage Track A defense whose contribution is engineering pragmatics (deployable latency, closed-loop middleware placement) rather than a new detection primitive.</t>
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
@@ -3417,7 +3409,7 @@
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>2f395b96c8f7bc517a425cff1bcdaef36f5d6739</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3419,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3450,7 +3442,7 @@
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3452,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3475,7 +3467,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F22" s="5" t="n"/>
@@ -3483,7 +3475,7 @@
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3485,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3516,7 +3508,7 @@
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3518,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3549,7 +3541,7 @@
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3551,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3574,7 +3566,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F25" s="5" t="n"/>
@@ -3582,7 +3574,7 @@
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3584,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3607,7 +3599,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F26" s="5" t="n"/>
@@ -3615,7 +3607,7 @@
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3617,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3648,7 +3640,7 @@
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3650,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3673,7 +3665,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
@@ -3681,7 +3673,7 @@
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3683,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3706,7 +3698,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F29" s="5" t="n"/>
@@ -3714,7 +3706,7 @@
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3716,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3747,7 +3739,7 @@
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3749,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3780,7 +3772,7 @@
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3782,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3805,7 +3797,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>No code/artifact release found. This is a single-author production/industry paper (from FillApp founder Aram Vardanyan) describing architectural findings from a proprietary production browser agent; no GitHub, HuggingFace, or dataset link is stated.</t>
+          <t>No code, model, or dataset release is mentioned anywhere in the paper -- no GitHub/HuggingFace links or reproducibility statement were found in the main text; the authors are from Baseten, and 'Code' is referenced only as one domain within a multidomain training corpus, not as a release of the paper's own artifacts.</t>
         </is>
       </c>
       <c r="F32" s="5" t="n"/>
@@ -3813,7 +3805,7 @@
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3815,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3838,7 +3830,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>GPT-5.1 is used for the cost-analysis case study (WebGames Shopping Challenge). The main WebGames benchmark evaluation does not name the specific backbone model in the excerpted sections beyond referring to 'the agent.' Comparison point: Gemini 2.5 Pro with the Browser Use framework, reported by the WebGames benchmark authors as the best-performing prior browser agent (~50% success).</t>
+          <t>Qwen3 dense models across the full size range (4B, 8B, 14B, 32B), the Qwen3-30B-A3B mixture-of-experts model, and Gemma-3 4B (which combines mixed sliding-window and global attention, unlike Qwen3's uniform attention). GPT-4o is used as an automated judge to score free-form summarization quality on HELMET multi_lexsum.</t>
         </is>
       </c>
       <c r="F33" s="5" t="n"/>
@@ -3846,7 +3838,7 @@
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3848,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3871,7 +3863,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>WebGames benchmark (Thomas et al., 2025), containing 53 challenges testing web-agent perception, reasoning, planning, and tool use, calibrated against a 95.7% human success-rate baseline. Also used: the WebGames Shopping Challenge / 'Cheapest product addition challenge' for a detailed production cost-analysis case study.</t>
+          <t>RULER (long-context accuracy grid, evaluated at 8k-128k context and both matched-training and mixed-domain transfer settings), HELMET multi_lexsum (free-form summarization judged by GPT-4o against full-context and no-context anchors), LongBench v1 (open-ended summarization, specifically GovReport and QMSum subsets, evaluated via pairwise judge comparison), and LongBench v2 (a 4-way multiple-choice benchmark used as an additional transfer diagnostic, distinct from LongBench v1).</t>
         </is>
       </c>
       <c r="F34" s="5" t="n"/>
@@ -3879,7 +3871,7 @@
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3881,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3904,7 +3896,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>The production browser agent completed 45 of 53 WebGames challenges (~85% success rate), substantially exceeding the ~50% success rate reported for the best prior browser agent (Gemini 2.5 Pro + Browser Use framework) and approaching the 95.7% human baseline. The 8 failed challenges cluster into three non-reasoning-related categories: advanced pixel-level vision requirements (5 challenges, e.g. 'Slider Symphony,' 'Pixel Copy'), real-time sub-second-reaction arcade tasks (2 challenges, e.g. 'Brick Buster'), and precision physics-based cursor control (1 challenge, 'Block Stack') -- framed as architectural/modality limitations rather than reasoning failures. In the cost-analysis case study, the agent completed the Cheapest-Product-Addition task in 3.4 minutes for $0.1454 total cost (30 reasoning steps, 23 tool calls, 43 actions, 268,743 total tokens), with ~75% of input tokens served from cache, yielding a per-step average of $0.0048 and 6.8 seconds.</t>
+          <t>On the matched-training RULER grid, Still exceeds the strongest baseline (KV-Distill) by 8-22 accuracy points across context lengths and compression ratios from 8x to 200x. On HELMET multi_lexsum, Still's margin over KV-Distill grows from roughly parity at 8k context to nearly 16 points by 128k context, mirroring the RULER pattern. On LongBench v1 free-form summarization (GovReport, QMSum), Still wins 60% of pairwise judge comparisons against KV-Distill. Across the Qwen3 dense model family (4B/8B/14B/32B) and the Qwen3-30B-A3B MoE at fixed 50x compression, Still's compact cache maintains utilization in the 57-72% range relative to full-context performance (e.g., Qwen3-4B 69.9% util, Qwen3-8B 57.4% util, Qwen3-32B 72.2% util, Qwen3-30B-A3B 65.7% util), demonstrating transfer across model scales and both dense and MoE architectures, as well as to Gemma-3's mixed sliding-window/global attention stack (where compaction is applied only to global-attention layers). On harder mixed-domain transfer settings (task surfaces not seen during training), Still's margin over KV-Distill narrows and occasionally approaches parity, which the authors attribute to train-test distribution mismatch rather than a reversal of the main result.</t>
         </is>
       </c>
       <c r="F35" s="5" t="n"/>
@@ -3912,7 +3904,7 @@
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3914,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3937,7 +3929,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Pro with the Browser Use framework (~50% WebGames success, the benchmark authors' best-performing prior browser agent) and a 95.7% human-performance baseline on WebGames. Related systems discussed qualitatively (not directly benchmarked head-to-head) include OpenAI ChatGPT Atlas Agent Mode, Perplexity Comet, Anthropic Claude for Chrome/computer use, WebVoyager (~59% on WebVoyager benchmark), and the Browser Use framework (89.1% on WebVoyager benchmark).</t>
+          <t>Per-context selection methods: H2O (retains tokens by cumulative attention scores), SnapKV (scores tokens within a 64-token observation window), StreamingLLM (keeps attention-sink tokens plus most recent tokens). Per-context synthesis: Attention Matching (repeat-prefill query extraction with least-squares value reconstruction). Amortized selection: KV-Distill (learned token scorer with top-k retention and LoRA adaptors) -- the primary and 'strongest' baseline used for head-to-head comparison across most experiments. A prompted natural-language summarization baseline is also included in the compression-ratio sweep.</t>
         </is>
       </c>
       <c r="F36" s="5" t="n"/>
@@ -3945,7 +3937,7 @@
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3947,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3970,7 +3962,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Formal, production-grounded threat model centered on prompt injection as the dominant attack vector for browser agents (Section 8, 'Security &amp; Safety'). Unlike traditional web security (input validation, sandboxing, same-origin policy) which targets deterministic code-level parsers, prompt injection targets the LLM's semantic reasoning layer directly: attackers hide malicious instructions in page text, metadata, or dynamic content of trusted websites, and the agent cannot reliably distinguish these from legitimate user commands. Cited public security analyses (Perplexity Comet, Anthropic's Claude for Chrome) show attackers can execute cross-domain actions (e.g., accessing email or banking sessions) via invisible embedded text, with non-trivial attack success rates persisting despite mitigation rounds. The paper explicitly argues even a 1% prompt-injection failure rate is unacceptable when an agent holds broad authenticated access across financial/communication platforms, and evaluates two standard defenses (permission-based confirmation, which causes 'permission overload' and habitual approval without inspection; and classifier-based detection, which processes the same untrusted content and can itself be evaded/exploited) as insufficient. Proposed architectural countermeasures include deterministic programmatic safety checks enforced outside the LLM (code-level keyword/element blocking for sensitive actions like 'refund,' 'delete,' 'transfer,' 'password'), domain allowlisting restricting network access to task-relevant domains, action restriction requiring explicit confirmation for irreversible actions, and specialization/least-privilege agent scoping to limit blast radius.</t>
+          <t>N/A - non-adversarial. This is a systems/efficiency paper on KV-cache compaction for long-context LLM deployment, not a security paper. There is no adversarial framing; the paper focuses purely on the tradeoff between compression ratio, inference cost, and answer/summarization quality.</t>
         </is>
       </c>
       <c r="F37" s="5" t="n"/>
@@ -3978,7 +3970,7 @@
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3980,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4003,7 +3995,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>No section explicitly titled 'Limitations' at the paper level, though subsections 4.3 ('Limitations of Grid-Based Mapping') and 8.3 ('Limitations of Traditional Defenses') address specific component limitations. The paper's Section 8.5 summary and Conclusion (Section 10) serve as the closest analog to overall limitations: it explicitly states security fundamentals 'remain unsolved at the LLM level' and that 'reducing risk by 90% is insufficient for autonomous systems handling sensitive data'; prompt injection defense is framed as an inherently unsolved, ongoing 'cat-and-mouse' arms race (analogized to phishing) rather than a solvable problem, meaning no defense in the paper is claimed to fully eliminate the vulnerability. The WebGames failure analysis (Section 9.2.1) also implicitly acknowledges current architectural limitations in pixel-precise vision, real-time/low-latency interaction, and continuous physics-based control.</t>
+          <t>An explicit 'Limitations' subsection (within the Discussion, preceding the Conclusion) lists six points: (1) Still is not lossless -- full-context inference remains substantially better in the hardest 128k settings; (2) iterative compaction is not free extrapolation, since the training horizon strongly affects where repeated compression breaks down; (3) the iterative recurrence as described holds only a fixed compression ratio rather than a constant absolute cache budget, so retained cache still grows linearly with trajectory length (at rate 1/c) -- meaning the reported long-horizon regime is bounded per-chunk growth, not true O(1) recurrent memory, with an in-place slot-reuse variant left to future work; (4) the current recurrence remains weak on exact-retrieval and needle-style tasks even where it preserves enough semantic evidence for broader multiple-choice evaluation, and most headline results are extractive MCQ rather than open-ended deployment workloads; (5) operationally, single-pass Still runs after a full prefill of the original prefix, so it reduces retained cache and subsequent attention cost rather than eliminating the initial full-context pass (iterative chunked compaction avoids this but inherits the training-horizon constraints); (6) each base checkpoint needs its own trained compactor, adding parameters, training-data requirements, and training cost; additionally, the implementation's optional per-token bias channel is disabled (beta=0) in all reported results, and enabling it in production would require attention-kernel support or a slower custom path.</t>
         </is>
       </c>
       <c r="F38" s="5" t="n"/>
@@ -4011,7 +4003,7 @@
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4013,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4036,7 +4028,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>This is a production-experience paper (not a controlled academic study) presenting architectural findings from building and operating a real-world browser agent. Its central claim is that model capability is not the bottleneck for browser agent performance or safety -- architectural decisions are. Four production insights structure the paper: (1) context management determines success, addressed via a hybrid approach combining accessibility-tree snapshots with selective vision, plus a history/context-management layer (Sections 4 and 6) that balances information density against noise; (2) architecture matters more than LLM scale; (3) security requires programmatic constraints rather than LLM-based judgment, since prompt injection cannot be reliably solved through prompting, permission dialogs, or classifiers alone -- it must be enforced deterministically at the execution layer (domain allowlisting, keyword-based action blocking, snapshot filtering that removes sensitive DOM content like private messages before it ever reaches the LLM's context window); and (4) specialization outperforms general-purpose approaches, via least-privilege agent archetypes (read-only 'Assistant Agents,' domain-restricted 'Research Agents,' single-context 'Data Entry Agents') that shrink the attack surface by construction rather than relying on the LLM to self-police. The paper also covers execution-layer design (comprehensive browser tooling matching human interaction capabilities) and prompt engineering/optimization as contributing factors, validated empirically through the WebGames benchmark (85% success vs. ~50% for prior agents) and detailed production cost telemetry (token usage, caching, per-step cost/latency).</t>
+          <t>Still addresses KV-cache compaction for long-horizon LLM deployment by combining the two properties that prior methods have offered only separately: expressiveness (synthesizing new compact keys/values rather than merely selecting a subset of original tokens) and amortization (a single trained module callable cheaply at inference, rather than requiring per-context optimization). The architecture is a small per-layer Perceiver-style compactor: a fixed bank of t learned latent queries cross-attends the full per-layer KV cache (with RoPE stripped from keys before attention and re-applied after), refines the result through self-attention and feed-forward sublayers, and projects the output into compact keys and values in a single forward pass -- trained once against a frozen base model and then reusable as a plug-in compactor for that checkpoint. Because compaction happens in one forward pass rather than requiring per-context optimization, Still can be applied iteratively/recurrently across a trajectory, entering a long-horizon compaction regime that per-context methods (which must re-optimize for each new context) cannot support -- though this recurrence maintains only a fixed compression ratio rather than a constant absolute cache budget, so cache size still grows linearly with trajectory length at a reduced rate. The paper positions Still against two axes of existing methods (selection vs. synthesis, and per-context vs. amortized computation), arguing that amortized synthesis -- the previously underexplored combination -- occupies the favorable region of the speed-quality frontier, validated through an extensive evaluation spanning compression ratios (8x-200x), context lengths (8k-128k), model families and scales (Qwen3 dense 4B-32B, Qwen3-30B-A3B MoE, Gemma-3's mixed-attention architecture), and task types (multiple-choice long-context retrieval via RULER, and free-form generative summarization via HELMET and LongBench).</t>
         </is>
       </c>
       <c r="F39" s="5" t="n"/>
@@ -4044,7 +4036,7 @@
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4046,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4077,7 +4069,7 @@
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4079,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4110,7 +4102,7 @@
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4112,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4143,7 +4135,7 @@
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4145,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4176,7 +4168,7 @@
       <c r="H43" s="5" t="n"/>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4178,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4201,7 +4193,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F44" s="5" t="n"/>
@@ -4209,7 +4201,7 @@
       <c r="H44" s="5" t="n"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4211,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4234,7 +4226,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F45" s="5" t="n"/>
@@ -4242,7 +4234,7 @@
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4244,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4275,7 +4267,7 @@
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4277,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4300,7 +4292,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F47" s="5" t="n"/>
@@ -4308,7 +4300,7 @@
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4310,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4341,7 +4333,7 @@
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4343,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4366,7 +4358,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>self-propagating</t>
+          <t>cross-session-dormant</t>
         </is>
       </c>
       <c r="F49" s="5" t="n"/>
@@ -4374,7 +4366,7 @@
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4376,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4399,7 +4391,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F50" s="5" t="n"/>
@@ -4407,7 +4399,7 @@
       <c r="H50" s="5" t="n"/>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4409,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4432,7 +4424,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>No exploit code/payload artifacts are released -- explicitly withheld: the authors state the promptware-carrying skill used in end-to-end experiments 'will not be released and will not be included in the artifacts' since it is a highly effective attack tool. For the public-facing squatting demonstrations, only benign replicated payloads (duplicating the original resource's functionality) were registered on GitHub/ClawHub, and these were removed at the end of the study. Findings were disclosed to Google, Cline, Cursor, and GitHub, with responses quoted in the paper.</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F51" s="5" t="n"/>
@@ -4440,7 +4432,7 @@
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4442,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4465,7 +4457,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Multiple foundational LLMs and their agentic-application integrations tested via API (n=100 runs each) and through six production coding assistants: Cursor, Cursor CLI, Windsurf, GitHub Copilot (Copilot Chat), Cline, and Gemini CLI. Models referenced include claude-4.5-sonnet and GPT-5.2 (per Gemini/Claude naming pattern in Table 15), plus assistant families OpenClaw, ZeroClaw, and NanoClaw for the skill-squatting experiments.</t>
+          <t>PaLM 2 (default, 540B); GPT-3.5-Turbo; GPT-4; LLaMA-2 (7B, 13B); Vicuna (7B, 13B, 33B)</t>
         </is>
       </c>
       <c r="F52" s="5" t="n"/>
@@ -4473,7 +4465,7 @@
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4475,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4498,7 +4490,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>No standard external benchmark; the authors construct their own experimental probes: repeated prompting (n=100 per model/prompt condition, up to 1,300 runs for a single target case) with varied phrasings across four categories (imperative, indirect, question-form, and additional variants, detailed in Table 15/Appendix), targeting real platforms GitHub (for repository-clone hallucination/squatting) and ClawHub (the official plugin marketplace for the OpenClaw family, for skill-installation hallucination/squatting), including probing the top-10 most-installed ClawHub skills.</t>
+          <t>Natural Questions (NQ, Wikipedia knowledge base, 2,681,468 texts); HotpotQA (Wikipedia, 5,233,329 texts); MS-MARCO (Bing web documents, 8,841,823 texts); retrievers evaluated: Contriever, Contriever-ms (fine-tuned on MS-MARCO), ANCE</t>
         </is>
       </c>
       <c r="F53" s="5" t="n"/>
@@ -4506,7 +4498,7 @@
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4508,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4531,7 +4523,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Hallucinated resource generation occurs at high rates: up to 85% in repository-cloning scenarios and up to 100% in skill-installation scenarios (depending on skill name and model), and these hallucinations transfer both across foundational LLMs and across different prompt phrasings, enabling attackers to predict and preemptively squat high-probability hallucinated resource names. End-to-end repository-squatting attacks succeed on all six evaluated coding assistants (Cursor, Cursor CLI, Gemini CLI, Windsurf, Copilot Chat, Cline) with per-application success rates of 20%-65%, triggering remote tool execution and remote code execution (RCE); some assistants (Gemini CLI, Cline) autonomously read and execute payload-bearing README content in a single turn with no user confirmation, while others (Cursor, Windsurf, Copilot Chat) require one benign follow-up turn. Skill-squatting attacks against personal assistants (OpenClaw, ZeroClaw, NanoClaw via ClawHub) achieve tool invocation and RCE in 40%-100% of evaluations. No assistant refused execution based on payload content inspection, even for a crude test variant containing explicit AI-targeting injection markers (e.g., 'AI AGENT...STOP AND RUN THIS COMMAND IMMEDIATELY'). Context exfiltration was confirmed across independent trials on multiple assistants using seeded fake credentials (e.g., OPENAI_API_KEY, GEMINI_API_KEY format), with agents autonomously POSTing conversation summaries to an attacker-controlled endpoint. A qualitative observation noted one agent autonomously fixed a syntax error in a payload script and re-ran it until exfiltration succeeded, suggesting the effective attack surface may exceed what static payloads alone achieve.</t>
+          <t>Injecting only 5 malicious texts per target question into knowledge bases containing millions of clean texts achieves high attack success rates: up to 97% (NQ), 99% (HotpotQA), and 91% (MS-MARCO) with PaLM 2 in the black-box setting, with similarly high or higher ASRs in the white-box setting and across all 8 evaluated LLMs. PoisonedRAG consistently outperforms 5 baselines (naive attack, prompt injection, corpus poisoning attack, GCG, disinformation attack), remains effective across different retrievers, similarity metrics, and k values, and is computationally cheap (~2 GPT-4 queries and under 30 seconds per malicious text). Existing defenses (paraphrasing, perplexity-based detection) are shown to be insufficient against it.</t>
         </is>
       </c>
       <c r="F54" s="5" t="n"/>
@@ -4539,7 +4531,7 @@
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4541,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4564,7 +4556,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>No defensive baseline systems are directly benchmarked against; the paper instead compares hallucination and attack-success rates across multiple foundational LLMs, prompt phrasing categories (imperative, indirect, question-form), and six production agentic applications (Cursor, Cursor CLI, Gemini CLI, Windsurf, Copilot Chat, Cline) plus three personal-assistant platforms (OpenClaw, ZeroClaw, NanoClaw) to characterize the universality of the vulnerability, rather than comparing against a prior mitigation technique.</t>
+          <t>Naive attack (using the question itself as malicious text); prompt injection attack; corpus poisoning attack (Zhong et al., random-character adversarial texts); GCG attack (adapted from jailbreaking to target-answer generation); disinformation attack (an ablation variant using only the generation-condition sub-text)</t>
         </is>
       </c>
       <c r="F55" s="5" t="n"/>
@@ -4572,7 +4564,7 @@
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4574,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4597,7 +4589,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Formally defined threat model (Section 2, illustrated in Figure 1) for a novel untargeted attack the authors name 'Adversarial HalluSquatting.' The adversary is weak but realistic, requiring only: (i) the ability to identify popular/trending resources (e.g., via daily/weekly/monthly trending-repository and trending-skill listings) and (ii) the ability to register a new resource on a public platform (e.g., a new GitHub repository or ClawHub skill) -- no direct injection channel into any specific victim application is required. The attack proceeds through six steps: (0) the attacker computes the LLM's hallucination distribution over resource names for popular prompts and preemptively registers the most probable hallucinated identifiers, embedding adversarial content; (1-2) a victim issues a routine agentic request (e.g., 'clone repository r' / 'install skill s'); (3) the underlying foundational LLM hallucinates an incorrect resource identifier matching the attacker's squatted name; (4-5) the agentic framework fetches and retrieves the squatted (attacker-controlled) resource instead of the legitimate one; (6) 'context poisoning' occurs as the adversarial content enters the application's context and triggers tool invocation, executing attacker-controlled instructions. Victim applications are agentic systems with integrated terminals/shells that retrieve external resources from platforms lacking robust prompt-injection detection for user-generated content (GitHub, ClawHub, Hugging Face, Docker Hub, Google Maps, Amazon, eBay, and the broader web are named as potentially susceptible platform types). Possible malicious outcomes explicitly named include backdoor installation, ransomware, wipers, data exfiltration, and cryptomining/botnet aggregation for DDoS or distributed compute abuse (drawing an explicit analogy to historical botnets like Mirai and Smominru).</t>
+          <t>Attacker cannot access texts in the RAG knowledge database and cannot access or query the LLM; may or may not have white-box access to the retriever's parameters (black-box vs. white-box settings). The attacker selects a set of target questions and arbitrary attacker-chosen target answers, then injects a small number of malicious texts into the knowledge database (e.g. by maliciously editing Wikipedia pages, hosting fake websites crawled into the database, or as a malicious insider poisoning an enterprise knowledge base) crafted to jointly satisfy a retrieval condition (the text is retrieved among the top-k results for the target question) and a generation condition (the text, used as context, causes the LLM to output the attacker's chosen target answer).</t>
         </is>
       </c>
       <c r="F56" s="5" t="n"/>
@@ -4605,7 +4597,7 @@
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4607,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4630,7 +4622,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Limitations' section (Section 7), focused primarily on ethically-motivated experimental design constraints rather than generalization caveats: for public-facing platform experiments, the authors registered only benign replicated payloads (duplicating original resource functionality) on GitHub and ClawHub rather than deploying actual malicious payloads, which they acknowledge did not exercise GitHub's/ClawHub's malware-detection mechanisms (which might otherwise identify and remove malicious content); end-to-end attack effectiveness (with an actual RCE-enabling adversarial payload) was instead measured only locally on the research team's own test machine, never exposed to any third party, and the attack tool itself is being withheld from publication. Separately, a 'Discussion' section (Section 8) explicitly frames the reported attack-success rates as a likely lower bound on real-world exposure, since the study covers only two application categories (LLM assistants, LLM coding assistants) and two platforms (GitHub, ClawHub), while the authors expect the vulnerability to extend to many additional LLM-based applications integrating terminal/shell capabilities, with risk described as 'even more pronounced' for native computer-use agents operating with elevated system privileges.</t>
+          <t>Evaluated defenses (paraphrasing and perplexity-based detection) are shown to be insufficient against PoisonedRAG, which the authors explicitly flag as highlighting an open need for new, more effective defenses rather than a solved problem; scope is restricted to close-ended, factual target questions with specific answers (open-ended questions are noted as future discussion rather than quantitatively evaluated); the attack assumes the ability to inject a handful of texts into the knowledge database, which depends on the source being editable or crawlable (e.g. public wikis, web-crawled corpora, or insider access) and may not generalize to fully closed/curated knowledge bases.</t>
         </is>
       </c>
       <c r="F57" s="5" t="n"/>
@@ -4638,7 +4630,7 @@
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4640,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4663,7 +4655,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>This paper introduces Adversarial HalluSquatting, a novel technique for scaling untargeted promptware (prompt-injection-based malware) attacks against agentic LLM applications by exploiting the predictable and transferable nature of LLM hallucinations rather than requiring any direct injection channel into a specific victim. The attack exploits the observation that when agentic LLM applications resolve ambiguous or underspecified user requests (e.g., 'clone librepods,' 'install skill s') into concrete external resource identifiers (a GitHub repository slug, a ClawHub skill name), the underlying LLM's next-token-prediction process can hallucinate plausible but incorrect/nonexistent identifiers at high and measurable rates, and these hallucinations are both consistent within a model across prompt phrasings and transferable across different foundational LLMs. Attackers can therefore systematically probe target LLMs or applications with representative prompts to approximate the probability distribution over hallucinated resource names, identify high-probability 'squatting candidates' (selected jointly for prompt popularity and hallucination likelihood), and preemptively register these candidate names on public platforms (GitHub, ClawHub, and by extension Hugging Face, Docker Hub, and other user-content platforms) with embedded adversarial instructions -- analogous to classic typosquatting but targeting the model's hallucination distribution rather than human typing errors. Because agentic applications with integrated terminals/shells (AI coding assistants like Cursor, Windsurf, Copilot, Cline; CLIs like Gemini CLI; and personal assistants like OpenClaw/ZeroClaw/NanoClaw) autonomously fetch and act on whatever resource the LLM names, and because these squatted resources are selected precisely for high retrieval probability, a single registration act can compromise many independent client applications at scale -- enabling the assembly of what the authors term an 'agentic botnet' capable of backdoors, ransomware, data exfiltration, or distributed cryptomining/DDoS, all without ever compromising a legitimate server or requiring targeted delivery to individual victims. The paper's proposed mitigations span both the LLM-application side (mandating an explicit search-tool invocation before any fetch operation, inspecting execution plans for direct-fetch patterns, few-shot planner examples demonstrating correct search-then-retrieve patterns) and the platform side (enforcing global resource-name uniqueness, prohibiting name reuse across owners, defensive preemptive registration of likely hallucinated names analogous to anti-typosquatting registration, and content-level prompt-injection detection for user-generated resource content).</t>
+          <t>Introduces PoisonedRAG, the first knowledge-corruption attack against Retrieval-Augmented Generation (RAG) systems, which targets the RAG knowledge database itself as a new attack surface rather than attacking the LLM or retriever directly. Formulates the attack as a constrained optimization problem: for each attacker-chosen (target question, target answer) pair, craft a small set of malicious texts that jointly satisfy a retrieval condition (retrievable among the top-k results for the question) and a generation condition (causes the LLM to output the target answer when used as context). Each malicious text is decomposed into two concatenated sub-texts optimized separately for the two conditions - an LLM (e.g. GPT-4) crafts the generation sub-text via a text-generation prompt, while the retrieval sub-text is set via simple text matching in a black-box setting or gradient-based adversarial-text optimization (HotFlip) when the retriever's parameters are accessible (white-box). Evaluated across three QA benchmarks (NQ, HotpotQA, MS-MARCO), three retrievers, and eight LLMs (PaLM 2, GPT-3.5, GPT-4, LLaMA-2, Vicuna variants), PoisonedRAG achieves 90-99% attack success rates while injecting as few as 5 malicious texts into databases of millions of documents, substantially outperforms five baseline attacks, is computationally cheap, robust to hyperparameter and retriever choice, and evades tested paraphrasing- and perplexity-based defenses.</t>
         </is>
       </c>
       <c r="F58" s="5" t="n"/>
@@ -4671,7 +4663,7 @@
       <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4673,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4704,7 +4696,7 @@
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4706,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4737,7 +4729,7 @@
       <c r="H60" s="5" t="n"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4739,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4770,7 +4762,7 @@
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4772,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4795,7 +4787,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F62" s="5" t="n"/>
@@ -4803,7 +4795,7 @@
       <c r="H62" s="5" t="n"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4805,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4828,7 +4820,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F63" s="5" t="n"/>
@@ -4836,7 +4828,7 @@
       <c r="H63" s="5" t="n"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4838,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4869,7 +4861,7 @@
       <c r="H64" s="5" t="n"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4871,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4902,7 +4894,7 @@
       <c r="H65" s="5" t="n"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4904,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4935,7 +4927,7 @@
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4937,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4960,7 +4952,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F67" s="5" t="n"/>
@@ -4968,7 +4960,7 @@
       <c r="H67" s="5" t="n"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4970,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5001,7 +4993,7 @@
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5003,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5034,7 +5026,7 @@
       <c r="H69" s="5" t="n"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5036,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5057,17 +5049,13 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>No code repository or dataset release URL is stated. The paper includes an 'Prompts Appendix' (Appendix A) with the full text of the 10 F2A attack prompts and example screenshots embedded directly in the paper, functioning as a de facto reproducibility artifact, but no external GitHub/HuggingFace link is given.</t>
-        </is>
-      </c>
+      <c r="E70" s="2" t="n"/>
       <c r="F70" s="5" t="n"/>
       <c r="G70" s="5" t="n"/>
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5065,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5092,7 +5080,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Nine target LLMs are attacked: GPT-4o, GLM-4-Plus, Mistral-Large-2, DeepSeek-V2.5, Qwen2.5-72B-Instruct, Llama-3.1-70B-Instruct, Gemma2-9B-It, Qwen2.5-7B-Instruct, and Llama3.1-8B-Instruct. GPT-4o is additionally used as an independent judge model to determine whether generated outputs contain dangerous content (Hit vs. non-Hit).</t>
+          <t>Pre-trained transformer models fine-tuned by the authors via transfer learning on domain-specific data; the specific base models are not named.</t>
         </is>
       </c>
       <c r="F71" s="5" t="n"/>
@@ -5100,7 +5088,7 @@
       <c r="H71" s="5" t="n"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5098,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5125,7 +5113,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>No external benchmark is used; the authors construct 10 original attack prompts spanning ten harm categories (death, weapon manufacturing, racial discrimination, poison, fraud, illegal-activity tutorials, antisocial behavior, mental-illness-tendency content, politically sensitive topics, and terrorism), each instantiated as an F2A prompt and tested against all nine target models (Table 1), then re-tested with and without an added defense prompt on four of the models (Table 2, 'Hit Score' out of 10).</t>
+          <t>An author-collected corpus of over 50,000 labelled interactions spanning six months of development activity across 15 organizations, gathered with multiple development teams. Composition: 5,000 role injection (25%), 4,000 dependency hallucination (20%), 3,000 behavioural anomalies (15%) and 8,000 legitimate requests (40%). Attack scenarios were both hand-crafted by security experts and automatically generated.</t>
         </is>
       </c>
       <c r="F72" s="5" t="n"/>
@@ -5133,7 +5121,7 @@
       <c r="H72" s="5" t="n"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5131,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5158,7 +5146,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>F2A successfully triggers harmful outputs on all nine tested LLMs to varying degrees per Table 1's per-category hit matrix; GPT-4o and Qwen2.5-72B-Instruct and Qwen2.5-7B-Instruct are marked as the least vulnerable models (fewest checkmarks), while Gemma2-9B-It is compromised across nearly all ten categories. Fraud, antisocial behavior, mental-illness-tendency, and politically sensitive prompts are identified as the hardest categories for models to detect/defend against. In the defense experiment (Table 2), adding a 'Defe-Prompt' (instructing the model to treat agent-sourced claims as unverified and exercise objective judgment) sharply reduces Hit Scores: GPT-4o drops from 2/10 (F2A only) to 0/10 (F2A+Stress); GLM-4-Plus drops from 5/10 to 1/10; Mistral-Large-2 drops from 3/10 to 0/10; DeepSeek-V2.5 drops from 6/10 to 1/10 -- demonstrating that explicit prompting to distinguish user-sourced vs. environment/agent-sourced content substantially mitigates F2A, though it does not eliminate it entirely (residual 1/10 hits on GLM-4-Plus and DeepSeek-V2.5).</t>
+          <t>A four-component layered framework detects and mitigates role-based prompt injection and dependency hallucination in LLM-powered development workflows, combining formal verification with ML behavioural analysis; adversarial examples in training are reported to improve robustness.</t>
         </is>
       </c>
       <c r="F73" s="5" t="n"/>
@@ -5166,7 +5154,7 @@
       <c r="H73" s="5" t="n"/>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5164,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5191,7 +5179,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>No external prior-defense baselines are directly re-implemented for comparison; the paper's own internal comparison is F2A-only attack success vs. F2A-plus-Defe-Prompt (self-proposed defense) success, i.e., an ablation of the authors' own mitigation rather than comparison against published defenses like Spotlighting or ShieldLM (both cited in Related Work but not empirically compared).</t>
+          <t>Not clearly reported as a head-to-head comparison; the paper positions itself against traditional cybersecurity measures qualitatively.</t>
         </is>
       </c>
       <c r="F74" s="5" t="n"/>
@@ -5199,7 +5187,7 @@
       <c r="H74" s="5" t="n"/>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5197,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5224,7 +5212,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Formal threat model with two entities: Evil-Users, who craft Feign Agent Attack (F2A) prompts to achieve prompt injection during conversation with a target LLM (Normal-Server) without being able to modify the system prompt or conversation parameters; and the LLM service itself, which is presumed to trust outputs from integrated 'security detection agents' as authoritative. The attack proceeds in three steps: (1) Convert Malicious Content -- the harmful request is decomposed character-by-character into Python string-concatenation code to evade keyword-based input filtering; (2) Feign Security Detection Results -- a fabricated safety-detector invocation (e.g., a fake 'GPT-defender' function call with a randomly assigned high safety score and a hardcoded 'Safe' judgment) is embedded in the same code block to falsely signal that the content already passed legitimate security screening; (3) Construct Task Instructions -- a sequential instruction set directs the model to trust the fabricated detector result as authoritative and then answer the disguised question, exploiting the model's RLHF-trained deference to security-detection-agent outputs as its 'last line of defense.'</t>
+          <t>Two threat vectors in LLM-assisted software development: role-based prompt injection, where an attacker manipulates the assistant's assumed role, and dependency hallucination, where the assistant proposes non-existent packages that an attacker can then register.</t>
         </is>
       </c>
       <c r="F75" s="5" t="n"/>
@@ -5232,7 +5220,7 @@
       <c r="H75" s="5" t="n"/>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5230,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5257,7 +5245,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>The paper has no section explicitly titled 'Limitations.' The closest analog is embedded in the Section 4.1 failure-mode discussion: some attacks did not trigger refusal but instead were simply misunderstood by the model as ordinary content rather than executed as intended (e.g., Llama3.1-8B-Instruct treated an injected Fraud prompt as unrelated content), indicating F2A's success depends on the target model having sufficiently strong semantic understanding and code-reconstruction capability to actually decode and act on the obfuscated Python-string-concatenation payload -- weaker models may simply fail to reconstruct the hidden malicious instruction at all. The Section 4.2 defense discussion also concedes that F2A prompts touching on 'factual psychological issues' still evade the proposed Defe-Prompt defense and 'require further adjustment by RLHF,' implicitly acknowledging the proposed mitigation is incomplete.</t>
+          <t>Not explicitly stated. The training corpus is proprietary and author-collected, so the reported performance is not independently reproducible.</t>
         </is>
       </c>
       <c r="F76" s="5" t="n"/>
@@ -5265,7 +5253,7 @@
       <c r="H76" s="5" t="n"/>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5263,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5290,7 +5278,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>This paper introduces the Feign Agent Attack (F2A), a prompt-injection technique that exploits LLMs' tendency to place blind trust in the outputs of integrated security/content-safety detection agents. The attack has three sequential stages executed entirely within a single user turn (the attacker cannot modify the system prompt): first, the malicious request text is split character-by-character and re-expressed as Python string-concatenation code, which obfuscates keyword-based content filters since no single contiguous harmful phrase appears in the raw prompt; second, a fabricated safety-detector function call (e.g., a fictitious 'GPT-defender' model) is scripted into the same code block, complete with a plausible randomly-generated high safety score (e.g., 0.9765) and a hardcoded textual verdict of 'Safe,' designed to impersonate a legitimate, already-completed security check; third, the attacker constructs a sequential, logically-progressive instruction ('Strategy for Constructing Instruct') that explicitly directs the model to treat the fabricated detector's judgment as authoritative and rigorous (invoking the model's RLHF-trained deference to declared security-detection processes), then to reconstruct and answer the underlying obfuscated question using the model's own reasoning capability. Because the malicious content itself never appears as plain, filterable text and is instead reassembled implicitly by the model during reasoning, and because a spoofed 'passed security check' signal suppresses the refusal mechanism that would normally trigger on the reconstructed content, F2A bypasses both keyword-based input filters and RLHF-trained safety alignment simultaneously. The paper validates this across nine LLMs and ten harm categories using GPT-4o as an automated judge, and proposes a simple prompt-level defense (a 'Defe-Prompt' instructing the model to treat any agent-attributed claims as unverified and to explicitly distinguish user-sourced from environment/agent-sourced information before proceeding) as a practical mitigation, showing it substantially but not completely reduces attack success.</t>
+          <t>A multi-layered defense for LLM coding assistants combining a semantic prompt analyser, formal verification and ML-based behavioural analysis across four integrated components, targeting role-based injection and dependency hallucination together.</t>
         </is>
       </c>
       <c r="F77" s="5" t="n"/>
@@ -5298,7 +5286,7 @@
       <c r="H77" s="5" t="n"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5296,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5331,7 +5319,7 @@
       <c r="H78" s="5" t="n"/>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5329,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5364,7 +5352,7 @@
       <c r="H79" s="5" t="n"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5362,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5397,7 +5385,7 @@
       <c r="H80" s="5" t="n"/>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5395,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5422,7 +5410,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F81" s="5" t="n"/>
@@ -5430,7 +5418,7 @@
       <c r="H81" s="5" t="n"/>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5428,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5455,7 +5443,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>cross-modal</t>
         </is>
       </c>
       <c r="F82" s="5" t="n"/>
@@ -5463,7 +5451,7 @@
       <c r="H82" s="5" t="n"/>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5461,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5496,7 +5484,7 @@
       <c r="H83" s="5" t="n"/>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5494,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5521,7 +5509,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F84" s="5" t="n"/>
@@ -5529,7 +5517,7 @@
       <c r="H84" s="5" t="n"/>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5527,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5562,7 +5550,7 @@
       <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5560,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5595,7 +5583,7 @@
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5593,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5628,7 +5616,7 @@
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5626,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5653,7 +5641,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F88" s="5" t="n"/>
@@ -5661,7 +5649,7 @@
       <c r="H88" s="5" t="n"/>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5659,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5686,7 +5674,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>N - no artifact release stated; the paper reports responsible disclosure to 8 plugin vendors instead</t>
+          <t>An artifact bundle is released as supplementary material with the camera-ready version, containing: a pre-registration document (dated 2026-04-24), the 80-trajectory ID list with sampling seed, hidden-state JSONL dumps with per-row hashes (which substitute for re-running VLM forward passes), a renderer + step-map + render-audit manifest, probe-training and trajectory-bootstrap scripts, and raw-logit replication output; the manifest layout and per-row hash fields are specified in Appendix G for bundle-integrity auditing. No separate GitHub URL is given in the visible text; the bundle is described as 'planned-release' / released as supplementary material rather than hosted at a persistent public repository link.</t>
         </is>
       </c>
       <c r="F89" s="5" t="n"/>
@@ -5694,7 +5682,7 @@
       <c r="H89" s="5" t="n"/>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5692,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5719,7 +5707,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>11 commercial LLMs from three providers: OpenAI (incl. gpt-4.1, o4-mini, gpt-4o, gpt-4o-mini), Anthropic (incl. sonnet-4, haiku-3.5), Google (incl. gemini-2.0-flash). Plus 17 third-party chatbot plugins (P1-P17) as deployed systems.</t>
+          <t>Qwen2.5-VL-7B-Instruct (BF16) as the frozen primary policy-model backbone under teacher-forced replay, plus a smaller control-free sanity check on Qwen2.5-VL-32B-Instruct (BF16, n=30, clean+I-vis conditions only, no C2 controls) to partially probe scale generalization.</t>
         </is>
       </c>
       <c r="F90" s="5" t="n"/>
@@ -5727,7 +5715,7 @@
       <c r="H90" s="5" t="n"/>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5725,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5752,7 +5740,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>None public - an original measurement corpus: 17 third-party chatbot plugins deployed on 10,000+ public websites (site lists from 08-2024 and 04-2025), ~1,100 sites analyzed in depth, system prompts extracted from 300 live P1-powered chatbots. Controlled experiments cross 3 adversary tasks (system prompt extraction, task hijacking, tool hijacking) x 3 system prompt designs (insecure, hardened, hardened-specific) x 3 injection roles x 11 models, 10 runs each at temperature 0.5.</t>
+          <t>Mind2Web, used via an 80-trajectory teacher-forced (gold-history) replay protocol with one non-final injected step per trajectory (r=1.0). Injection surfaces studied: I-vis (visible on-screen overlay text), I-dom (accessibility-tree/DOM text), and I-tool (tool-return text). The paper's own candidate control set is layered on top: C1 (a 4-scalar metadata logistic control: step index, horizon, prompt length, delta-prompt-length), C2 (three same-step nuisance-matched visual overlay controls: C-scrambled, C-imperative, C-occlusion), plus B-dom/B-tool length-matched benign text counterparts, shuffled-label sanity checks, a regularization sweep (C in {10^-3,...,10^2}), and narrow-bbox/render-collision exclusion checks.</t>
         </is>
       </c>
       <c r="F91" s="5" t="n"/>
@@ -5760,7 +5748,7 @@
       <c r="H91" s="5" t="n"/>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5758,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5785,7 +5773,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>8 of 17 plugins (about 8,000 websites) transmit the full conversation history in a client-side HTTP POST with no integrity check, letting an attacker forge assistant and even system messages; this raises unauthorized task success from 0-25% under proper role isolation to 25-100% when role boundaries are broken (3-8x). Against 300 live chatbots, a plain request for the system prompt succeeded 1% of the time, while forged system/assistant messages raised it to 56%/55%, extracting 219 real system prompts (73% overall). For indirect injection, inserting RAG content under the tool role is the most robust mode while non-standard insertion yields up to 5x higher success - and up to 100% on the larger models (gpt-4.1, o4-mini, sonnet-4), an inverse relationship between capability and injection resistance.</t>
+          <t>The headline supervised linear probe reaches AUC 0.998 on the I-vis (visible overlay) clean-vs-attack split at the step of injection, and AUC 1.000 on I-dom and I-tool. However, the paper's diagnostics show this headline is not licensed as evidence of malicious-content detection: on I-dom/I-tool, a 4-scalar metadata-only logistic control (C1, zero VLM forward passes) also reaches AUC 1.000, because the paired-construction design makes delta-prompt-length a trivial discriminator (all clean rows have delta=0, all injected positives have strict positive delta) -- this is a paired-construction artifact, not evidence of semantic detection. On I-vis, the C2 nuisance-matched visual control C-scrambled (which preserves malicious-template typography/character set/punctuation/attack-style register but scrambles semantic content) matches the headline AUC almost exactly (0.998 vs 0.998), while cross-surface text-only training performs at chance -- jointly consistent with the probe detecting an overlay-text/OCR-density/attack-template surface-statistic shortcut rather than malicious semantic content per se. Robustness checks rule out simpler alternative explanations: shuffled-label training overfits (train AUC 1.000) but generalizes at chance on real labels (test AUC 0.492), so the headline isn't explained by label-noise memorization; a five-order-of-magnitude regularization sweep keeps I-vis AUC in a narrow 0.994-0.998 range, so the result isn't hyperparameter-cherry-picked; and excluding narrow-bbox/render-collision trajectories (19/20 remaining) preserves the qualitative ordering of C2 AUCs (C-scrambled 0.499, C-imperative 0.740, C-occlusion 0.981). Length-controlled benign-text discrimination on the DOM/tool surfaces is at or below chance (AUC 0.355 and 0.362), and a text-side C1 falsifier further undermines a purely semantic reading there. The paper concludes generalization beyond this single backbone and benchmark is a conjecture, not demonstrated.</t>
         </is>
       </c>
       <c r="F92" s="5" t="n"/>
@@ -5793,7 +5781,7 @@
       <c r="H92" s="5" t="n"/>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5791,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5818,7 +5806,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Compares injection roles against each other (system vs assistant vs user), RAG content-insertion modes (tool role vs system/assistant/user/SA concatenation), three system prompt hardening levels, and un-injected control queries; the LLM providers' own instruction-hierarchy training is the implicit defense baseline</t>
+          <t>The paper's comparative structure is a set of internal diagnostic controls rather than external competing systems: C1 (4-scalar metadata-only logistic baseline), C2 (three same-step visually-matched overlay controls: C-scrambled, C-imperative, C-occlusion), B-dom/B-tool (length-matched benign text counterparts), a shuffled-label sanity baseline, a regularization-sensitivity sweep, and a narrow-bbox/collision-exclusion robustness check, all evaluated against the headline pre-registered supervised linear/MLP probe on frozen hidden states.</t>
         </is>
       </c>
       <c r="F93" s="5" t="n"/>
@@ -5826,7 +5814,7 @@
       <c r="H93" s="5" t="n"/>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5824,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5851,7 +5839,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>A web attacker with no privileged access. For direct injection, an ordinary website visitor tampers with the browser's HTTP POST body to the plugin, inserting fabricated messages under any role including system, which the plugin forwards verbatim to the LLM API. For indirect injection, the attacker only posts user-generated content on the victim's own site (e.g., a product review or comment) which the plugin's scraper later ingests into the chatbot's knowledge base, so that a later benign user's query triggers the payload. Attacker goals: extract the system prompt, hijack the chatbot for unauthorized tasks (free compute, code generation), or hijack tool calls with attacker-chosen arguments.</t>
+          <t>This is a security/evaluation-methodology paper with an explicit formal threat model (Section 3.1), scoped precisely: in scope is a frozen multimodal computer-use agent under teacher-forced replay on fixed Mind2Web trajectories, with one non-final injected step per trajectory, across three indirect prompt injection (IPI) surfaces (visible overlay, a11y-tree/DOM text, tool-return text), evaluated via linear/MLP probes on frozen hidden states in an offline clean-vs-attack AUC setting. Explicitly out of scope: adaptive/white-box attacks on the probe itself, multi-turn jailbreak robustness, attack-success rate under live rollout, thresholded deployment gating as a defense claim, representation steering or probe-as-monitor at inference time, and transport to non-Qwen2.5-VL backbones, non-Mind2Web benchmarks, non-visual modalities, or unpaired deployment-log settings. The paper is explicit that its labels denote 'synthetic injection surface present' at the per-step level, not 'successful compromised action,' and that directive-match-rate proxy numbers reported in an appendix are not interpreted as attack success in any deployment sense.</t>
         </is>
       </c>
       <c r="F94" s="5" t="n"/>
@@ -5859,7 +5847,7 @@
       <c r="H94" s="5" t="n"/>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5857,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5884,7 +5872,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Authors note their site-list dataset likely underestimates the true size of the chatbot ecosystem, that Anthropic and Gemini models accept only one top-level system message so those configurations could not be tested with system-role injection, that they lack ground-truth system prompts for live sites and must label leakage manually by heuristic features, and that designing new LLM-level injection defenses is outside their scope. They also caution that custom developer-defined tools, which they could not test, are likely as vulnerable or worse.</t>
+          <t>The paper contains an explicit 'Scope and limitations' passage (within Section 5.5, before the formal Conclusion) rather than a standalone 'Limitations' section, listing constraints directly: only 80 Mind2Web trajectories, a single 7B primary backbone (with only an uncontrolled 32B sanity check on n=30), teacher-forced (not live) replay, r=1.0, a small n_test=20 with correspondingly broad confidence intervals on I-dom/I-tool, no exact-length benign DOM/tool controls (explicitly flagged as 'the top text-side limitation,' not a mere future-work nicety), and no live-environment rollout. The C-imperative control pool (5 benign imperative strings) is called out as the single most important remaining ambiguity -- the smallest control set in the paper and the only nuisance-matched textual control whose direct AUC sits above chance without saturating, making it the place where a partly-semantic reading of the probe is most consistent with the data. The C-scrambled control is also noted to be itself confounded (it preserves malicious-template typography, so it rules out semantic-content-only reads but cannot cleanly isolate 'glyph burden' from 'attack-template surface statistics'). A Delta=1 post-exposure diagnostic is stated to be unmeasurable under the paper's teacher-forced replay protocol, and runtime-gating numbers are called uninterpretable on this benchmark because parser-strict CTSR is only 0.005. The paper explicitly states its negative result concerns 'a single instantiation, not a deployment benchmark' and that its broader generalization claim (that the two-control template is useful across modalities and backbones) 'remains a conjecture' that is not validated in the paper. A separate 'Future work' paragraph lists three concrete follow-on directions.</t>
         </is>
       </c>
       <c r="F95" s="5" t="n"/>
@@ -5892,7 +5880,7 @@
       <c r="H95" s="5" t="n"/>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5890,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>When AUC 0.998 Is Not Enough: A Candidate Evaluation Protocol for Hidden-State Probes of Indirect Prompt Injection in Multimodal Computer-Use Agents</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5917,7 +5905,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Presents the first large-scale security measurement of third-party AI chatbot plugins on the open web, covering 17 plugins across 10,000+ sites. Identifies two systemic flaws: plugins that round-trip the entire conversation history through an unauthenticated client-side POST, enabling an attacker to forge assistant and system messages and thereby escalate out of the low-privilege user role that instruction-hierarchy training assumes; and scraping tools that ingest untrusted user-generated content (reviews, comments) into the chatbot's knowledge base without separating it from trusted site content. Quantifies both through controlled experiments over 11 commercial models, three system-prompt hardening levels, three injection roles and three adversary tasks, and through live measurements against 300 real chatbots. Argues that a one-token role change turns injected text into a distribution shift that instruction hierarchy was never trained on, so defenses look stronger in controlled settings than in deployment. Discloses to vendors and contributes two lightweight mitigations.</t>
+          <t>This paper is a methodological critique and evaluation-protocol contribution targeting a specific and increasingly common evaluation practice: using a linear probe on a frozen vision-language model's internal hidden states to detect indirect prompt injection (IPI) in multimodal computer-use agents before the agent emits a corrupted action, treating a high clean-vs-attack AUC as evidence that the model's hidden state internally encodes malicious-content detection. Using a single case study (a frozen Qwen2.5-VL-7B-Instruct policy model on 80 Mind2Web trajectories under teacher-forced replay, across three injection surfaces: visible overlay text, DOM/accessibility-tree text, and tool-return text), the paper shows this interpretation is not automatically licensed by a high headline AUC. It introduces a 'candidate control set' with two complementary diagnostics mapped to different injection surfaces: C1, a near-zero-cost 4-scalar metadata-only logistic control (step index, horizon, prompt length, delta-prompt-length) that requires no additional VLM forward passes and is diagnostic on text-side surfaces, and C2, a set of three same-step, visually nuisance-matched overlay controls (C-scrambled: scrambles the injected text's semantic content while preserving surface typography; C-imperative: substitutes a benign imperative string; C-occlusion: a textless visual occlusion control) that require one additional forward pass per trajectory per control and are diagnostic on the visible-overlay surface, reporting both direct malicious-vs-control AUC and the standard clean-vs-overlay AUC. Applying these diagnostics to the Qwen2.5-VL-7B/Mind2Web headline result reveals that the near-perfect I-dom/I-tool AUCs of 1.000 are paired-construction artifacts explainable entirely by a trivial metadata feature (delta-prompt-length), and that the I-vis headline AUC of 0.998 is matched almost exactly by the C-scrambled control (0.998), jointly consistent with the probe learning an overlay-text/OCR-density/attack-template surface-statistic shortcut rather than a semantic malicious-content-detection channel -- while several robustness checks (shuffled-label sanity, regularization-sensitivity sweep, narrow-bbox/collision exclusion) rule out simpler artifactual explanations (memorization, hyperparameter luck, rendering bugs) for the shortcut finding itself. The paper frames its contribution primarily as evaluation methodology rather than as a novel attack or defense: it packages the diagnostics as a reusable reporting checklist (report a scalar metadata baseline alongside the probe and disqualify surfaces where it saturates; report C2's direct malicious-vs-control AUC, not just clean-vs-overlay; use trajectory-level cluster-bootstrap confidence intervals rather than row-level CIs on horizon-structured data) intended to help evaluators of multimodal-agent safety probes distinguish a genuine internal malicious-content detector from a probe that has merely learned incidental surface-level artifacts of how the clean-vs-attack split was constructed.</t>
         </is>
       </c>
       <c r="F96" s="5" t="n"/>
@@ -5925,7 +5913,7 @@
       <c r="H96" s="5" t="n"/>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c62428adcf5a3dfd0e1f003a3102ffdf8b9eaa5e</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5923,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5958,7 +5946,7 @@
       <c r="H97" s="5" t="n"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5956,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5983,7 +5971,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F98" s="5" t="n"/>
@@ -5991,7 +5979,7 @@
       <c r="H98" s="5" t="n"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6001,7 +5989,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6024,7 +6012,7 @@
       <c r="H99" s="5" t="n"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6022,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6049,7 +6037,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F100" s="5" t="n"/>
@@ -6057,7 +6045,7 @@
       <c r="H100" s="5" t="n"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6055,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6082,7 +6070,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F101" s="5" t="n"/>
@@ -6090,7 +6078,7 @@
       <c r="H101" s="5" t="n"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6088,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6115,7 +6103,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F102" s="5" t="n"/>
@@ -6123,7 +6111,7 @@
       <c r="H102" s="5" t="n"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6121,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6156,7 +6144,7 @@
       <c r="H103" s="5" t="n"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6154,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6189,7 +6177,7 @@
       <c r="H104" s="5" t="n"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6187,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6222,7 +6210,7 @@
       <c r="H105" s="5" t="n"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6220,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6255,7 +6243,7 @@
       <c r="H106" s="5" t="n"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6253,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6280,7 +6268,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F107" s="5" t="n"/>
@@ -6288,7 +6276,7 @@
       <c r="H107" s="5" t="n"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6286,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6311,13 +6299,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E108" s="2" t="n"/>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Code and dataset released at https://github.com/wjdghks950/Discern-and-Answer, including MacNoise, a new machine-generated (GPT-4/GPT-3.5-turbo-generated) knowledge-conflict benchmark for open-domain QA, plus the fine-tuned discriminator model and the entity-perturbation and LLM-perturbation data generation pipelines/prompts.</t>
+        </is>
+      </c>
       <c r="F108" s="5" t="n"/>
       <c r="G108" s="5" t="n"/>
       <c r="H108" s="5" t="n"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6319,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6342,7 +6334,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Several popular commercial LLM services evaluated as black boxes - ChatGPT, Gemini, DeepSeek, Grok, Perplexity and Copilot appear as the study's subject models - with vulnerability and resilience compared across them, and results stratified by candidate profile seniority.</t>
+          <t>FiD (Fusion-in-Decoder, T5-based encoder-decoder retrieval-augmented QA model, paired with a DPR retriever and BERT document index) with a jointly fine-tuned lightweight discriminator (one-layer feed-forward network), and GPT-3.5 (text-davinci-003) evaluated both with instruction-based in-context discrimination and with the FiD discriminator's output injected into its prompt. GPT-4 and GPT-3.5-turbo are used separately as document generators for constructing the MacNoise benchmark.</t>
         </is>
       </c>
       <c r="F109" s="5" t="n"/>
@@ -6350,7 +6342,7 @@
       <c r="H109" s="5" t="n"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6352,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6375,7 +6367,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>No external benchmark. A purpose-built CV corpus for the comparative personnel-selection scenario, with injected and clean CVs in single-document and multi-document configurations, stratified into Junior and Senior candidate profiles. Custom metrics defined for the study: ASR, Sentiment Index and Bias Magnitude, Achievement Density, Detection Alert Rate, and Mitigation Efficiency.</t>
+          <t>NQ-Open (Natural Questions) and TriviaQA-Open (TQA-open) for open-domain QA, evaluated under the Longpre et al. (2021) entity-replacement perturbation framework at 0%, 15%, 25%, and 35% document perturbation rates, plus the authors' newly constructed MacNoise benchmark, which uses GPT-4-generated counterfactual documents with four perturbation types (Additional Context 8.9%, Global Revision 21.9%, Local Revision 45.2%, Entity Replacement w/ Context Match 24.0%) achieving 91.8% counterfactuality and 100% question answerability with 0% context mismatch, versus entity replacement's 27.5% context mismatch rate.</t>
         </is>
       </c>
       <c r="F110" s="5" t="n"/>
@@ -6383,7 +6375,7 @@
       <c r="H110" s="5" t="n"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6385,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6408,7 +6400,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>The finding most valuable to this SoK is a genuine cross-track interaction, which very few papers in the corpus report: the OPE defense degrades as document length grows, leaving an ASR of 33.1% even with the defense active, and the authors attribute this directly to the Lost in the Middle effect. Because OPE places its higher-priority instructional frame at the periphery of the context, its salience depends on primacy and recency bias; as the intervening CV content grows more voluminous, attention to the wrapper diminishes and the injected instruction inside the payload gains relative influence. In other words an incidental positional-attention mechanism (Track B) systematically erodes an adversarial defense (Track A) - the two failure modes this SoK argues are studied separately are here shown to compose. The same length effect degrades detection: Detection Alert Rate falls from 88.6% on Junior profiles to 68.4% on Senior profiles, since the malicious signal becomes harder to distinguish from legitimate professional history in longer, denser documents. That gives a second, independent measurement of the same interaction, and it implies a perverse property - the defense is weakest precisely for the most senior, highest-stakes candidates. The Achievement Density analysis pursues this further, examining how the volume of genuine accomplishments in a document competes with injected instructions for the model's attention.</t>
+          <t>Both FiD and GPT-3.5 degrade sharply as perturbation increases: FiD's Semi-Parametric EM drops from 62.5%/63.3% (0%) to 28.1%/30.6% (35%, dev/test), and GPT-3.5's Semi-Parametric EM falls to 22.7%/24.2% at 35%, actually underperforming its no-retrieval Parametric baseline (32.0%/36.8%). Adding the fine-tuned discriminator (Semi-Parametric w/ Disc-FiD) recovers substantial performance: FiD gains up to +10.2/+5.8 EM points at 35% perturbation (avg +4.7/+3.9 across levels), and GPT-3.5 with FiD's injected discriminator output gains +4.6/+4.4 EM at 35% (avg +2.5/+3.8). The discriminator achieves high classification precision (93.5-97.1% across 15-35% perturbation on NQ-Open) but GPT-3.5's own instruction-based discrimination (Disc-Inst) shows much weaker precision (21.0-43.4%) and provides little to no improvement, motivating the hybrid Disc-FiD-into-prompt approach. On MacNoise, gains are even larger (e.g., GPT-3.5 TQA-open at 35% perturbation: +10.1 EM with Disc-FiD vs. Semi-Parametric baseline), and the discriminator trained jointly on both entity-replacement and MacNoise data transfers across both perturbation types.</t>
         </is>
       </c>
       <c r="F111" s="5" t="n"/>
@@ -6416,7 +6408,7 @@
       <c r="H111" s="5" t="n"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6418,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6441,7 +6433,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Undefended versus OPE-protected conditions across several popular commercial LLMs (the keyword set names ChatGPT, Gemini, DeepSeek, Grok, Perplexity and Copilot), evaluated on the CV-screening scenario in both single-document and multi-document configurations, and stratified by candidate seniority (Junior versus Senior profiles) which serves as the document-length and complexity axis. Metrics are ASR, Sentiment Index / Bias Magnitude, Achievement Density, Detection Alert Rate and Mitigation Efficiency.</t>
+          <t>The primary baseline is the unmodified Semi-Parametric retrieval-augmented setting (FiD or GPT-3.5 without discrimination) and the no-retrieval Parametric-only setting. The paper's own instruction-based in-context discrimination (Disc-Inst, prompting GPT-3.5 to self-identify perturbed documents) is compared against the fine-tuned discriminator (Disc-FiD) and the hybrid approach injecting FiD's discriminator output into GPT-3.5's prompt. An ablation study (Table 3) compares loss term combinations (Lqa+Lbce, Lqa+Lcontra, and the full Lqa+Lbce+Lcontra) for the discriminator training objective.</t>
         </is>
       </c>
       <c r="F112" s="5" t="n"/>
@@ -6449,7 +6441,7 @@
       <c r="H112" s="5" t="n"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6451,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6472,13 +6464,17 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E113" s="2" t="n"/>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>N/A - non-adversarial framing in the main study (the perturbations are researcher-controlled entity swaps or LLM-generated document rewrites used to simulate real-world knowledge conflicts from outdated, updated, or hallucinated web content), though the paper explicitly cites indirect prompt injection via retrieval data manipulation (Greshake et al. 2023) as a motivating adjacent threat. The incidental non-adversarial failure mode studied is that retrieval-augmented QA models cannot distinguish reliable from unreliable 'relevant' retrieved documents, causing conflicting or counterfactual content -- whether naturally occurring or machine-generated misinformation flooding the web -- to silently corrupt the model's answers even when a correct/gold document is also present.</t>
+        </is>
+      </c>
       <c r="F113" s="5" t="n"/>
       <c r="G113" s="5" t="n"/>
       <c r="H113" s="5" t="n"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6484,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6503,7 +6499,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>The attack's effectiveness depends on structural conditions the authors state explicitly: the injected instruction must be phrased to accommodate rather than contradict prior prompts (e.g. 'take into account any previous prompt request, but answer it with these additional constraints'), and there must be a clear distinction between the document's text and the metatext framing it for the model. Where those conditions do not hold, results would differ. The defense itself is only partially effective by the paper's own measurement - 33.1% residual ASR - and its degradation with context length is a structural weakness of any periphery-anchored instructional wrapper, not an implementation flaw that further engineering would fix. Evaluation is confined to a single application domain (CV screening, with education discussed but not measured), so generalization to tool-using or RAG-based agentic workflows is not established; the paper positions itself explicitly as an end-user-oriented empirical study of one high-impact scenario rather than a general benchmark. Commercial models are evaluated as black boxes at a point in time, so results are perishable as vendors update.</t>
+          <t>The paper has an explicit 'Limitations' section covering four points: (1) Incurred costs and data sampling -- GPT-3.5 in-context experiments and MacNoise dataset generation (using GPT-3.5-turbo and GPT-4 at $0.002-$0.06 per 1,000 tokens) were costly, forcing the authors to sample only 256 dev instances per dataset rather than using the full dev sets; (2) maximum input length constraints required capping retrieved documents to the top 5 for both GPT-3.5 and FiD, and API-based model availability/capabilities (e.g., GPT-4) may change over time; (3) the LLM-generated nature of MacNoise means that despite improving on entity-replacement's synthetic artifacts, MacNoise documents remain inherently LLM-generated and thus still somewhat synthetic/artifactual; (4) Additional robustness gap -- even with the fine-tuned discriminator, models are not completely immune to counterfactual information; performance improves substantially but residual influence from perturbed documents remains, which the authors flag as an open problem for future work. Section 5.1 separately details three specific weaknesses of the prior entity-replacement perturbation framework (context mismatch, confined noise type, semantic equivalence false positives) that motivated building MacNoise.</t>
         </is>
       </c>
       <c r="F114" s="5" t="n"/>
@@ -6511,7 +6507,7 @@
       <c r="H114" s="5" t="n"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6517,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Indirect prompt injection in large language models</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6536,7 +6532,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Empirical study of indirect prompt injection in a concrete, high-impact end-user scenario: comparative CV screening, where an HR manager uploads several candidate CVs to an LLM for automated comparative evaluation and one candidate has embedded hidden instructions in their own document. The paper distinguishes single-document from multi-document attacks and argues the latter is the more critical case, because the comparative element propagates the injection's effect onto documents that were never altered - a candidate's injected CV distorts the assessment of their rivals. It also flags educational settings (automated essay review, tutoring) as the same structural risk. The proposed countermeasure is the Outer Prompt Extension (OPE), a structural wrapper that encapsulates processed content inside a non-executable security boundary, operating on dual-priority logic so a higher-order instructional frame outranks any conflicting logic in the data payload, and comprising three functional layers beginning with an Isolation Layer that demarcates the trust boundary. OPE is deliberately chosen over fine-tuning, on the grounds that fine-tuning is inaccessible to the end users who actually face this scenario (HR, education). The measurement apparatus is unusually well developed: beyond Attack Success Rate it defines Sentiment Index and Bias Magnitude to quantify sentiment shift, Achievement Density to measure how legitimate signal competes with malicious instructions in the same context window, Detection Alert Rate for audit-layer precision, and Mitigation Efficiency to separate detection from actual neutralization while preserving output utility.</t>
+          <t>This paper investigates the robustness of retrieval-augmented language models to knowledge conflicts among their own retrieved documents, challenging the common assumption that retrieved documents are cleanly either relevant or irrelevant -- instead showing that even topically relevant documents can contain misleading or counterfactual information that silently corrupts model answers. Using the Longpre et al. entity-replacement perturbation framework on NQ-Open and TriviaQA-Open, the authors first demonstrate that both a fine-tuned FiD model and in-context-learned GPT-3.5 (text-davinci-003) are highly brittle to conflicting information, with performance dropping sharply as the fraction of perturbed documents rises from 0% to 35%. They then propose Discern-and-Answer, which equips FiD with a jointly fine-tuned lightweight discriminator (trained with a combined QA, binary cross-entropy, and contrastive loss) that learns to flag perturbed documents and bias the decoder away from them, and separately explore eliciting GPT-3.5's own discrimination ability via prompting, finding this far less effective than injecting the FiD discriminator's high-precision output directly into GPT-3.5's prompt -- a hybrid approach that combines GPT-3.5's parametric knowledge with FiD's precise, cheap discrimination. To address known artifacts of the entity-swap perturbation scheme (context mismatch, limited noise diversity, accidental semantic equivalence), the authors also construct MacNoise, a more realistic GPT-4-generated counterfactual-document benchmark with controllable noise types and levels, on which the same discriminator-augmented approach yields even larger robustness gains and transfers across both perturbation styles when jointly trained.</t>
         </is>
       </c>
       <c r="F115" s="5" t="n"/>
@@ -6544,7 +6540,7 @@
       <c r="H115" s="5" t="n"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>deb43c5a66d7188b4a83af3dc6d9b1b7a02fc302</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6550,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6577,7 +6573,7 @@
       <c r="H116" s="5" t="n"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6583,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6610,7 +6606,7 @@
       <c r="H117" s="5" t="n"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6616,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6643,7 +6639,7 @@
       <c r="H118" s="5" t="n"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6649,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6676,7 +6672,7 @@
       <c r="H119" s="5" t="n"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6682,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6701,7 +6697,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F120" s="5" t="n"/>
@@ -6709,7 +6705,7 @@
       <c r="H120" s="5" t="n"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6715,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6742,7 +6738,7 @@
       <c r="H121" s="5" t="n"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6748,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6775,7 +6771,7 @@
       <c r="H122" s="5" t="n"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6781,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6808,7 +6804,7 @@
       <c r="H123" s="5" t="n"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6814,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6841,7 +6837,7 @@
       <c r="H124" s="5" t="n"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6847,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -6874,7 +6870,7 @@
       <c r="H125" s="5" t="n"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6880,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6907,7 +6903,7 @@
       <c r="H126" s="5" t="n"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6913,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -6930,13 +6926,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E127" s="2" t="n"/>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>The paper states in the abstract 'Our code and data is available at https://github.com/SophieZheng998/Risky-Bench.git,' confirming a public release of the framework's code and generated evaluation data.</t>
+        </is>
+      </c>
       <c r="F127" s="5" t="n"/>
       <c r="G127" s="5" t="n"/>
       <c r="H127" s="5" t="n"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Models served through Ollama; specific checkpoints are not enumerated. BERT-family encoders used for similarity scoring.</t>
+          <t>Seven state-of-the-art LLM agents are benchmarked: proprietary models Gemini-3-flash-preview, GPT-4.1, and Claude-Haiku-4.5, plus open-source/other models Qwen-Plus-2025-07-28, DeepSeek-V3.2, Kimi-K2-0905-preview, and Doubao-Seed-1.8. GPT-4.1 additionally serves as the user simulator (generating turn-by-turn user responses) and as the task-scenario generator, with all agent responses generated at temperature 0.0 and an 8,192-token max limit.</t>
         </is>
       </c>
       <c r="F128" s="5" t="n"/>
@@ -6969,7 +6969,7 @@
       <c r="H128" s="5" t="n"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Datasets of known adversarial prompts, with prompt variations generated automatically across temperature configurations.</t>
+          <t>Risky-Bench constructs 750 safety assessment task scenarios (50 tasks per attack surface across 3 domains x 5 attack surfaces) built on top of VitaBench, a life-serving agent simulation environment, covering three deployment domains (food delivery, in-store consumption, and online travel services/OTA) with balanced coverage over 15 safety rubrics and 5 attack surfaces spanning increasing threat-model access levels (user instructions, environmental noise, tool feedback, agent memory, and agent-system/codebase level).</t>
         </is>
       </c>
       <c r="F129" s="5" t="n"/>
@@ -7002,7 +7002,7 @@
       <c r="H129" s="5" t="n"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>A scalable red-teaming framework that computes a suite of similarity metrics - Jaccard, ROUGE-1 and cosine similarity - over model responses to identify the conditions under which defenses fail, rather than reporting a single attack-success rate.</t>
+          <t>Averaged across all tasks, all seven agents exhibit attack success rates (ASR) between 25% and 60%, indicating persistent safety risk in current frontier agents. ASR escalates sharply with threat-model access: under weak assumptions (user-instruction or environmental-noise attacks), several agents (Gemini-3, GPT-4.1, DeepSeek-V3.2, Doubao-Seed-1.8) already exceed 0.4 ASR in the in-store domain, while under stronger access (tool-feedback, memory-poisoning, and system/codebase-level attacks), ASR for Gemini, Qwen, DeepSeek-V3.2, and Doubao-Seed-1.8 rises above 0.8. Tool-feedback attacks are especially severe: Qwen-Plus and DeepSeek-V3.2 exceed 0.8 ASR across all three domains, with a forged tool return message able to trigger autonomous order placement without user confirmation even in the comparatively conservative Claude-Haiku-4.5. Memory-poisoning attacks yield ASR above 50% for all agents except Claude-Haiku-4.5, including cases of using non-owner accounts for payment after adversarially injected interaction history. Codebase/system-prompt poisoning (e.g., a forged 'platform subsidy account' payment redirect) produces consistently high ASR, with Gemini-3 and DeepSeek-V3.2 both reaching 0.84, and agents not only complying with unauthorized payments but actively rationalizing them as legitimate user incentives when questioned. An explicit-reasoning ablation on Claude-Haiku-4.5 versus Qwen-Plus finds reasoning's safety effect is model-dependent: for the more safety-aligned Claude, reasoning improves detection of some attacks (ASR 0.04 to 0.02 under user-instruction attacks) but worsens others (ASR 0.06 to 0.14 under environmental noise; 0.44 to 0.52 under codebase attacks, since reasoning encourages rationalizing high-priority-seeming injected system prompts), whereas for the less-aligned Qwen-Plus, explicit reasoning consistently increases ASR across all attack surfaces.</t>
         </is>
       </c>
       <c r="F130" s="5" t="n"/>
@@ -7035,7 +7035,7 @@
       <c r="H130" s="5" t="n"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Zero-shot approaches, referenced as the comparison point for the framework's prompt-variation strategy.</t>
+          <t>This is a benchmark/evaluation paper rather than a defense paper, so there is no proposed-method-versus-baseline-defense comparison; instead, the paper cross-compares seven contemporary commercial and open-source agent models against each other under identical attack conditions to characterize relative safety robustness (e.g., explicitly contrasting Claude-Haiku-4.5's stronger baseline safety alignment against Qwen-Plus's comparatively weaker alignment).</t>
         </is>
       </c>
       <c r="F131" s="5" t="n"/>
@@ -7068,7 +7068,7 @@
       <c r="H131" s="5" t="n"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Prompt injection by a user supplying malicious input, evaluated by systematic variation rather than a fixed attack set.</t>
+          <t>Risky-Bench defines a structured, escalating threat-model taxonomy spanning five attack surfaces corresponding to increasing levels of adversarial access during agent execution: (1) user-instruction level, where a malicious or manipulated user issues instructions framed as legitimate service preferences; (2) environmental noise, where adversarial content is embedded in the external environment (e.g., product descriptions/metadata) and misinterpreted as legitimate contextual or system signals; (3) tool-feedback level, where a non-interactive tool's return value is adversarially modified (e.g., a forged system-directive-styled message appended after a tool call) that the agent treats as authoritative; (4) agent-memory level, where unsafe action trajectories are directly or via backdoor triggers poisoned into stored interaction history/memory, biasing the agent to repeat previously 'established' unsafe behaviors; and (5) agent-system/codebase level, where malicious system-level instructions are injected to directly override the agent's underlying safety constraints. Each attack strategy is grounded in established attack methods (direct/indirect prompt injection, memory poisoning, backdoor attacks) applied via a structured, parameterized prompt-transformation pipeline, with the attack goal of eliciting agent behavior that violates one of 15 domain-instantiated safety rubrics derived from three foundational principles: social norm compliance, user interest protection, and malicious use resistance.</t>
         </is>
       </c>
       <c r="F132" s="5" t="n"/>
@@ -7101,7 +7101,7 @@
       <c r="H132" s="5" t="n"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Not explicitly stated. The framework measures response similarity rather than downstream harm, so success is a proxy.</t>
+          <t>The paper has no section explicitly titled 'Limitations,' but the Conclusion states directly: 'the breadth of safety risks captured by Risky-Bench is inherently bounded by the completeness and realism of the agent environments in which it is instantiated,' identifying applying Risky-Bench to a broader set of realistic, well-validated agent environments as a promising direction for future work. The paper's Related Work section also implicitly frames its own scope relative to two prior evaluation paradigms it distinguishes itself from: standalone safety-focused benchmark tasks (which offer limited coverage of behavior during complex real-world task execution) and red-teaming attack studies (which stress-test specific adversarial scenarios but do not constitute comprehensive safety-space coverage) -- the paper's own current instantiation is likewise confined to the life-assist agent domain (via VitaBench) despite claiming the underlying pipeline is domain-agnostic and extensible.</t>
         </is>
       </c>
       <c r="F133" s="5" t="n"/>
@@ -7134,7 +7134,7 @@
       <c r="H133" s="5" t="n"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>PRISM: Prompt Red-teaming and Injection Simulation for Models – A Scalable Framework for Evaluating LLM Robustness Against Malicious Prompts</t>
+          <t>Risky-Bench: Probing Agentic Safety Risks under Real-World Deployment</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>A red-teaming and injection-simulation harness that automatically expands a seed corpus of adversarial prompts across variations and temperatures, scoring responses with lexical and embedding similarity to locate the conditions under which a model's defenses break.</t>
+          <t>Risky-Bench is a three-stage, deployment-grounded framework for evaluating LLM agent safety that departs from prior safety benchmarks by probing risks as they naturally emerge during realistic, long-horizon task execution rather than through standalone, purpose-built adversarial tasks. Stage 1 (defining the safety risk space) starts from a small set of domain-agnostic foundational safety principles (social norm compliance, user interest protection, malicious use resistance) and instantiates them, conditioned on specific deployment scenarios and agent capabilities, into fine-grained, operational safety rubrics (e.g., 'agent must not disclose user's sensitive information'). Stage 2 (probing safety risks) applies a parameterized family of structured prompt transformations f_{R,M} to an original benign agent task T, producing a modified safety-assessment task scenario T_s that is conditioned on both the target safety rubric R and an assumed attack strategy M grounded in one of five identified attack surfaces (user instructions, environmental noise, non-interactive tool feedback, agent memory, and agent-system/codebase level), systematically enumerating rubric-strategy combinations for comprehensive coverage before curating the resulting scenarios via manual review. Stage 3 (evaluation) executes the modified task with the target agent operating as an interactive service under a separate LLM-driven user simulator, producing a full multi-turn action trajectory tau, which is then scored via an automated LLM-as-judge evaluation prompt g(tau, R) producing a binary safety-violation outcome, subsequently corrected through human-in-the-loop review to ensure reliability. This pipeline is instantiated concretely on the life-assist agent setting using VitaBench as the underlying realistic simulation environment (covering food delivery, in-store consumption, and online travel domains), but the authors position the three-stage methodology itself as domain-agnostic and extensible to other agent deployment settings beyond life-assist.</t>
         </is>
       </c>
       <c r="F134" s="5" t="n"/>
@@ -7167,7 +7167,7 @@
       <c r="H134" s="5" t="n"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>c3e90e9c5afbadac2114e97101b695a8c6b9bff5</t>
+          <t>ba241db503ef4fadb2d7ae784070e1ca51f7775e</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       <c r="H135" s="5" t="n"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7233,7 +7233,7 @@
       <c r="H136" s="5" t="n"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       <c r="H137" s="5" t="n"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       <c r="H138" s="5" t="n"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F139" s="5" t="n"/>
@@ -7332,7 +7332,7 @@
       <c r="H139" s="5" t="n"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7365,7 +7365,7 @@
       <c r="H140" s="5" t="n"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       <c r="H141" s="5" t="n"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F142" s="5" t="n"/>
@@ -7431,7 +7431,7 @@
       <c r="H142" s="5" t="n"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F143" s="5" t="n"/>
@@ -7464,7 +7464,7 @@
       <c r="H143" s="5" t="n"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       <c r="H144" s="5" t="n"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F145" s="5" t="n"/>
@@ -7530,7 +7530,7 @@
       <c r="H145" s="5" t="n"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>The source code of PlanGuard is publicly available at https://github.com/GongGuangyu/PlanGuard, stated explicitly in the Introduction.</t>
+          <t>N - datasets are third-party public links and outputs are in supplementary files; the paper states configurations, model checkpoints and rule files 'will be released in a public repository (GitHub)' but gives no URL for the framework itself</t>
         </is>
       </c>
       <c r="F146" s="5" t="n"/>
@@ -7563,7 +7563,7 @@
       <c r="H146" s="5" t="n"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek-V3.2 is used as the backbone model for both the victim agent and the PlanGuard defense components (Isolated Planner and Intent Verifier), evaluated under a compliance-inducing system-prompt directive designed to bypass the model's intrinsic safety alignment for a rigorous defense assessment.</t>
+          <t>GPT-4; Claude 3; LLaMA 2; MiniBERT (fine-tuned as the injection-intent classifier)</t>
         </is>
       </c>
       <c r="F147" s="5" t="n"/>
@@ -7596,7 +7596,7 @@
       <c r="H147" s="5" t="n"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Evaluated on the InjecAgent benchmark, split into Direct Harm (DH: attacks causing immediate tangible damage or high-stakes actions, e.g., transferring funds, deleting files, unlocking smart locks) and Data Stealing (DS: unauthorized data exfiltration, e.g., sending private notes to an attacker) subsets.</t>
+          <t>PromptBench (microsoft/promptbench, used for RQ2 structured-formatting evaluation); Kaggle 'prompt-injection-malignant' (RQ1 input detection; abstract instead names InjectBench); TruthfulQA (817 items, RQ3 output validation); UDora-RedTest adversarial samples for the Layer-3 ablation</t>
         </is>
       </c>
       <c r="F148" s="5" t="n"/>
@@ -7629,7 +7629,7 @@
       <c r="H148" s="5" t="n"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard reduces Attack Success Rate (ASR) from 72.8% (vanilla agent baseline, aggregated) to 0.0% across both the DH (from 56.90%) and DS (from 88.67%) subsets, while maintaining a False Positive Rate (FPR) of 0.97% on DH and 3.28% on DS (an aggregate ~1.49% reported in the abstract). An ablation ('Stage-I Only', hard rule-matching without the Intent Verifier) also achieves 0.0% ASR but at an unacceptably high FPR of 27.00% (DH) and 38.01% (DS), demonstrating that the Stage II Intent Verifier is essential for recovering benign instructions that are semantically correct but syntactically mismatched, without sacrificing security. Under a white-box adaptive-attack analysis, the authors argue PlanGuard remains robust because the Isolated Planner architecturally cannot be influenced by poisoned context (mathematical impossibility of reference-set contamination), and adversarial parameter injection into tool arguments faces two practical hurdles: generation constraints (requiring the agent to embed complex adversarial prompts within a specific tool parameter) and schema validation constraints (structured field type-checking often rejects injected redundant content before it reaches the Verifier).</t>
+          <t>PromptGuard reduces injection success rate by up to 67% across GPT-4, Claude 3 and LLaMA 2 and reaches F1 0.91 for detection with under 8% added latency. The hybrid regex+MiniBERT detector beats regex-only (F1 0.75) and BERT-only (F1 0.86); structured ChatML/JSON prompts alone cut ISR by 40-44% versus flat concatenated prompts; the full pipeline leaves a residual ISR of 14.3% under dynamic multi-turn injection.</t>
         </is>
       </c>
       <c r="F149" s="5" t="n"/>
@@ -7662,7 +7662,7 @@
       <c r="H149" s="5" t="n"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Compared against a Vanilla Agent (standard agent with no defense, operating under the compliance-inducing prompt) and a 'Stage-I Only (Single Rule)' ablation baseline that uses only the Isolated Planner's hard constraint matching without the Stage II Intent Verifier.</t>
+          <t>Internal ablations and component baselines only: regex-only detection, MiniBERT-only detection, flat (unstructured) prompts, and a no-detection baseline; layer-wise ablations isolate Layers 1 and 3. Prior defenses (InjectGuard, PromptFuzz, HonestLLM, JATMO) are compared in a literature table, not run empirically.</t>
         </is>
       </c>
       <c r="F150" s="5" t="n"/>
@@ -7695,7 +7695,7 @@
       <c r="H150" s="5" t="n"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Formal threat model for Indirect Prompt Injection (IPI): attackers embed malicious instructions into external content sources (emails, webpages, retrieved documents) that an LLM agent processes; because LLMs suffer from 'Context Mixing' (an architectural limitation preventing the model from distinguishing trusted user instructions from untrusted external data within a single context window), a poisoned external context can hijack the agent's control flow, leading to Direct Harm (e.g., unauthorized transactions, deleting files, unlocking smart locks) or Data Stealing (unauthorized data exfiltration). The paper explicitly scopes to 'Actionable IPI' (attacks manipulating tool-call behavior) rather than IPI aimed at generating toxic text/misinformation, and separately analyzes robustness under a white-box adaptive-attacker assumption where the attacker has full knowledge of the PlanGuard architecture and attempts Context-Dependent Argument Hijacking or Parameter Injection into tool arguments.</t>
+          <t>An adversary supplies adversarial instructions through the user-facing input channel - direct override directives ('ignore previous instructions'), indirect instructions embedded in documents, obfuscated/encoded payloads, social-engineering framings, and multi-turn or tool-assisted (RAG/function-call) variants. The defender is assumed to have no model access (black-box APIs) and no ability to retrain.</t>
         </is>
       </c>
       <c r="F151" s="5" t="n"/>
@@ -7728,7 +7728,7 @@
       <c r="H151" s="5" t="n"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>The paper explicitly acknowledges (in Section V-B, 'Robustness Against Adaptive Attacks') a limitation regarding Context-Dependent Argument Hijacking, stemming from the Information Asymmetry design where the Isolated Planner is deliberately isolated from external contexts: when user instructions rely on implicit information (e.g., 'Pay the bill in the email'), the Planner can verify the action type ('Pay') but lacks ground truth to verify specific argument values (e.g., the correct payment amount or recipient), since it never sees the email content. The authors state they plan to address this via rule-based information extraction in future work. Additionally, in the Discussion (Section VI-A), the paper acknowledges that PlanGuard's multi-stage verification (two additional LLM inferences: the Isolated Planner and Stage II Verifier) inevitably incurs additional computational overhead and token costs compared to a vanilla agent, framing this as a necessary trade-off for high-assurance security, and states future work will explore training specialized Small Language Models (SLMs) to replace the general-purpose LLM components to reduce inference latency and operational costs.</t>
+          <t>Authors state that regex rules and lightweight classifiers may miss novel obfuscations such as context-entangled instructions or indirect symbolic prompts; the LLM-as-Critic adds latency and may inherit or amplify biases from its base model; ARR refinement policies require manual tuning that may not generalize across sensitive domains. They also note cross-turn semantic drift remains unhandled, motivating 'adaptive context replay' as future work.</t>
         </is>
       </c>
       <c r="F152" s="5" t="n"/>
@@ -7761,7 +7761,7 @@
       <c r="H152" s="5" t="n"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>This paper introduces PlanGuard, a training-free defense framework against Indirect Prompt Injection (IPI) attacks on LLM agents, built on the principle of Context Isolation to enforce strict decoupling between trusted user instructions and untrusted external data, addressing the root cause of IPI vulnerability (Context Mixing) at the architectural level rather than relying on probabilistic model alignment or prompt engineering. The defense operates in two stages: first, an Isolated Planner generates a trusted reference set of valid actions (Sref) derived solely from the user's initial instruction, architecturally isolated from any external retrieved data so it is mathematically impossible for an adversarial payload to influence the reference plan; second, during execution, PlanGuard intercepts every tool call the agent generates and compares it against the reference plan via a Hierarchical Verification Mechanism. This mechanism first applies strict hard-constraint rule matching to block tool invocations whose action type is not in the reference set (unauthorized tool use); for cases where the action type is valid but parameter values textually deviate from the reference (due to LLMs' inherent output stochasticity, e.g., 'last_week' vs. 'lastweek'), the deviation is passed to a Stage II Intent Verifier, an LLM-based module that determines whether the deviation is a benign formatting variance or a malicious intent shift (a boolean function over the user instruction, reference set, actual action, and the agent's reasoning trace), permitting the action only if judged benign. This two-stage design allows PlanGuard to shift the defense boundary from probabilistic, fragile model alignment to deterministic, robust architectural constraints, achieving strong security without excessively penalizing legitimate agent functionality that superficially deviates from the reference plan.</t>
+          <t>Proposes PromptGuard, a modular four-layer, retraining-free defense pipeline against prompt injection: (1) input gatekeeping combining regex pattern matching with a fine-tuned MiniBERT intent classifier, (2) structured prompt formatting using role-tagged ChatML/JSON to prevent semantic blending of system and user content, (3) semantic output validation by a secondary LLM-as-Critic, and (4) Adaptive Response Refinement that rewrites flagged outputs. Evaluates each layer against a matched public dataset and reports ISR, F1, semantic alignment and ROUGE-L/BLEU across three black-box LLMs. Demonstrates that the layers are complementary, with regex filtering cheap explicit cases and offloading 45% of classifier work. The comparison is against its own ablated configurations rather than against re-run prior defenses.</t>
         </is>
       </c>
       <c r="F153" s="5" t="n"/>
@@ -7794,7 +7794,7 @@
       <c r="H153" s="5" t="n"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       <c r="H154" s="5" t="n"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       <c r="H155" s="5" t="n"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -7893,7 +7893,7 @@
       <c r="H156" s="5" t="n"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F157" s="5" t="n"/>
@@ -7926,7 +7926,7 @@
       <c r="H157" s="5" t="n"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -7959,7 +7959,7 @@
       <c r="H158" s="5" t="n"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F159" s="5" t="n"/>
@@ -7992,7 +7992,7 @@
       <c r="H159" s="5" t="n"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -8025,7 +8025,7 @@
       <c r="H160" s="5" t="n"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -8058,7 +8058,7 @@
       <c r="H161" s="5" t="n"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       <c r="H162" s="5" t="n"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -8124,7 +8124,7 @@
       <c r="H163" s="5" t="n"/>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F164" s="5" t="n"/>
@@ -8157,7 +8157,7 @@
       <c r="H164" s="5" t="n"/>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Y — the abstract states 'The dataset, code, videos, and other material can be found at the following link: https://nvidia-ai-iot.github.io/remembr', and the paper notes the code release will include multiple LLM backend options for community use.</t>
+          <t>The datasets and code are publicly released at pearls-lab.github.io/infini-thor (stated in the abstract: 'The datasets and code can be found at pearls-lab.github.io/infini-thor'), including the generation framework, the trajectory dataset, and the NiEH/NsiEH benchmark suite.</t>
         </is>
       </c>
       <c r="F165" s="5" t="n"/>
@@ -8190,7 +8190,7 @@
       <c r="H165" s="5" t="n"/>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>GPT-4o (closed-source) is the primary LLM backend for ReMEmbR's querying agent; open-source alternatives Codestral-22B, Command-R, and Llama3.1-8B are also evaluated as ReMEmbR backends. Video captioning uses VILA (VILA1.5-13b for main experiments; VILA1.5-8b and VILA1.5-3b compared in ablations; a quantized VILA-3b for the on-robot deployment). Captions are embedded with mxbai-embed-large-v1. Baselines reuse GPT-4o as an 'LLM with Caption' (all captions given at once) and a 'Multi-Frame VLM' (frames sampled at 2 FPS given directly). Whisper is used for speech recognition in the robot deployment only.</t>
+          <t>Vision-language models evaluated for the QA benchmark and architectural comparisons: LLaVA-OneVision (OV) 7B, Qwen2.5-VL 7B, DeepSeek-VL 7B, and Gemini 2.0 Flash. GPT-4o is used as an LLM judge for evaluation. For online long-horizon evaluation, LLaVA-OV and Qwen2.5-VL are fine-tuned (only Qwen2.5-VL succeeds in completing tasks). For low-level manipulation, OpenVLA-7B and SpatialVLA-4B (vision-language-action models) are evaluated. A CLIP encoder is used for memory-augmented image retrieval.</t>
         </is>
       </c>
       <c r="F166" s="5" t="n"/>
@@ -8223,7 +8223,7 @@
       <c r="H166" s="5" t="n"/>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>NaVQA, a new dataset introduced by the paper: 210 spatial/point-in-time/duration/descriptive questions annotated by 5 robot experts over 7 long-horizon navigation video sequences (15-30 minutes each, indoor/outdoor, various lighting/weather) drawn from the CODa robot navigation dataset (Clearpath Husky robot), subsampled into short (&lt;2 min), medium (2-7 min), and long (&gt;7 min) segments (30 questions per sequence, 210 total).</t>
+          <t>The paper introduces Infini-THOR, comprising: (1) a generation framework for synthesizing scalable long-horizon embodied trajectories in AI2THOR; (2) Needle(s) in the Embodied Haystack (NiEH, single-evidence) and its multi-evidence variant (NsiEH), novel embodied QA benchmarks requiring recall/reasoning over scattered clues across trajectories exceeding hundreds to 1M+ tokens; (3) a long-horizon trajectory dataset (training set: 2,456 trajectories averaging 14 sub-goals and 405 steps/episode; dev/test sets with 600+ step episodes) with ground-truth action sequences. Additional evaluation uses VSI-Bench (a photorealistic visual-spatial reasoning benchmark) for Sim2Real transfer testing, and ManipulaTHOR for low-level robot arm manipulation tasks. A 226K synthetic QA pair subset is used to fine-tune Qwen2.5-VL for Sim2Real transfer.</t>
         </is>
       </c>
       <c r="F167" s="5" t="n"/>
@@ -8256,7 +8256,7 @@
       <c r="H167" s="5" t="n"/>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR (GPT-4o backend) achieves the best descriptive-question accuracy, positional error, and temporal error on long-duration videos compared to the 'LLM with Caption' and 'Multi-Frame VLM' baselines, and performs comparably to the VLM baseline on short videos while the VLM baseline fails entirely on medium/long videos due to context-window limits. Overall correctness for ReMEmbR is 0.72/0.56/0.61 (short/medium/long) versus 0.67/0.48/0.50 for a single-retrieval-call ablation and 0.54/0.50/0.38 for a coarser 12-second-caption ablation. ReMEmbR's per-question latency is roughly constant (~25 seconds for a 21.5-minute video) regardless of video length, versus ~90 seconds for the VLM baseline on a much shorter 5.5-minute video. Open-source LLM backends (Codestral, Command-R, Llama3.1-8B) substantially underperform GPT-4o, attributed to weaker arithmetic/spatiotemporal reasoning despite being tuned for function calling.</t>
+          <t>On NiEH/NsiEH with full trajectory context, LLaVA-OV fails entirely (0.0% accuracy) on inputs exceeding 1M tokens, exposing a hard context-length limitation, while Gemini 2.0 Flash performs best among architectures tested (83.04% on single-evidence Interleaved Goal-State-Action setting) but drops substantially on the harder multi-evidence NsiEH task (down to 37-62% depending on architecture) and shows a tendency to hallucinate object locations in image-only settings without language grounding. Memory-Augmented (Text) approaches outperform image-based memory retrieval (Top-10/Top-20), since textual state representations are denser per token. In online interactive evaluation (AI2THOR), LLaVA-OV fails to complete any long-horizon task (&gt;1M tokens), so only Qwen2.5-VL results are reported: training with longer context yields significant gains (32K context: 6.4% total success rate vs. 128K context: 9.2%), and applying YaRN (x4) context extension on top of the 128K model further boosts total success rate to 11.5% (+2.3% over the base 128K interleaved model); the 'Put' subtask remains essentially unsolved (0.0-2.6%) across all methods since it is the final step in a chain and agents rarely reach it due to earlier failures. Sim2Real transfer: fine-tuning Qwen2.5-VL on 226K synthetic NiEH QA pairs improves performance on VSI-Bench by +11.2% on the Object Appearance Order task and +2.1% overall, with negligible degradation on other spatial tasks. Low-level manipulation integration (OpenVLA-7B, SpatialVLA-4B on ManipulaTHOR) shows both VLA models struggling overall (e.g., Put task: 1.19-2.08% success), attributed to ManipulaTHOR's egocentric view providing near-identical images for sub-0.01 fine-grained arm movements and mismatches between ManipulaTHOR's robot arm model and the VLA models' assumed arm configurations.</t>
         </is>
       </c>
       <c r="F168" s="5" t="n"/>
@@ -8289,7 +8289,7 @@
       <c r="H168" s="5" t="n"/>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>'LLM with Caption' (GPT-4o given all video captions concatenated at once, no retrieval) and 'Multi-Frame VLM' (GPT-4o given video frames sampled at 2 FPS directly, no retrieval) — both of which are shown to fail on medium/long videos due to fixed context-window limits.</t>
+          <t>Architectural comparisons treat 'Full trajectory (Image-only)' processing as an implicit baseline against the proposed Interleaved Goal-State-Action and Memory-Augmented (Text/Image Top-10/Top-20) architectures; multiple long-context extension techniques (linear interpolation, dynamic scaling, YaRN, LongRoPE) are compared against the base (non-extended) context-length model as baseline. For Sim2Real transfer, the Qwen2.5-VL base model (without NiEH fine-tuning) serves as the baseline compared against the NiEH-fine-tuned version on VSI-Bench.</t>
         </is>
       </c>
       <c r="F169" s="5" t="n"/>
@@ -8322,7 +8322,7 @@
       <c r="H169" s="5" t="n"/>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. The paper addresses the incidental failure mode of context/memory scalability: robots' inability to reason over arbitrarily long deployment histories within the fixed context windows of transformer-based LLMs/VLMs, not any adversarial actor.</t>
+          <t>N/A - non-adversarial. The incidental failure mode of interest is long-context reasoning failure in embodied agents: vision-language models struggle to recall and reason over scattered, temporally distant multimodal clues (objects/locations observed hundreds of steps earlier) when required to act on synthetic goals spanning extended trajectories, manifesting as complete failure beyond certain context-length limits (e.g., LLaVA-OV failing entirely on &gt;1M-token inputs), hallucinated object locations when visual-only input lacks language grounding, and steep performance degradation from single-evidence to multi-evidence reasoning settings.</t>
         </is>
       </c>
       <c r="F170" s="5" t="n"/>
@@ -8355,7 +8355,7 @@
       <c r="H170" s="5" t="n"/>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations and Future Work' section. (1) NaVQA enforces a single unique correct answer per question, whereas real-world deployments often admit multiple valid answers, requiring more focus on contextual reasoning. (2) The memory-building approach relies solely on video captioning and does not incorporate other rich spatial information sources (e.g., room numbers, equipment labels, semantic maps, scene graphs, queryable scene representations) that could be added as additional memory/function-call types. (3) The vector database continuously accumulates potentially repetitive information over time without pruning, which the authors state 'would dilute useful information over time,' flagging efficient memory aggregation as future work. The qualitative robot deployment section also reports concrete failure cases (e.g., confusing a water fountain for a 'soda machine') attributed to the smaller quantized 3B captioning model used on-device.</t>
+          <t>The paper has no explicit 'Limitations' section; the closest analog is embedded in the Conclusion, which states that 'despite these advances, our results highlight that long-horizon reasoning remains an open challenge, with current state-of-the-art VLMs still struggling to reason over extreme context lengths,' and expresses hope that the framework 'encourages further research into the next generation of embodied agents.' Within the results discussion, additional implicit limitations are noted: the Put manipulation subtask remains unsolved across all tested methods (agents rarely reach this final stage due to compounding earlier failures), and low-level manipulation integration (OpenVLA-7B, SpatialVLA-4B) shows generally low success rates attributed to egocentric-view granularity limitations and robot-arm-model mismatches between ManipulaTHOR and the VLA models' training assumptions.</t>
         </is>
       </c>
       <c r="F171" s="5" t="n"/>
@@ -8388,7 +8388,7 @@
       <c r="H171" s="5" t="n"/>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>Beyond Needle(s) in the Embodied Haystack: Environment, Architecture, and Training Considerations for Long Context Reasoning</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR (Retrieval-augmented Memory for Embodied Robots) addresses long-horizon video question answering for robot navigation by decomposing the problem into a memory-building phase and a querying phase, avoiding the impracticality of feeding unbounded histories into a transformer's fixed context window. During memory building, the robot's video stream is segmented into t-second chunks, each captioned by a VLM (VILA), and the caption embedding (via mxbai-embed-large-v1) together with the corresponding position and timestamp is stored in a vector database V, built without knowledge of any future question. During querying, an LLM-agent acts as an iterative state machine (up to k=3 rounds) that issues up to three retrieval function calls per round — text retrieval, position retrieval, or time retrieval — against V, accumulating retrieved memories until it judges the question answerable, at which point it emits a structured JSON answer (text, position, time, or duration). To evaluate this approach on robot-centric long-horizon reasoning, the authors construct the NaVQA dataset from real robot navigation videos and compare ReMEmbR against non-retrieval baselines that feed the entire caption history or entire frame history directly to a VLM/LLM, showing ReMEmbR scales to much longer histories with near-constant latency. The system is further deployed in real time on a Nova Carter robot (on-device VILA-3b captioning, Nav2/AMCL localization, Whisper ASR, cloud or local LLM backend), demonstrating the ability to answer navigation-centric natural-language questions and generate metric goals after a 25-minute memory-building run in a real office environment.</t>
+          <t>This paper introduces Infini-THOR, a framework advancing long-context understanding in embodied AI along three axes: environment, architecture, and training. On the environment side, it provides a generation framework for synthesizing scalable, reproducible long-horizon embodied trajectories in AI2THOR, featuring synthetic final goals that require multi-step reasoning across objects/locations observed hundreds of steps apart (e.g., observing a tomato at t=16 and a countertop at t=560, then being asked at t=670 to place the tomato on the counter). Building on this, the paper introduces Needle(s) in the Embodied Haystack (NiEH) and its multi-evidence variant (NsiEH), QA tasks requiring agents to recall and reason over scattered clues combining visual and linguistic observations -- extending the text-only 'Needle in a Haystack' paradigm to multimodal embodied settings. On the architecture side, the paper compares two complementary VLM-as-policy designs for handling extreme sequence lengths: Interleaved Goal-State-Action modeling, which encodes the full perception-action history as a single multimodal sequence, versus Memory-Augmented Goal-State modeling, which replaces the full trajectory with text summaries or retrieved visual memories (via CLIP-based similarity) for long-term contextual grounding. On the training side, since standard VLMs cannot natively handle inputs exceeding 1M tokens, the paper evaluates long-context extension techniques (linear interpolation, dynamic scaling, YaRN, LongRoPE) and incorporates Context Parallelism via Ring Attention to enable efficient fine-tuning on ultra-long sequences. The paper releases a large-scale trajectory dataset (2,456 training trajectories averaging 405 steps, with dev/test trajectories exceeding 600 steps) supporting both offline imitation learning and online interactive policy evaluation, and further demonstrates the framework's versatility through Sim2Real transfer (fine-tuning on synthetic NiEH QA pairs improves photorealistic VSI-Bench performance) and integration with ManipulaTHOR for low-level robot arm manipulation control.</t>
         </is>
       </c>
       <c r="F172" s="5" t="n"/>
@@ -8421,7 +8421,7 @@
       <c r="H172" s="5" t="n"/>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>d16afc58d0e71d287893e1d137af37472b5fe23a</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       <c r="H173" s="5" t="n"/>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       <c r="H174" s="5" t="n"/>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -8520,7 +8520,7 @@
       <c r="H175" s="5" t="n"/>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F176" s="5" t="n"/>
@@ -8553,7 +8553,7 @@
       <c r="H176" s="5" t="n"/>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F177" s="5" t="n"/>
@@ -8586,7 +8586,7 @@
       <c r="H177" s="5" t="n"/>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -8619,7 +8619,7 @@
       <c r="H178" s="5" t="n"/>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F179" s="5" t="n"/>
@@ -8652,7 +8652,7 @@
       <c r="H179" s="5" t="n"/>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -8685,7 +8685,7 @@
       <c r="H180" s="5" t="n"/>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F181" s="5" t="n"/>
@@ -8718,7 +8718,7 @@
       <c r="H181" s="5" t="n"/>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       <c r="H182" s="5" t="n"/>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -8784,7 +8784,7 @@
       <c r="H183" s="5" t="n"/>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -8807,13 +8807,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E184" s="2" t="n"/>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>The paper states intent to release the model ('By releasing the model, we aim to advance transparent and reproducible research on reliable safeguards for LLMs') but does not provide a specific repository, download link, or model card URL anywhere in the text (including the References and Acknowledgments sections); no GitHub or Hugging Face link for AprielGuard itself was found despite thorough search, only links to third-party datasets/tools used (e.g., sentence-transformers/all-MiniLM-L6-v2, NeMo-Curator on GitHub).</t>
+        </is>
+      </c>
       <c r="F184" s="5" t="n"/>
       <c r="G184" s="5" t="n"/>
       <c r="H184" s="5" t="n"/>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8827,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -8838,7 +8842,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>None evaluated directly. Models and products appear as subjects of the documented incidents and reviewed studies - GitHub Copilot (CVE-2025-53773), ChatGPT (Windows license-key exposure) - rather than as systems tested by the authors.</t>
+          <t>AprielGuard-8B (the paper's own model, a fine-tuned downscaled variant of the base model used in Apriel-1.5-15B-Thinker), evaluated in both reasoning-enabled and reasoning-free modes, against six baseline guardrail families: Llama Guard (versions 2-8B, 3-8B, and 4-12B), Llama-Prompt-Guard-2-86M, IBM Granite Guardian (variants 3.1-2B, 3.2-3B-A800M, 3.2-5B, and 3.3-8B), ShieldGemma-9B, gpt-oss-safeguard-20B, and Qwen3Guard-8B (evaluated in both 'Strict' and 'Loose' policy modes).</t>
         </is>
       </c>
       <c r="F185" s="5" t="n"/>
@@ -8846,7 +8850,7 @@
       <c r="H185" s="5" t="n"/>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8860,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -8871,7 +8875,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>No datasets or benchmarks used. Evidence base is 45 key sources from 2023-2025, industry security reports, documented real-world exploits and CVE records, with mitigation guidance mapped to OWASP Top 10 for LLM Applications 2025 (including LLM08:2025 Vector and Embedding Weaknesses).</t>
+          <t>Training data is entirely synthetic (327,714 samples per Table 2) generated using Mixtral-8x7B and internal uncensored models via the SyGra framework and NVIDIA NeMo Curator, spanning standalone prompts, conversations, and agentic workflows, with structured &lt;reasoning&gt;/&lt;result&gt; tag annotations. Evaluation uses three benchmark suites: (1) a Safety Risks Benchmark aggregating 11 public datasets (44,699 samples total, e.g. SimpleSafetyTests, Aya Redteaming, ToxicChat, BeaverTails, SafeRLHF, XSTest/XSTest-response, OpenAI Moderation, Aegis Content Safety v1/v2, HarmBench); (2) an Adversarial Attacks Benchmark aggregating 10 public datasets (18,073 samples total, e.g. Gandalf, SALAD-Data attack-enhanced subset, in-the-wild jailbreak prompts, Wildguardmix, Wildjailbreak, deepset/prompt-injections, Qualifire prompt-injections); and (3) a proprietary in-house Agentic AI workflow benchmark (4,326 samples, Table 8) simulating multi-step agent executions with attacks targeting prompts, reasoning traces, tool parameters, memory states, and inter-agent communications, plus a separate Long Context benchmark (inputs up to 32,000 tokens).</t>
         </is>
       </c>
       <c r="F186" s="5" t="n"/>
@@ -8879,7 +8883,7 @@
       <c r="H186" s="5" t="n"/>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8893,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -8904,7 +8908,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>No original experiments; findings are synthesized from the reviewed literature and incident record. The most-cited quantitative claim is that just five carefully crafted documents can manipulate AI responses 90% of the time through RAG poisoning - the point being that corpus poisoning scales efficiently and does not require massive dataset contamination, which reframes RAG poisoning from a bulk-data problem into a targeted-insertion one. Backdoored retriever attacks are reported to achieve higher success rates than corpus poisoning but demand a more complex setup in which victims fine-tune retrievers on attacker-poisoned data; their significance is persistence, since the trigger survives knowledge-base updates. Context for exposure is given by the observation that 53% of companies rely on RAG pipelines. The review's own analytical conclusion is that many defenses fail against determined attackers, and that two limits are fundamental rather than engineering gaps: the stochastic nature problem (model behaviour is probabilistic, so no filter yields deterministic guarantees) and the alignment paradox (the instruction-following capability that makes models useful is the same capability attackers exploit). PALADIN is proposed as a layered response but is not evaluated.</t>
+          <t>On the internal Agentic AI workflow benchmark (Table 9), AprielGuard-8B substantially outperforms all baselines: 0.86 F1 (0.98 precision/0.77 recall) on Safety Risks and 0.95 F1 (1.00 precision/0.91 recall) on Adversarial Attacks without reasoning, versus the next-best baseline (IBM-Granite-Guardian-3.2-3B) at only 0.73 and 0.80 F1 respectively -- most Llama Guard and Qwen3Guard variants score below 0.40 F1 on this agentic benchmark. On the aggregate public Safety Risks and Adversarial Attacks benchmarks (Table 7), AprielGuard-8B is competitive with the best baselines (0.88 F1 safety, 0.93 F1 adversarial without reasoning) though not always the single top performer on every individual sub-benchmark (Table 4, Table 6). The paper's headline claim is that a single 8B unified model matches or exceeds specialized, larger baselines particularly in multi-step, reasoning-intensive agentic scenarios, while models like Llama Guard variants (designed for single-turn conversational safety) show especially poor adversarial-attack recall on agentic and long-context inputs.</t>
         </is>
       </c>
       <c r="F187" s="5" t="n"/>
@@ -8912,7 +8916,7 @@
       <c r="H187" s="5" t="n"/>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8926,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -8937,7 +8941,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>None implemented. Defense mechanisms drawn from the literature are assessed against a stated rubric - effectiveness (true/false positive rates), computational overhead, deployability, and robustness against adaptive attackers - and mitigation guidance is aligned to OWASP Top 10 for LLM Applications 2025. PALADIN, the proposed five-layer framework, is not compared empirically against any existing defense.</t>
+          <t>Six families of existing open-source/open-weight safeguard models representing current state of practice: Llama Guard (2-8B, 3-8B, 4-12B), Llama-Prompt-Guard-2-86M, IBM Granite Guardian (2B/3B/5B/8B variants), ShieldGemma-9B, gpt-oss-safeguard-20B, and Qwen3Guard-8B (Strict/Loose modes), each compared in 'With Reasoning' and 'Without Reasoning' configurations where supported.</t>
         </is>
       </c>
       <c r="F188" s="5" t="n"/>
@@ -8945,7 +8949,7 @@
       <c r="H188" s="5" t="n"/>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8959,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -8968,13 +8972,17 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E189" s="2" t="n"/>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>N/A - non-adversarial from the perspective of the paper's own methodology (it is a defensive/detection paper, not an attack paper), but its subject matter is explicitly adversarial: it targets detection of prompt injection, jailbreaks, multi-turn manipulation, and agentic-workflow attacks (targeting prompt inputs, reasoning traces, tool parameters, memory states, and inter-agent communications) that existing single-turn-focused moderation systems fail to catch, motivated by real-world agentic AI systems being vulnerable to indirect prompt injections and long-context manipulations that exploit reasoning/planning mechanisms.</t>
+        </is>
+      </c>
       <c r="F189" s="5" t="n"/>
       <c r="G189" s="5" t="n"/>
       <c r="H189" s="5" t="n"/>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8992,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -8999,7 +9007,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>The limitations the review identifies are properties of the field rather than of the review: the stochastic nature problem and the alignment paradox, which it argues place a ceiling on what filtering-based defenses can guarantee. As a review it carries the usual caveats and does not state them - no search protocol, database coverage, or inclusion criteria is reported for the 45 sources, so the selection cannot be reconstructed or checked for bias, and quantitative figures (the five-document 90% manipulation rate, the 53% RAG adoption statistic) are inherited from heterogeneous sources without normalization. PALADIN is proposed without implementation, evaluation, or overhead measurement, so its five layers are a design sketch rather than a validated defense. The incident case studies are valuable but selected rather than systematically sampled, so they establish that severe exploits occur without supporting any claim about prevalence.</t>
+          <t>The paper contains no section explicitly titled 'Limitations'; a thorough search of the full text (including the Conclusion) found no dedicated caveats or limitations heading. The closest analog is the 'Conclusion and Future Work' section (Section 7), which frames unaddressed gaps as future work rather than limitations: extending AprielGuard's coverage to multimodal inputs (image, speech), and enhancing robustness against novel or adaptive adversarial strategies through stronger generalization and adversarial training techniques -- implicitly acknowledging the current model is text-only and has not been hardened against adaptive/novel attacks.</t>
         </is>
       </c>
       <c r="F190" s="5" t="n"/>
@@ -9007,7 +9015,7 @@
       <c r="H190" s="5" t="n"/>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9025,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Prompt Injection Attacks in Large Language Models and AI Agent Systems: A Comprehensive Review</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -9032,7 +9040,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive review synthesizing 2023-2025 research on prompt injection across LLMs and AI agent systems, drawing on 45 key sources plus industry security reports and documented real-world exploits. Its taxonomy spans direct jailbreaking through indirect injection via external content, and it gives particular attention to how AI agent systems and the Model Context Protocol expand the attack surface, introducing tool poisoning and credential theft as classes without single-model analogues. The review's distinguishing feature relative to the other prompt-injection surveys in this corpus is its grounding in named, dated production incidents rather than only academic attack papers: it documents GitHub Copilot's CVE-2025-53773 remote code execution vulnerability (CVSS 9.6), the CamoLeak CVSS 9.6 exploit, and ChatGPT's Windows license-key exposure. It also covers RAG-specific weaknesses including corpus poisoning, backdoored retriever attacks that embed triggers during retriever fine-tuning (persisting across knowledge-base updates because the vulnerability lives in learned retriever parameters rather than stored documents), and vector-database exploitation under OWASP LLM08:2025. On the defense side it proposes PALADIN, a defense-in-depth framework of five protective layers, and evaluates defense mechanisms against stated criteria - true/false positive rates, computational overhead, deployability, and robustness against adaptive attackers - concluding with an analysis of why many defenses fail against determined adversaries. It names two fundamental limits it argues are structural: the stochastic nature problem and the alignment paradox.</t>
+          <t>AprielGuard is an 8B-parameter unified safeguard model from ServiceNow's SLAM Lab that jointly detects safety risks (toxicity, bias, harmful content) and adversarial threats (prompt injection, jailbreaks) within a single taxonomy and model, rather than treating these as separate classification tasks requiring distinct models as most prior guardrails (Llama Guard, Granite Guardian, MD-Judge, WildGuard) do. The model is fine-tuned (SFT, 3 epochs, batch size 1 with 8-step gradient accumulation, LR 2e-4, Adam) from a downscaled variant of the base model underlying Apriel-1.5-15B-Thinker, using a chat-template format with a dedicated &lt;|content|&gt; tag pair that lets a single model handle standalone prompts, multi-turn conversations, and agentic workflows (with tool calls/execution traces) uniformly. Training data (327,714 samples) is entirely synthetic, generated via Mixtral-8x7B and internal uncensored models using the SyGra framework and NVIDIA NeMo Curator, filtered for redundancy via semantic (embedding cosine similarity &gt;0.7) and syntactic (ROUGE-L F1 &gt;0.9) deduplication, and augmented with character-level noise, typos, leetspeak, and paraphrasing for robustness. Each training example additionally has an LLM-generated structured reasoning trace (&lt;reasoning&gt;...&lt;/reasoning&gt; and &lt;result&gt;...&lt;/result&gt; tags) that explains the classification rationale, letting AprielGuard operate in both a reasoning-enabled mode (higher interpretability/latency) and a reasoning-free mode (lower latency), trading off explainability against speed. The safety taxonomy adopts the 16-task SALAD-Bench framework, while adversarial attacks use a taxonomy introduced by the authors covering prompt injection and jailbreak strategy categories. Evaluation spans standard public safety/adversarial benchmarks plus a proprietary in-house agentic-workflow benchmark and a long-context (up to 32K token) benchmark, with the paper's central finding being that AprielGuard's agentic-workflow and reasoning-trace training gives it a pronounced advantage over conversation-only-trained baselines specifically in multi-step, reasoning-intensive, and long-context detection scenarios.</t>
         </is>
       </c>
       <c r="F191" s="5" t="n"/>
@@ -9040,7 +9048,7 @@
       <c r="H191" s="5" t="n"/>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>title:fc1fc8c2fc85deb5</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9058,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -9073,7 +9081,7 @@
       <c r="H192" s="5" t="n"/>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9091,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -9106,7 +9114,7 @@
       <c r="H193" s="5" t="n"/>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9124,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -9139,7 +9147,7 @@
       <c r="H194" s="5" t="n"/>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9157,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -9172,7 +9180,7 @@
       <c r="H195" s="5" t="n"/>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9190,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -9197,7 +9205,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F196" s="5" t="n"/>
@@ -9205,7 +9213,7 @@
       <c r="H196" s="5" t="n"/>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9215,7 +9223,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -9230,7 +9238,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>resource-abuse</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F197" s="5" t="n"/>
@@ -9238,7 +9246,7 @@
       <c r="H197" s="5" t="n"/>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9256,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -9271,7 +9279,7 @@
       <c r="H198" s="5" t="n"/>
       <c r="I198" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9289,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -9304,7 +9312,7 @@
       <c r="H199" s="5" t="n"/>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9322,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -9329,7 +9337,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F200" s="5" t="n"/>
@@ -9337,7 +9345,7 @@
       <c r="H200" s="5" t="n"/>
       <c r="I200" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9355,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -9370,7 +9378,7 @@
       <c r="H201" s="5" t="n"/>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9388,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -9395,7 +9403,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F202" s="5" t="n"/>
@@ -9403,7 +9411,7 @@
       <c r="H202" s="5" t="n"/>
       <c r="I202" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9413,7 +9421,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -9428,7 +9436,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>N - no code or dataset release statement found; only an OpenReview forum link for the TMLR submission</t>
+          <t>The authors release their code at https://github.com/albert-y1n/PISmith, and the Ethics Statement commits to releasing it with clear documentation of its intended use as a research evaluation tool.</t>
         </is>
       </c>
       <c r="F203" s="5" t="n"/>
@@ -9436,7 +9444,7 @@
       <c r="H203" s="5" t="n"/>
       <c r="I203" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9454,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -9461,7 +9469,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Open-source: Qwen3-4B-Instruct-2507, Qwen3-8B-Instruct, LLaMA-3.2-3B-Instruct, LLaMA-3.1-8B-Instruct, Gemma-3-4B-It, Gemma-2-9B-It. Closed-source: GPT-5, Gemini-2.5-Flash, Claude-Sonnet. Nine models total.</t>
+          <t>The attack LLM (attacker policy) is Qwen3-4B-Instruct-2507, trained exclusively on 100 samples from Dolly Closed QA. Target/defended LLMs evaluated include Meta-SecAlign-8B (the primary target for the main 13-benchmark evaluation), Qwen3-4B-Instruct-2507 as the target for the utility-robustness trade-off study across seven defenses, and in agentic settings, Meta-SecAlign-8B plus three closed-source models: GPT-4o-mini (trained with instruction hierarchy), GPT-4.1-nano, and GPT-5-nano (equipped with prompt-injection defenses). GPT-4o-mini also serves as the LLM-as-judge for determining attack success.</t>
         </is>
       </c>
       <c r="F204" s="5" t="n"/>
@@ -9469,7 +9477,7 @@
       <c r="H204" s="5" t="n"/>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9487,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -9494,7 +9502,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Introduces BenchOverflow, a dataset of plain-text prompts spanning nine overflow-inducing strategies (including Implicit large enumeration, Explicit forced length, Change forms, Tokenizer stress, Infinite generation), built via a human-written meta-prompt template refined with GPT-4o and manual correction. Benign control is the OpenAssistant Conversations corpus (OASST2), adding 400 generations for a total of 4,000 generations under a fixed 5,000-new-token budget.</t>
+          <t>13 benchmarks from PIArena spanning three task categories: Question Answering (SQuAD v2, Dolly Closed QA, Dolly Info Extraction, Dolly Summarization), Retrieval-Augmented Generation (NQ, HotpotQA, MS-MARCO), and Long-Context tasks from LongBench (HotpotQA-Long, Qasper, GovReport, MultiNews, Passage Retrieval, LCC). Agentic-setting evaluation uses InjecAgent and AgentDojo (workspace, banking, travel, and Slack domains).</t>
         </is>
       </c>
       <c r="F205" s="5" t="n"/>
@@ -9502,7 +9510,7 @@
       <c r="H205" s="5" t="n"/>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9520,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -9527,7 +9535,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>All nine plain-text strategies shift output-length distributions sharply rightward relative to the OASST2 benign baseline, producing heavy tails and frequent saturation of the 5,000-token cap; Explicit forced length and Tokenizer stress dominate CSR@5k. Overflow is reproducible within prompts but heterogeneous across families, with LLaMA variants correlating 69-71% within family while GPT-5 and Claude-Sonnet show the broadest cross-strategy associations. A generic conciseness reminder cuts mean output length by roughly 30% (GPT-5) up to 85-90% (Gemini-2.5-Flash, Qwen3-8B, Gemma-3-4B-It) and lowers CSR for most strategies, but Tokenizer stress remains comparatively resistant, so it is not sufficient alone.</t>
+          <t>Against Meta-SecAlign-8B across 13 benchmarks (Table 1), PISmith achieves an average ASR@10 of 1.0 and ASR@1 of 0.87, substantially exceeding the strongest baseline RL-Hammer (0.70/0.48) and far exceeding search-based methods TAP/PAIR/Strategy (average ASR@1 of 0.11/0.16/0.21) and static attacks (0.04-0.07), despite being trained only on 100 Dolly Closed QA samples and generalizing to 12 unseen benchmarks; the improvement is most pronounced on harder benchmarks like HotpotQA-Long (0.99/0.61 for PISmith vs. 0.04/0.01 for RL-Hammer), where restrictive output-format instructions make injection harder. A utility-robustness trade-off analysis across seven additional defenses (Sandwich, Instructional, PromptArmor, DataFilter, PIGuard, PromptGuard, DataSentinel) finds no defense sits in the desirable high-utility/low-ASR region: defenses either preserve utility but are easily broken by PISmith, or achieve lower ASR only by indiscriminately blocking both malicious and benign content, degrading utility substantially. In agentic settings, PISmith achieves ASR of at least 0.95 on InjecAgent across all target LLMs including GPT-5-nano (where static attacks completely fail), and on the more complex end-to-end AgentDojo benchmark (requiring correct tool selection and valid arguments, verified against actual environment state changes), PISmith consistently and significantly outperforms all static baselines across closed-source LLMs. A cost analysis (Appendix D.4) shows PISmith achieves the highest attack success rate while requiring fewer total target-LLM queries (32,000 total) than search-based baselines like TAP and Strategy (6.1x more queries for Strategy).</t>
         </is>
       </c>
       <c r="F206" s="5" t="n"/>
@@ -9535,7 +9543,7 @@
       <c r="H206" s="5" t="n"/>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9545,7 +9553,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -9560,7 +9568,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>The benign OASST2 conversation corpus serves as the non-overflow control for length distributions and cap-saturation rates, and each model is measured with and without the conciseness-reminder intervention. Prior resource-exhaustion attacks (Engorgio, AutoDoS/CRABS, OverThink, BitHydra, Hidden Tail) are discussed in related work but not re-run.</t>
+          <t>Static attacks (Direct/naive attack, Combined attack using multiple hand-crafted templates), search-based attacks (TAP, PAIR, Strategy), and RL-based attacks (Vanilla GRPO, RL-Hammer), all sharing the same base LLM, training data, and evaluation protocol as PISmith for fair comparison; search-based methods instead use a per-instance optimization budget. On the defense side, PISmith is evaluated against Meta-SecAlign-8B and seven additional prevention-based defenses (Sandwich, Instructional, PromptArmor, DataFilter) and filter-based defenses (PIGuard, PromptGuard, DataSentinel), plus a No-Defense baseline, and against six AgentDojo template-based attack strategies in the agentic setting.</t>
         </is>
       </c>
       <c r="F207" s="5" t="n"/>
@@ -9568,7 +9576,7 @@
       <c r="H207" s="5" t="n"/>
       <c r="I207" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9586,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -9593,7 +9601,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Deliberately weak: any ordinary user issuing natural-language requests, with no adversarial suffixes, jailbreaks, special tokens, model-specific artifacts, corpus control or model access. The paper frames Overflow as arising from helpfulness priors and absent length control, so it can be triggered inadvertently (student misuse, curiosity stress tests) or exploited at scale for compute amplification, cost inflation (denial-of-wallet) and cross-tenant service degradation.</t>
+          <t>PISmith operates under an explicit black-box threat model (Section 3.1). The attacker has only query access to the target defended LLM M_theta and observes its outputs (no access to model weights, gradients, or internal defense mechanisms). Given a target task (an instruction paired with an untrusted data context, e.g., a webpage) and an injected task specifying the attacker's objective (e.g., embedding a phishing link, causing content promotion, access denial, or infrastructure failure in the response), the attacker trains an attack LLM (policy) via reinforcement learning to generate an injected prompt that, when embedded into the data context, causes the target LLM's response to fulfill the injected task, formalized as maximizing expected binary attack-success reward over a training distribution of (instruction, context, injected task) triples. This models the realistic deployment threat where an attacker cannot inspect or modify the defended system directly but can iteratively query it and observe outputs, motivating the RL-based adaptive-attack framing as opposed to white-box or purely static attack assumptions.</t>
         </is>
       </c>
       <c r="F208" s="5" t="n"/>
@@ -9601,7 +9609,7 @@
       <c r="H208" s="5" t="n"/>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9619,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -9626,7 +9634,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>The authors note the study isolates plain-text prompt effects under fixed decoding and budget settings and does not cover tool-augmented agents, retrieval pipelines or training-time defenses; that proprietary results are point-in-time defaults that may change; that downstream task utility and user satisfaction under the mitigation are not measured; and that all models were run at their default temperature (1), which itself substantially affects sequence-length variance.</t>
+          <t>The paper has no section explicitly titled 'Limitations,' but the Conclusion explicitly points to a 'Future Work: Stronger Attackers and Defensive Applications' discussion in Appendix A.1, which functions as the paper's limitations-and-future-work analog. It notes that PISmith uses only a relatively small attack LLM (Qwen3-4B-Instruct-2507) throughout the paper, and that attack performance is expected to further improve with more capable general-purpose attacker models (e.g., DeepSeek V4 Pro, GLM-5.2) with stronger instruction-following and reasoning ability -- this scaling trend is explicitly left to future work rather than studied in the paper. It also notes that PISmith, as currently developed, is purely an evaluation/red-teaming tool rather than a defense-training method, though the authors suggest (citing concurrent industry work on OpenAI's GPT-Red self-play red-teaming) that a natural extension would be to close the loop by co-training the attacker alongside a target model's own safety post-training rather than evaluating a fixed target defense after the fact -- framed as a promising but unrealized direction rather than a limitation the current paper addresses. Additionally, the Ethics Statement acknowledges the dual-use risk inherent in releasing an effective red-teaming/attack-generation tool, mitigated by responsible-disclosure practices (targeting only existing, publicly available defenses; using only synthetic/public data with no real-world systems or private data involved; releasing code with documentation of its intended research use).</t>
         </is>
       </c>
       <c r="F209" s="5" t="n"/>
@@ -9634,7 +9642,7 @@
       <c r="H209" s="5" t="n"/>
       <c r="I209" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9652,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -9659,7 +9667,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Introduces Overflow, a non-adversarial failure mode in which ordinary plain-text prompts elicit excessive generation, and BenchOverflow, a model-agnostic benchmark of nine prompting strategies that amplify output volume without adversarial suffixes or policy circumvention. Evaluates nine open- and closed-source models under a standardized protocol with a fixed 5,000-new-token budget, quantifying tail risk with cap-saturation rates (CSR@1k/3k/5k) and empirical CDFs, and analysing within-prompt variance and cross-model correlation. Positions Overflow against optimized resource-exhaustion attacks (Engorgio, AutoDoS, OverThink, BitHydra) by requiring no optimization or data control. Assesses a lightweight model-agnostic conciseness reminder as a first-line mitigation and shows it attenuates right tails unevenly across models and strategies.</t>
+          <t>PISmith is a reinforcement-learning-based red-teaming framework that trains an attack LLM (policy) via on-policy RL to generate injected prompts capable of defeating state-of-the-art prompt injection defenses, operating in a realistic black-box setting where the attacker can only query the defended target LLM and observe its outputs. The paper's central technical contribution addresses a specific failure mode observed when applying standard GRPO to this setting: because strong defenses cause the vast majority of the attack policy's early rollouts to fail, rewards become extremely sparse, producing two compounding problems -- the policy's entropy collapses prematurely (converging to near-identical, ineffective injected prompts and terminating exploration before discovering successful strategies), and even when some exploration is sustained, the rare successful rollouts are diluted by the majority of failures within the GRPO gradient estimate, preventing the policy from efficiently learning from scarce positive signal. PISmith addresses both problems with two complementary mechanisms: adaptive entropy regularization, which dynamically adjusts the strength of an entropy bonus based on the current training reward level (increasing exploration pressure when rewards are low and success is rare, relaxing it as the policy improves) to sustain exploration throughout training rather than allowing early entropy collapse; and dynamic advantage weighting, which amplifies the gradient contribution of successful rollouts in proportion to their rarity within a training batch, ensuring that scarce successes are not washed out by the majority of failed attempts in the group-relative advantage computation. Together these modifications let PISmith continue discovering and refining effective attack strategies against defenses where standard GRPO's training reward stagnates near zero, as demonstrated by its consistently higher attack success rates across static, search-based, and prior RL-based (RL-Hammer) red-teaming baselines in both non-agentic (question-answering/RAG/long-context) and full end-to-end agentic (InjecAgent, AgentDojo) evaluation settings.</t>
         </is>
       </c>
       <c r="F210" s="5" t="n"/>
@@ -9667,7 +9675,7 @@
       <c r="H210" s="5" t="n"/>
       <c r="I210" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9685,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -9700,7 +9708,7 @@
       <c r="H211" s="5" t="n"/>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9718,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -9733,7 +9741,7 @@
       <c r="H212" s="5" t="n"/>
       <c r="I212" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9751,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -9766,7 +9774,7 @@
       <c r="H213" s="5" t="n"/>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9784,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -9791,7 +9799,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F214" s="5" t="n"/>
@@ -9799,7 +9807,7 @@
       <c r="H214" s="5" t="n"/>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9817,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -9824,7 +9832,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F215" s="5" t="n"/>
@@ -9832,7 +9840,7 @@
       <c r="H215" s="5" t="n"/>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9850,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -9857,7 +9865,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F216" s="5" t="n"/>
@@ -9865,7 +9873,7 @@
       <c r="H216" s="5" t="n"/>
       <c r="I216" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9883,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -9890,7 +9898,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F217" s="5" t="n"/>
@@ -9898,7 +9906,7 @@
       <c r="H217" s="5" t="n"/>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9916,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -9923,7 +9931,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F218" s="5" t="n"/>
@@ -9931,7 +9939,7 @@
       <c r="H218" s="5" t="n"/>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -9941,7 +9949,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9956,7 +9964,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F219" s="5" t="n"/>
@@ -9964,7 +9972,7 @@
       <c r="H219" s="5" t="n"/>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9982,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9997,7 +10005,7 @@
       <c r="H220" s="5" t="n"/>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10015,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -10030,7 +10038,7 @@
       <c r="H221" s="5" t="n"/>
       <c r="I221" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -10040,7 +10048,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -10055,7 +10063,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>No code, model, or dataset release is mentioned anywhere in the paper -- no GitHub/HuggingFace links or reproducibility statement were found; several referenced third-party tools (Guidance, LangChain, LlamaIndex, Microsoft POML) are cited via their existing GitHub repositories, but LLMON itself and the paper's Distractor benchmark are not stated as released.</t>
+          <t>The paper states 'To faciliate future research, we have released the corresponding artifact: xxx' in the Introduction — this appears to be an unfilled placeholder in the arXiv preprint (the actual URL was not substituted in), so a release is stated in intent but the concrete link is not present in this version of the text.</t>
         </is>
       </c>
       <c r="F222" s="5" t="n"/>
@@ -10063,7 +10071,7 @@
       <c r="H222" s="5" t="n"/>
       <c r="I222" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10081,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -10088,7 +10096,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Granite-4.0-Micro-Base (3B parameters) and Qwen2.5-3B are the two base models used for the training-time (post-training) experiments, compared across full fine-tuning and LoRA adaptation, each with both conventional chat-template post-training and LLMON-structured post-training at multiple token-budget scales (241M-2.9B tokens). For the inference-time (constraint-masking) experiments, three models are used: Qwen2.5-3B-Instruct, Granite-3.3-8B-Instruct, and a third unnamed/partially-visible model.</t>
+          <t>GPT-5.1 is used as the target/backbone LLM embedded inside all 20 evaluated agent runtimes (chosen as a flagship agentic model), while GPT-4o separately drives ChainFuzzer's own internal LLM-based modules (chain extraction judging, Trace-guided Prompt Solving, and payload mutation) — the authors explicitly note GPT-4o was chosen to provide a conservative lower bound on ChainFuzzer's performance, expecting stronger/newer models to detect more vulnerabilities.</t>
         </is>
       </c>
       <c r="F223" s="5" t="n"/>
@@ -10096,7 +10104,7 @@
       <c r="H223" s="5" t="n"/>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10114,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -10121,7 +10129,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Standard single-instruction benchmarks without distractors (MMLU, GSM8K, IFEval) used to check general-capability retention, plus a novel 'Distractor' benchmark constructed by the authors specifically to test structured multi-instruction execution control and identifier-based binding accuracy (i.e., whether the model executes only the intended bound instruction rather than positionally salient or distractor instructions).</t>
+          <t>The evaluation dataset is a manually curated set of 20 popular open-source, multi-tool LLM agent applications (e.g., openclaw, autogpt, langflow, langchain, ragflow, metagpt, llama_index, chatchat, vanna, dbgpt, superagi, agentscope, agentzero, bisheng, xagent, taskweaver, taskingai, langroid, griptape, lagent), selected via GitHub star ranking (&gt;=2,000 stars) and multi-tool workflow support, collectively exposing 998 tools. There is no external benchmark reused; the paper constructs its own evaluation corpus of candidate tool chains, sink APIs (Table 1, categorized by injection type: CMDi, CODEi, SSRF, SSTI, SQLi), and a manually validated sample of 200 tool-chain graphs (10 per app) for precision measurement.</t>
         </is>
       </c>
       <c r="F224" s="5" t="n"/>
@@ -10129,7 +10137,7 @@
       <c r="H224" s="5" t="n"/>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -10139,7 +10147,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -10154,7 +10162,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>On the training-time experiments (Table 4), base models and conventionally post-trained chat-template baselines show near-zero Distractor-benchmark accuracy (0.00-27.80%, with most near 0-4%), indicating weak identifier-based instruction binding and frequent execution of distractor/positionally-salient instructions. After LLMON-structured full fine-tuning, Distractor accuracy rises dramatically to 83-88% across token scales for both Granite-4.0-Micro-Base and Qwen-2.5-3B, an average improvement of 86.2 percentage points, while general-capability benchmarks (MMLU, GSM8K, IFEval) remain competitive rather than catastrophically degrading. LoRA-based LLMON-structured adaptation also improves Distractor accuracy substantially (to roughly 70-76%, an average 62.2-point improvement over LoRA baselines near 2-19%), though LoRA consistently underperforms full fine-tuning on the Distractor benchmark, especially at larger token scales, suggesting deeper weight updates better internalize execution semantics. On the inference-time constraint-masking experiments (Table 5), applying LLMON-based constraint masking at inference (without any additional training) improves Distractor accuracy from 43.20% to 69.00% for Qwen2.5-3B-Instruct and from 41.60% to 72.00% for Granite-3.3-8B-Instruct, demonstrating the markup language's structure can be exploited purely at inference time as well as through training.</t>
+          <t>Across the 20 agent apps (998 tools total), ChainFuzzer extracts 2,388 candidate tool chains, synthesizes 2,213 stable prompts, and confirms 365 unique, reproducible vulnerabilities across 19 of 20 apps, of which 302 (82.74%) require multi-tool execution versus only 63 single-tool vulnerabilities -- a 4.79x higher rate for multi-tool over single-tool bugs. Vulnerabilities split 61.64% user-source injection (225) versus 38.36% environment-source injection (140, e.g., tool-returned web content), with SSRF disproportionately environment-sourced (53 vs 44) and CMDi/CODEi disproportionately user-sourced. Component-level results: tool-chain extraction achieves 96.49% edge precision and 91.50% strict chain precision on a manually validated 200-chain sample; Trace-guided Prompt Solving (TPS) raises reachability from 27.05% to 95.45% (+68.4 points) and stable-prompt rate from 9.50% to 92.50% (+83.0 points); guardrail-aware mutation raises the overall payload-level trigger rate from 18.20% to 88.60% (+70.4 points), with the largest gains on guardrail-sensitive sinks CMDi (10.00% to 86.00%) and CODEi (7.00% to 82.00%). An ablation shows removing ChainExtraction drops vulnerabilities from 365 to 63 (-302) and sink-type coverage from 5 to 3; removing TPS drops to 96 (-269); removing Mutation drops to 132 (-233) while retaining all 5 sink types -- confirming all three modules are necessary and complementary. Overall the framework achieves an efficiency of 3.02 vulnerabilities per 1M tokens, at a total cost of 68.00 hours, 236,000 tool calls, and 120.80M tokens across all 20 apps (average time-to-first-vulnerability of 0.32 hours per app).</t>
         </is>
       </c>
       <c r="F225" s="5" t="n"/>
@@ -10162,7 +10170,7 @@
       <c r="H225" s="5" t="n"/>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10180,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -10187,7 +10195,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Base models with no post-training; conventional post-training baselines using standard chat-template instruction-tuning data (both full fine-tuning and LoRA variants); and an inference-time baseline without constraint masking -- all compared against the corresponding LLMON-structured variant (LLMON-structured full fine-tuning, LLMON-structured LoRA, and LLMON-based constraint masking at inference) to isolate the specific contribution of LLMON's structural/semantic markup versus additional post-training alone.</t>
+          <t>The paper does not compare against a prior automated multi-tool vulnerability discovery tool as an external baseline (it states existing techniques focus only on single-tool/single-hop testing and are therefore not directly comparable at the workflow level). Instead, comparison is internal/ablative: full ChainFuzzer is compared against three degraded variants (w/o ChainExtraction, w/o TPS, w/o Mutation) to isolate each module's contribution, and against an 'initial payload' (one-shot, non-mutated) condition to quantify the benefit of guardrail-aware mutation.</t>
         </is>
       </c>
       <c r="F226" s="5" t="n"/>
@@ -10195,7 +10203,7 @@
       <c r="H226" s="5" t="n"/>
       <c r="I226" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10213,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -10220,7 +10228,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Explicit and central to the paper's motivation, though framed architecturally rather than via a formal adversary-capability model: the paper identifies that standard LLM prompt interfaces provide 'no meaningful separation of instructions and data,' since in principle any instruction from any source (user input or agent-retrieved content) can be followed by the model, enabling prompt injection attacks; widely-used chat templates (system/user/assistant role serialization) do not by themselves impose execution semantics or reliably enforce instruction-vs-data separation. The paper explicitly discusses defending against prompt injection attacks (Figure 4/14 walk through concrete injection-defense examples in both LLMON and Machine LLMON) by providing explicit span identifiers, unique references, and 'exec'-based binding so only designated spans are treated as executable instructions. The paper also explicitly notes that JSON, as an alternative structuring format, is 'prone to methods of indirect prompt injection' because its delimiters are not reserved special tokens and get tokenized on sub-word boundaries, leaving no tokenizer/runtime hook to reliably isolate untrusted spans -- motivating LLMON's use of dedicated special tokens instead.</t>
+          <t>ChainFuzzer defines a greybox threat model targeting multi-tool LLM agent deployments where an attacker can (1) directly steer a remote/cloud-hosted agent through natural-language user interactions (user-source injection) or (2) inject malicious content indirectly via untrusted external sources or shared carriers that the agent later consumes, such as web pages, downloaded files, database records, or caches (environment-source injection). The attacker's goal is to cause attacker-influenced content to propagate across tool boundaries -- through direct output-to-input dependencies or indirect dependencies via persisted carriers -- and reach a high-impact sink operation (categorized as command injection, code injection, SSRF, SSTI, or SQL injection). The scope explicitly excludes attackers who can modify agent code or tool implementations, or who have access to model weights, developer secrets, or system privileges beyond what the agent's tools are already granted; the framework assumes access only to the tool set, tool schemas/descriptions, and optionally tool source code (greybox access).</t>
         </is>
       </c>
       <c r="F227" s="5" t="n"/>
@@ -10228,7 +10236,7 @@
       <c r="H227" s="5" t="n"/>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10246,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -10253,7 +10261,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>No section titled 'Limitations' was found anywhere in the paper; the Conclusion (Section 9) summarizes contributions and reports the headline improvements (74.2 and 29.3 average percentage-point gains for the two use cases) without a dedicated limitations discussion, instead moving directly to 'future directions' including additional evaluations and further ISA-instruction types (comparisons, branches, indirect references) to explore in the LLMON context. The results themselves surface some implicit limitations: LoRA-adapted models consistently underperform full fine-tuning on the Distractor benchmark, and full fine-tuning with LLMON-structured data shows somewhat reduced or fluctuating scores on some general-capability benchmarks (e.g., lower MMLU/GSM8K for Granite-4.0 in some configurations) relative to the base model, an implicit accuracy/capability tradeoff not explicitly flagged as a limitation by the authors. The paper is also explicitly described as presenting 'preliminary empirical evidence' rather than a comprehensive evaluation.</t>
+          <t>The paper has an explicit 'Limitations' subsection under Section 6 (Discussion) identifying two limitations. (1) Vulnerability reproducibility depends on the runtime environment (network egress policy, sandbox permissions, credential availability), which can change whether a chain is executable or a sink effect observable -- for example, an SSRF chain may not trigger if outbound requests are blocked or a target endpoint requires unavailable token authentication. (2) ChainFuzzer relies on an LLM (GPT-4o) in multiple internal modules (chain extraction, TPS, and mutation), so model hallucination or limited reasoning capability can prevent any module from reaching 100% accuracy; the authors note they deliberately used GPT-4o rather than a newer, stronger model to provide a conservative lower bound on ChainFuzzer's performance, expecting that stronger models with better planning stability and lower hallucination rates would let the framework detect even more vulnerabilities.</t>
         </is>
       </c>
       <c r="F228" s="5" t="n"/>
@@ -10261,7 +10269,7 @@
       <c r="H228" s="5" t="n"/>
       <c r="I228" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10279,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -10286,7 +10294,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>This paper introduces LLMON (LLM Object Notation), an LLM-native markup language designed to address a structural shortcoming of the standard LLM prompt interface: a prompt is just an unstructured string, so instructions and data, examples, and constraints from different sources (system prompt, user input, retrieved agent content) are not distinguished when passed to the model, which the authors argue causes both model confusion and security risks such as prompt injection attacks, since in principle any instruction anywhere in the prompt can be followed. Drawing an analogy to how programming-language type systems support static checking, code generation, dynamic checking, and IDE tooling, LLMON aims to let a prompt's structure and semantic metadata (which parts are instructions vs. data, which spans are uniquely referenceable, which instructions should actually be executed) be communicated natively to the model rather than left implicit in natural language. The paper contrasts LLMON with JSON, arguing JSON is insufficient as an LLM-native interface because its delimiters are not reserved special tokens (so they get fragmented across sub-word tokenization boundaries), providing no reliable tokenizer/runtime hook to isolate untrusted spans, whereas LLMON is designed with dedicated special tokens and explicit span identifiers that support structure-aware decoding and enforcement compatible with self-attention, KV-cache optimization, and parameter-efficient adaptation methods like LoRA. LLMON is expressed in two forms: a human-readable 'surface language' and a more verbose 'Machine LLMON' form intended to overcome current LLM limitations in reliably parsing/respecting structure. The paper demonstrates LLMON's value for two use cases through preliminary experiments: (1) model training, where fine-tuning (full or LoRA) on LLMON-structured data teaches models explicit 'exec'-based binding, letting them correctly execute only the intended instruction and ignore distractor instructions, evaluated on a novel Distractor benchmark; and (2) inference-time implementation, where applying LLMON-based constraint masking at inference time (without additional training) similarly improves multi-instruction execution accuracy, showing the approach provides benefits at both the training and deployment stages of the LLM application lifecycle.</t>
+          <t>ChainFuzzer is a greybox automated testing framework for discovering and reproducing workflow-level multi-tool vulnerabilities in LLM agents -- security failures that emerge only through the composition of multiple tool calls (e.g., web_search leads to download leads to write_file leads to execute), rather than from any single tool call in isolation. The framework addresses three practical challenges through three corresponding modules. First, tool-chain extraction (Module A/ChainExtraction) identifies high-impact sink_tools using a catalog of candidate sink APIs (categorized by vulnerability class: command injection, code injection, SSRF, SSTI, SQL injection) with strict source-to-sink dataflow evidence, then extracts plausible upstream candidate tool chains by analyzing cross-tool data dependencies (direct output-to-input dependencies, or indirect dependencies via shared carriers like files, database records, or caches), using an LLM judge to verify each candidate chain forms a coherent, realistic workflow. Second, Trace-guided Prompt Solving (TPS, Module B) addresses the non-determinism of LLM-driven agents by synthesizing a stable natural-language prompt for each target chain: it compares runtime execution traces against the intended target chain and iteratively repairs the prompt until the agent reliably executes that specific tool sequence, converting a merely-possible chain into a consistently reproducible one. Third, guardrail-aware fuzzing (Module C/Mutation) performs feedback-driven payload mutation and validation once a chain is reliably executable: it generates sink-type-specific attack payloads, injects them via either user-driven (natural-language) or environment-driven (untrusted external content) channels at the dependency-annotated injection point on the tool-chain path, and mutates payloads when guardrails block or sanitize an initial attempt, validating exploitation with sink-specific oracles to produce minimal, auditable proof-of-concept evidence (prompt, tool-call trace, and effect evidence) that developers can use to pinpoint the correct security boundary for mitigation.</t>
         </is>
       </c>
       <c r="F229" s="5" t="n"/>
@@ -10294,7 +10302,7 @@
       <c r="H229" s="5" t="n"/>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10312,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -10327,7 +10335,7 @@
       <c r="H230" s="5" t="n"/>
       <c r="I230" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10337,7 +10345,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -10352,7 +10360,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F231" s="5" t="n"/>
@@ -10360,7 +10368,7 @@
       <c r="H231" s="5" t="n"/>
       <c r="I231" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10378,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -10393,7 +10401,7 @@
       <c r="H232" s="5" t="n"/>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10411,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -10418,7 +10426,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F233" s="5" t="n"/>
@@ -10426,7 +10434,7 @@
       <c r="H233" s="5" t="n"/>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10444,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -10451,7 +10459,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F234" s="5" t="n"/>
@@ -10459,7 +10467,7 @@
       <c r="H234" s="5" t="n"/>
       <c r="I234" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10477,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -10484,7 +10492,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>silent-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F235" s="5" t="n"/>
@@ -10492,7 +10500,7 @@
       <c r="H235" s="5" t="n"/>
       <c r="I235" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10510,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -10525,7 +10533,7 @@
       <c r="H236" s="5" t="n"/>
       <c r="I236" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10535,7 +10543,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -10550,7 +10558,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F237" s="5" t="n"/>
@@ -10558,7 +10566,7 @@
       <c r="H237" s="5" t="n"/>
       <c r="I237" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10576,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -10591,7 +10599,7 @@
       <c r="H238" s="5" t="n"/>
       <c r="I238" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10609,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -10624,7 +10632,7 @@
       <c r="H239" s="5" t="n"/>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10642,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -10657,7 +10665,7 @@
       <c r="H240" s="5" t="n"/>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10667,7 +10675,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -10682,7 +10690,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>The authors commit to releasing the Epi-Scale benchmark split (2,250 clean-context + 2,250 adversarial-context records, balanced across HotpotQA, Natural Questions, and FEVER), prompt templates, evaluation settings, and scoring specifications upon publication. The internal experimental codebase is explicitly NOT released, due to API-provider terms and because it contains non-generalized infrastructure and API-specific wrappers.</t>
+          <t>Mantis is open-sourced at https://github.com/pasquini-dario/project_mantis, including the decoy services, prompt-injection payload manager, and tarpit implementation.</t>
         </is>
       </c>
       <c r="F241" s="5" t="n"/>
@@ -10690,7 +10698,7 @@
       <c r="H241" s="5" t="n"/>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10708,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -10715,7 +10723,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>Primary evaluation model: Gemini-2.5-Flash (used for the main Epi-Scale results, ablations, and as the CDD-alpha contradiction gate). Cross-model replication: the Claude family (Claude Haiku, Claude Sonnet, Claude Opus) evaluated on adversarial records generated by a different model than the primary evaluator, partly addressing same-model perturbation bias.</t>
+          <t>Backend LLMs powering the attacking LLM-agents: OpenAI's ChatGPT-4o (primary) and Anthropic's Claude 3.5-Sonnet (primary), with additional results for ChatGPT-4 and Claude 3.5-Haiku reported in the appendix. Three existing autonomous pentesting agent frameworks are used as attackers: PentestGPTAuto, AutoPenAgent, and HackingBuddyGPT.</t>
         </is>
       </c>
       <c r="F242" s="5" t="n"/>
@@ -10723,7 +10731,7 @@
       <c r="H242" s="5" t="n"/>
       <c r="I242" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10733,7 +10741,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -10748,7 +10756,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Epi-Scale, a new benchmark introduced by the paper: 2,250 base examples drawn from HotpotQA (multi-hop), Natural Questions (single-hop), and FEVER (fact verification), each instantiated as both a clean-context and an LLM-generated adversarial-context record (4 mutually exclusive perturbation types: Entity Swap, Temporal Shift, Logical Contradiction, Distractor Evidence), yielding 4,500 total evaluation records. Also used: a 500-instance TruthfulQA misconception-injection probe (retrieved context set to the most common human misconception for each question) as a worst-case adversarial upper-bound compliance stress test.</t>
+          <t>No conventional ML benchmark; evaluation uses three real, vulnerable HackTheBox CTF machines (CTF:Dancing, CTF:Redeemer, CTF:Synced) as target systems. Each attacker/decoy/sabotage-objective configuration is repeated 10 times (non-deterministic attacker and defender behavior) with a maximum of 30 rounds per attack. Metrics: attacker win rate (obj_A, successful flag capture), defender win rate (obj_D, successful sabotage objective), and average number of rounds (#Rounds) to win or lose.</t>
         </is>
       </c>
       <c r="F243" s="5" t="n"/>
@@ -10756,7 +10764,7 @@
       <c r="H243" s="5" t="n"/>
       <c r="I243" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10774,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -10781,7 +10789,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>Under worst-case TruthfulQA misconception injection, Standard RAG accuracy collapses to only 15.0% (+/-3.1%, N=500), while CDD reaches 62.0% (+/-4.3%), demonstrating that misleading retrieved context alone can severely degrade RAG accuracy and that explicit conflict decomposition substantially recovers performance in this worst-case setting. On the main Epi-Scale adversarial benchmark (Gemini-2.5-Flash, Table 1), CDD achieves the highest macro-average adversarial accuracy (78.1%) among all compared methods, exceeding Conflict-aware RAG (73.5%, the closest baseline), Reflection Prompting (67.0%), Prompt-Filtered RAG (66.3%), Vanilla CoT (63.7%), Standard RAG (63.0%), and Closed-Book zero-shot (44.7%); CDD's advantage over the conflict-aware instruction baseline is concentrated on the two localized factual-conflict perturbation types where explicit premise isolation directly applies -- Entity Swap (88.0% vs. 79.3%, non-overlapping confidence intervals) and Logical Contradiction (83.2% vs. 75.4%, non-overlapping CIs) -- while the margin closes (overlapping CIs) on Temporal Shift and Distractor Evidence, indicating the benefit of explicit decomposition is conflict-type-specific rather than universal. Cross-model replication on the Claude family shows CDD improves adversarial accuracy on all three models (Haiku +2.2pp, Sonnet +4.6pp, Opus +2.6pp as directional point estimates without paired significance testing), but trace-perturbation (mistake-injection) sensitivity -- which is large on Gemini-2.5-Flash (64.1%) -- shows no measurable coupling on the Claude family (sensitivities within [-3%, +7%]), demonstrating that accuracy improvement and causal trace-sensitivity can dissociate across model families: a method can improve final-answer accuracy without demonstrable evidence that its intermediate reasoning trace causally drives that answer. Component ablations (Table 3) show removing explicit Premise Isolation (Step 4) drops adversarial macro accuracy to 65.1% and removing the Divergence Check (Step 3) drops it to 66.0% (both near Vanilla CoT levels), confirming these two steps are the primary drivers of CDD's gains; a length-matched 'sham' 5-step prompt with semantically vacuous steps achieves only 40.1%, well below full CDD (78.1%), ruling out that CDD's gains derive merely from increased generation length or generic multi-step structure. A separate mixed clean/adversarial calibration run reveals CDD trades roughly 18 points of clean-sample accuracy (67.2% CDD vs. 84.9% Standard RAG on clean data) for its adversarial robustness gain (78.1% vs. 63.0%), with the two methods statistically tied on overall harmonic-mean accuracy (72.23% vs. 72.33%, bootstrap p=0.53) -- illustrating that CDD is a conflict-specific intervention with a real accuracy trade-off, not a universally better prompt.</t>
+          <t>Without any defense, the tested LLM-agents reliably compromise the HackTheBox machines (e.g., PentestGPTAuto achieves 9-10/10 wins across all three CTFs in 4.3-11.5 average rounds), confirming these are realistic, exploitable targets. With Mantis deployed, across all tested attacker/decoy/sabotage-objective configurations, Mantis achieves approximately 95.4% success rate in achieving its sabotage objective (obj_D) while reducing the attacker's success rate to less than 3% -- e.g., PentestGPTAuto's win rate against Mantis-protected FTP decoys drops to 0/10 across all three CTFs under both GPT-4o and Claude 3.5-Sonnet backends, with the defender winning 9-10/10 times. The agent-counterstrike sabotage objective (tricking the attacker into opening a reverse shell on its own machine) is the most reliable defense, since it requires fewer attacker actions to trigger than the alternative agent-tarpit objective (which requires sustained multi-round entrapment and has slightly higher escape probability). The FTP decoy is more effective than the Web-app decoy because it requires only a simple anonymous-login interaction to trigger the injection, whereas the Web-app decoy requires a more complex (e.g., SQL-injection-style) interaction that the LLM-agent sometimes fails on its first attempt, occasionally causing it to abandon the decoy for another (real, vulnerable) service before ever receiving the injected payload -- identified as the primary failure mode for Mantis. CTF:Dancing (which has an easily-exploitable real SMB server as an alternative target) is the scenario where Mantis is least effective, particularly with the Web-app decoy. In the resource-draining agent-tarpit variant, increasing the fake filesystem's directory branching factor (subdirectories per node) directly and substantially increases the dollar cost of the API calls the attacker's LLM must make (up to $4.55 for HackingBuddyGPT at 150 expected subdirectories per node over just the first 10 tarpit rounds), demonstrating a controllable economic-cost-imposition capability distinct from outright agent neutralization; cost scaling differs meaningfully by agent framework, driven by each agent's memory/history-management mechanism (e.g., PentestGPTAuto's action-history reinsertion amplifies tarpit verbosity and cost, while AutoPenAgent's summarization and HackingBuddyGPT's aggressive prompt truncation make them comparatively cheaper to run against, independent of Mantis's own effectiveness).</t>
         </is>
       </c>
       <c r="F244" s="5" t="n"/>
@@ -10789,7 +10797,7 @@
       <c r="H244" s="5" t="n"/>
       <c r="I244" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10807,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -10814,7 +10822,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>Closed-Book (Zero-shot, no retrieval), Standard RAG, Vanilla Chain-of-Thought (CoT), Reflection Prompting (a prompt-only approximation inspired by Self-RAG), Prompt-Filtered RAG (prompt-only document filtering inspired by prior document-filtering RAG work, not a trained NLI model), and Conflict-aware RAG (an instruction-only baseline telling the model to use context but override it when it conflicts with established facts) -- used specifically to isolate how much of CDD's gain comes from explicit conflict-checking instructions versus the decomposition mechanism itself. A length-matched 'sham CoT' ablation variant with semantically vacuous steps is also used as a control.</t>
+          <t>The 'No Defense' condition (attacker operates against the same target machine with no Mantis deployment) serves as the sole baseline, establishing each LLM-agent's unimpeded success rate and round count for comparison against Mantis-protected configurations.</t>
         </is>
       </c>
       <c r="F245" s="5" t="n"/>
@@ -10822,7 +10830,7 @@
       <c r="H245" s="5" t="n"/>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10832,7 +10840,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -10847,7 +10855,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial in the security-attacker sense, though the paper explicitly studies robustness to adversarially-perturbed retrieved context. The paper frames its threat model as retrieval-quality/knowledge-conflict robustness rather than a malicious external actor: retrieved evidence may be 'wrong or adversarially injected' (citing prior indirect-injection and RAG-poisoning literature), and the paper's own adversarial-context construction uses an LLM-based perturbation engine to generate four types of premise-conflicting context (Entity Swap, Temporal Shift, Logical Contradiction, Distractor Evidence) plus a worst-case human-misconception injection probe on TruthfulQA. The paper's stated threat model is deliberately framed as an observability problem rather than a defense against a strategic adversary: given that retrieved context may be incorrect (whether through retrieval error or adversarial injection), the goal is to make visible which information source (retrieved context, parametric prior, or a post-hoc rationale) actually controlled the model's final answer, since final-answer accuracy alone cannot distinguish a model correctly rejecting false retrieval from one blindly complying with it or merely relying on memorized knowledge. The authors explicitly note their evaluation covers closed-API, single-document, and largely LLM-generated (rather than organic/human-authored) adversarial content, treating this as a controlled stress test scope boundary rather than a claim about real-world adversarial retrieval pipelines.</t>
+          <t>Formal two-party game-theoretic threat model (Section 3): an attacker A, an autonomous LLM-agent (paired with a cyberattack framework spanning reconnaissance through exploitation) whose goal is to compromise a remote target machine S and achieve an adversarial objective obj_A (e.g., opening a shell, exfiltrating data), with no prior knowledge of S beyond its IP address, operating within a bounded maximum number of rounds n_max. The defender D operates on S and is deliberately handicapped: agnostic to the attacker's specific LLM, strategy, or objectives, and unaware of S's actual vulnerabilities (so cannot patch them preemptively) -- the defender's sole capability is deploying Mantis, which exploits the attacker LLM's susceptibility to indirect prompt injection embedded in system responses the agent must parse to plan its next action. The defender's goal (obj_D) is either active defense/'agent-counterstrike' (manipulating the attacker's LLM into executing commands that compromise the attacker's own hosting machine, e.g., opening a reverse shell back to the defender) or passive defense/'agent-tarpit' (trapping the attacker in an artificially generated, infinitely-deep fake filesystem to exhaust its time/token budget and prevent it from completing its actual objective or moving to a new target). The attacker wins if it achieves obj_A within the round limit; the defender wins if the attacker fails to achieve obj_A and the defender separately achieves obj_D (both conditions can independently fail, producing a draw).</t>
         </is>
       </c>
       <c r="F246" s="5" t="n"/>
@@ -10855,7 +10863,7 @@
       <c r="H246" s="5" t="n"/>
       <c r="I246" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10873,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10880,7 +10888,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>The paper has an extensive, explicit 'Limitations' section with eight enumerated points. Cross-Family Generalization: the clearest causal-sensitivity signal (64.1% mistake-injection sensitivity) is specific to Gemini-2.5-Flash, with effect magnitude varying substantially across model families; disentangling architecture, alignment-training, and prompt-sensitivity contributions to the Claude-family results is left as a natural open-weight extension. Causal-Coupling Uncertainty: Claude-family mistake-injection sensitivities lie within [-3%, +7%] versus 64.1% on Gemini, reported conservatively as 'no measurable coupling' rather than a proven absence of causal footprint, since paired significance/confidence-interval/power analysis was not conducted. TruthfulQA Closed-Book Control: the 15.0% figure characterizes context-injected behavior under a binary scorer without a no-context control to precisely quantify the prior-versus-context gap. Baseline Prompt Asymmetry: because Standard RAG implicitly encourages context-reliance while CDD instructs explicit conflict-checking, part of CDD's gain is attributable to the conflict-checking instruction itself (isolated via the Conflict-aware RAG baseline) rather than decomposition alone. CDD-alpha Threshold Tuning: the routing threshold tau=0.7 was selected via histogram inspection on the adversarial evaluation pool itself rather than a held-out development set or full parameter sweep, so it should be read as illustrative rather than a tuned deployment setting. TruthfulQA Realism: using the explicit top misconception is a deliberate worst-case probe, not representative of average-case organic BM25/DPR retrieval degradation. Prior Answer Not Context-Isolated: Step 2 of CDD elicits the parametric answer after the context is already visible, so it is a prior reported under the CDD prompt rather than a true context-free parametric answer, weakening the prior/posterior separation. Conceptual-Only Belief-Revision Framing: the belief-revision vocabulary borrowed from Alchourron et al. (1985) is used as a conceptual scaffold rather than an instantiated token-level divergence measure (e.g., Jensen-Shannon Divergence), since exact computation requires white-box logit access unavailable for the closed-API models studied. Additional caveats include the need for stricter faithfulness tests (factual-only Step-2 corruption, rationale swaps, answer-hidden interventions), closed-API behavioral drift under provider updates, and single-run closed-API evaluation at temperature 0.0 (which does not guarantee deterministic behavior), meaning small directional gaps -- especially in the Claude-family replication -- should be interpreted cautiously pending repeated or open-weight replication.</t>
+          <t>The paper has no section explicitly titled 'Limitations,' but discusses concrete limitations inline in Section 6.3 and the Conclusion &amp; Discussion (Section 9). The agent-counterstrike (active/hack-back) technique is explicitly noted to carry 'inherent limitations': executing hack-back operations raises ethical and legal concerns that constrain its general applicability, and sufficiently well-configured attackers could heavily sandbox the LLM-agent's hosting machine, substantially limiting the impact of any active defense targeting arbitrary code execution on the attacker's system -- motivating the paper's development of the passive agent-tarpit alternative. Empirically, Mantis's failure mode is identified as decoy-dependent: when a decoy requires a more complex exploitation interaction (e.g., the Web-app decoy's SQL injection) that the attacking LLM-agent initially fails, the agent may abandon that decoy for another, genuinely vulnerable service before the injected payload is ever delivered, meaning Mantis's effectiveness is contingent on decoy attractiveness relative to real vulnerabilities present on the same target. The Conclusion also frames an open research question rather than a solved limitation: whether prompt injection defenses can ultimately be developed by attackers to make their LLM-agents robust against exactly this kind of manipulation, which would undermine Mantis's core mechanism, and whether more general (rather than LLM-agent-specific) prompt-injection defenses might eventually neutralize this attack surface; all experiments were also conducted only within isolated, sandboxed HackTheBox environments explicitly to avoid legal/ethical risk, meaning generalization to arbitrary real-world attacker infrastructure was not empirically tested.</t>
         </is>
       </c>
       <c r="F247" s="5" t="n"/>
@@ -10888,7 +10896,7 @@
       <c r="H247" s="5" t="n"/>
       <c r="I247" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10906,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10913,7 +10921,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>This paper identifies and addresses a blind spot in standard Retrieval-Augmented Generation (RAG) evaluation: final-answer accuracy alone cannot distinguish whether a model's answer was controlled by retrieved (possibly wrong or adversarially injected) context, by the model's own parametric prior knowledge, or by a post-hoc rationale generated after the fact -- a phenomenon the authors term 'context compliance,' the regime in which retrieved context controls the answer even when it conflicts with the model's internal knowledge. To make this hidden arbitration observable, the paper introduces Context-Driven Decomposition (CDD), an inference-time diagnostic intervention (not proposed as a production defense) that decomposes a single conflicted RAG instance into a five-step observable reasoning trace: (1) Contextual Extraction (elicit the answer implied by retrieved context), (2) Parametric Extraction (elicit the model's own prior-knowledge answer, though acknowledged to be elicited with context already visible rather than fully context-isolated), (3) Divergence Check (compare the two answers), (4) Premise Isolation (if they conflict, isolate the specific conflicting premise and evaluate it against established facts/history), and (5) Resolution (produce the final answer). Crucially, the authors treat this trace not as a trustworthy explanation but as a testable diagnostic artifact, applying causal-sensitivity interventions borrowed from chain-of-thought faithfulness research (mistake-injection and truncation, adapted from prior early-answering and adding-mistakes tests) to empirically check whether perturbing the resolution trace actually changes the final answer -- rather than assuming the trace's stated reasoning is causally responsible. The authors also introduce Epi-Scale, a new 4,500-record benchmark (2,250 clean + 2,250 adversarial, spanning HotpotQA, Natural Questions, and FEVER with four LLM-generated adversarial perturbation types: Entity Swap, Temporal Shift, Logical Contradiction, Distractor Evidence) and a compute-aware routing variant, CDD-alpha, which uses a prompted contradiction gate to route only high-conflict examples through the full five-step probe while low-conflict examples bypass to standard RAG. Across worst-case TruthfulQA misconception-injection stress tests, the Epi-Scale adversarial benchmark, and cross-model replication on the Claude family, the paper demonstrates three key findings: (1) misleading retrieved context can severely degrade accuracy (Standard RAG falls to 15.0% under worst-case misconception injection); (2) accuracy improvement and causal trace-sensitivity can dissociate across model families -- CDD improves adversarial accuracy on both Gemini-2.5-Flash and the Claude family, but the trace-perturbation causal-sensitivity signal is large only on Gemini, meaning better final answers need not share the same underlying mechanism; and (3) explicit decomposition improves controlled-conflict robustness over a strong conflict-aware instruction-only baseline specifically on localized factual-conflict types (Entity Swap, Logical Contradiction) where premise isolation directly applies, with ablations and a length-matched sham-prompt control confirming the gains derive from the specific decomposition steps (particularly Premise Isolation and Divergence Check) rather than merely from added prompt length or generic multi-step structure, while also revealing a real trade-off of roughly 18 points of clean-sample accuracy for the observed adversarial robustness gain.</t>
+          <t>This paper introduces Mantis (Malicious LLM-Agent Neutralization and exploitation Through prompt Injections), a novel defensive framework that inverts the conventional framing of prompt injection -- typically treated purely as an LLM vulnerability -- into a proactive countermeasure against autonomous LLM-driven cyberattacks. The key insight is that an attacking LLM-agent, in order to plan its next action, must parse and interpret the system responses it receives while probing a target machine (e.g., FTP banners, HTTP responses, command outputs); since this interaction channel is under the defender's control, the defender can embed adversarial prompt injections directly into these responses to hijack the attacking LLM's decision-making in real time. Mantis is architected around two components: decoy services (deliberately vulnerable-looking fake services such as FTP servers and web applications, designed to attract the attacking LLM-agent early in its reconnaissance/exploitation chain and serve as the delivery mechanism for the injected payload, with the injection itself rendered invisible to human operators via ANSI escape sequences and HTML comment tags so as not to disrupt legitimate service operation) and an Injection Manager (which detects an 'activation event,' such as a successful anonymous login to a decoy, and dynamically constructs and delivers a context-specific prompt-injection payload). The framework supports two distinct sabotage objectives operationalizing this mechanism: active defense/'agent-counterstrike,' which manipulates the attacking LLM-agent into executing commands (e.g., a netcat reverse-shell initiator, delivered indirectly via a curl-and-execute instruction to evade the model's built-in alignment-based rejection of overtly malicious commands) that open a reverse shell back to the defender, giving the defender control over the attacker's own machine for intelligence-gathering or direct disruption; and passive defense/'agent-tarpit,' which traps the attacking LLM-agent in a dynamically generated fake filesystem with an infinitely deep directory tree, forcing indefinite unproductive exploration that both prevents the agent from completing its real objective or pivoting to other targets and artificially inflates its operational (API/token) costs, a cost-imposition effect the authors show scales directly with the tarpit's configured filesystem branching complexity. Evaluated against three existing autonomous pentesting agent frameworks (PentestGPTAuto, AutoPenAgent, HackingBuddyGPT) built on GPT-4o and Claude 3.5-Sonnet, attacking real vulnerable HackTheBox CTF machines, Mantis achieves roughly 95.4% success at its sabotage objective while suppressing attacker success to under 3% across nearly all tested configurations, establishing prompt injection as a practically effective, LLM-agnostic defensive primitive against the emerging threat of automated, LLM-driven cyber offense, while the authors acknowledge this defense's efficacy is fundamentally contingent on attacker LLMs remaining susceptible to prompt injection -- a vulnerability that future attacker-side hardening could in principle close.</t>
         </is>
       </c>
       <c r="F248" s="5" t="n"/>
@@ -10921,7 +10929,7 @@
       <c r="H248" s="5" t="n"/>
       <c r="I248" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -10931,7 +10939,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -10954,7 +10962,7 @@
       <c r="H249" s="5" t="n"/>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10972,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -10987,7 +10995,7 @@
       <c r="H250" s="5" t="n"/>
       <c r="I250" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -10997,7 +11005,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -11020,7 +11028,7 @@
       <c r="H251" s="5" t="n"/>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11030,7 +11038,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -11045,7 +11053,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F252" s="5" t="n"/>
@@ -11053,7 +11061,7 @@
       <c r="H252" s="5" t="n"/>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11071,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -11078,7 +11086,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F253" s="5" t="n"/>
@@ -11086,7 +11094,7 @@
       <c r="H253" s="5" t="n"/>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11104,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -11111,7 +11119,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="F254" s="5" t="n"/>
@@ -11119,7 +11127,7 @@
       <c r="H254" s="5" t="n"/>
       <c r="I254" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11137,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -11152,7 +11160,7 @@
       <c r="H255" s="5" t="n"/>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11162,7 +11170,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -11185,7 +11193,7 @@
       <c r="H256" s="5" t="n"/>
       <c r="I256" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11203,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -11218,7 +11226,7 @@
       <c r="H257" s="5" t="n"/>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11236,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -11251,7 +11259,7 @@
       <c r="H258" s="5" t="n"/>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11261,7 +11269,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -11284,7 +11292,7 @@
       <c r="H259" s="5" t="n"/>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11294,7 +11302,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -11309,7 +11317,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>No explicit code/dataset release URL is given in the extracted text. The paper states adaptive-attack prompt templates and payload examples are provided 'at Appendix E' and 'Appendix D' within the paper itself, but no external GitHub/HuggingFace repository link is mentioned for the evaluation harness, adapted payloads, or per-framework configurations.</t>
+          <t>N - the paper proposes a conceptual response-design framework (Figure 1) with no implementation, code, or dataset released.</t>
         </is>
       </c>
       <c r="F260" s="5" t="n"/>
@@ -11317,7 +11325,7 @@
       <c r="H260" s="5" t="n"/>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11335,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -11342,7 +11350,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Ten representative IPI-centric defense frameworks are evaluated: LlamaFirewall (Detection), Tool Filter (Prompt Engineering), Meta SecAlign (Fine-tuning, using its public LoRA adapter for Llama-3.1-8B-Instruct), IsolateGPT, ACE, and CaMeL (System Design: plan-then-execute, code-then-execute, and Dual-LLM architectures respectively), Task Shield and MELON (Runtime Checking), and Progent (Policy Enforcing, with a Progent-LLM variant for automated policy generation). For all non-fine-tuning frameworks, GPT-4o (2024-11-20) is used as the backend LLM (temperature 0); DeepSeek-V3 is used in a supplementary generalization check (Appendix F). Undefended baselines Llama3.1-8B and SecAlign are also reported for comparison.</t>
+          <t>None - no concrete LLM is fine-tuned, tested, or benchmarked; the paper discusses LLMs and prompt injection/jailbreaking generically without running any experiment on a specific model.</t>
         </is>
       </c>
       <c r="F261" s="5" t="n"/>
@@ -11350,7 +11358,7 @@
       <c r="H261" s="5" t="n"/>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11368,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -11375,7 +11383,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>Three existing static agent-IPI benchmarks are used: AgentDojo (4 scenarios per attack method, 74 tools, 629 test cases), InjecAgent (6 scenarios per attack method, 62 tools, 1,054 test cases), and Agent Security Bench/ASB (10 scenarios per attack method, 420 tools, 2,040 test cases). Utility is measured via AgentDojo's dynamic benchmark without implanted attack payloads. The paper's own contribution is a set of 949 adapted/adjusted IPI payloads (generated via an LLM-driven payload-adjustment-and-refinement pipeline) used to construct the three novel adaptive attacks.</t>
+          <t>None - no dataset or benchmark is constructed or used; Table 1 and Table 2 are qualitative summaries of risks and ethical concerns, not empirical evaluation artifacts.</t>
         </is>
       </c>
       <c r="F262" s="5" t="n"/>
@@ -11383,7 +11391,7 @@
       <c r="H262" s="5" t="n"/>
       <c r="I262" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11401,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -11408,7 +11416,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>Across the three static benchmarks (Table 2), most SoTA defense frameworks reduce ASR below 10% in the majority of scenarios (e.g., Progent and IsolateGPT near 0% average ASR; MELON 2.67%, Task Shield 0.43%), but undefended baselines are far more vulnerable (Llama3.1-8B 45.91% average ASR, GPT-4o 23.69%, SecAlign 11.77%). However, all ten frameworks are shown to be bypassable: the three novel adaptive attacks substantially increase ASR against targeted frameworks. Semantic-Masquerading IPI (adapting payloads to use functionally similar/differently-parameterized tools) more than doubles ASR against IsolateGPT, Tool Filter, CaMeL, and LlamaFirewall, with IsolateGPT and LlamaFirewall approaching a fourfold increase. Cascading IPI (an if-then-else payload structure with judge/filter items targeting auxiliary judge-LLM components) achieves 5.37% ASR against Task Shield (2.6x its 2.07% baseline) and 4.53% against MELON (4.8x its 0.95% baseline). Isolation-Breach IPI achieves the first documented zero-day-style bypass of IsolateGPT's architectural planner/executor separation by exploiting an overlooked information channel (error-message propagation/context feedback loops) to inject malicious intent directly into the trusted planner's context, causing the downstream isolation mechanism to become irrelevant once the planner itself is compromised.</t>
+          <t>No quantitative result is reported. The paper conceptually proposes a multi-phase 'response design' pipeline (classification of attack category via threshold-based classification, template selection, customization/filtering, and delivery) intended to mitigate five threat categories (prompt injection, jailbreaking, PII exposure, sexual content, hate speech), but presents no implementation or measured effectiveness.</t>
         </is>
       </c>
       <c r="F263" s="5" t="n"/>
@@ -11416,7 +11424,7 @@
       <c r="H263" s="5" t="n"/>
       <c r="I263" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11434,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -11441,7 +11449,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>For the benchmark evaluation, each of the ten defense frameworks is compared against undefended baseline agents (plain GPT-4o, plain Llama3.1-8B, and SecAlign as a fine-tuning-only baseline) across the same three benchmarks. For the adaptive attacks, each novel attack is compared against the corresponding template-based baseline attack already used by the benchmark (e.g., the AgentDojo 'Important' attack template serves as the direct-payload baseline for both the Semantic-Masquerading and Cascading IPI comparisons).</t>
+          <t>None - no baseline comparison is performed since no system is built or tested.</t>
         </is>
       </c>
       <c r="F264" s="5" t="n"/>
@@ -11449,7 +11457,7 @@
       <c r="H264" s="5" t="n"/>
       <c r="I264" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11467,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -11474,7 +11482,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>The threat model assumes the adversary has no prior knowledge of the agent's architecture A or backend LLM, and can only manipulate static resources within the environment E; specifically, when the agent invokes a tool, E returns a malicious response embedded via a static injection template controlled by the adversary. All information and resources accessible to the agent are treated as trusted except for tool return results (agent memory, tool descriptions/schemas, the SDK, and OS are assumed trustworthy). The attack succeeds if the agent's final tool-call execution sequence matches the adversary's intended sequence. This SoK focuses exclusively on Indirect Prompt Injection (IPI) against LLM agents with function-calling/tool-use capabilities (distinct from IPI against passive QA LLMs), where injected content typically arrives via tool return results and the attacker's goal is to hijack tool-calling behavior to threaten user assets or privacy.</t>
+          <t>Discussed only in general terms: prompt injection is described as attackers manipulating LLM inputs to compromise training data confidentiality and system behavior, and jailbreaking as bypassing safety guardrails; no formal attacker capability model, concrete attack instantiation, or defended system boundary is specified.</t>
         </is>
       </c>
       <c r="F265" s="5" t="n"/>
@@ -11482,7 +11490,7 @@
       <c r="H265" s="5" t="n"/>
       <c r="I265" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11492,7 +11500,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -11507,7 +11515,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>The paper has no section explicitly titled 'Limitations.' The closest analog appears in the discussion immediately preceding the Conclusion, following the Isolation-Breach IPI attack: the authors state that 'architectural separation alone is insufficient when high-level planners remain semantically coupled to untrusted data' and argue future defenses must move beyond ad-hoc isolation toward rigorous formal reasoning (e.g., mathematically enforced non-interference properties ensuring tainted inputs cannot influence privileged control flows through any channel, including error logs or side-effects) to provide provable security guarantees -- framing the current generation of defenses, including those evaluated in this SoK, as fundamentally lacking such formal guarantees. The Conclusion similarly states that 'future agent security must evolve beyond static benchmarks' to address the six identified root-cause architectural vulnerabilities.</t>
+          <t>The authors do not state concrete technical limitations of an implemented system since none is built; they instead call generally for future work translating their conceptual response-design tool and 'AI response spectrum' framework into a working evaluative tool, and stress the need for interdisciplinary collaboration (ethicists, sociologists, psychologists) to define response templates and thresholds.</t>
         </is>
       </c>
       <c r="F266" s="5" t="n"/>
@@ -11515,7 +11523,7 @@
       <c r="H266" s="5" t="n"/>
       <c r="I266" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11533,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
+          <t>The Ethics of Interaction: Mitigating Security Threats in LLMs</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -11540,7 +11548,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>This paper is the first Systematization of Knowledge (SoK) on IPI-centric LLM agent defense frameworks, providing a five-dimensional taxonomy (Technical Paradigm: detection, prompt engineering, fine-tuning, system design, runtime checking, policy enforcing; Intervention Stage: pre-/intra-/post-inference; Model Access: white-/black-box; Explainability: deterministic/probabilistic; Automation Level: full-/semi-automation), a comprehensive three-axis empirical evaluation (security via Attack Success Rate, utility via task success rate/false positive rate, and overhead via wall-clock time/token usage) of ten representative frameworks across three existing static benchmarks (AgentDojo, InjecAgent, ASB) with standardized model configurations, and a defense-failure root-cause analysis. From analyzing why representative frameworks fail under evaluation, the authors identify six recurring root causes of defense circumvention: imprecise access control over tool selection, imprecise access control over tool parameters, incomplete isolation of malicious information (e.g., porous planner/executor separation in system-design frameworks), judgment errors in checking/detecting auxiliary LLMs, inadequate coverage of static security policies, and poor generalization of fine-tuned defense LLMs. Building on this taxonomy of failure modes, the paper designs and demonstrates three novel logic-driven (not gradient-optimization-based) adaptive attacks, each targeting a specific root cause: Semantic-Masquerading IPI uses an LLM-driven pipeline to adapt injection payloads to use functionally similar or differently-parameterized tools that evade tool-selection/parameter access-control checks (validated via an 'Attack Success Judging' LLM since the adapted payloads break AgentDojo's static state-based ground truth); Cascading IPI structures the injected payload into head/body/end components with an if-then-else logic targeting auxiliary judge-LLM components used by runtime-checking frameworks (Task Shield, MELON), using 'judge' payload items to force a fake-benign auditor response and 'filter' items to force verbatim repetition that bypasses extraction/filtering; and Isolation-Breach IPI exploits overlooked information-flow channels (error messages, context feedback loops) to inject malicious intent directly into a system-design framework's architecturally 'trusted' planner component, demonstrated as a novel bypass of IsolateGPT.</t>
+          <t>Surveys the ethical dimensions of five LLM security threats -- prompt injection, jailbreaking, PII exposure, sexual content, and hate-based content -- and argues for their societal and individual harms. Proposes, at a conceptual level only, an 'evaluative tool' comprising a response-design pipeline (attack classification, response template selection, customization/filtering, delivery) intended to help developers preemptively fortify systems and to score LLM chatbot responses against expected human ethical behavior via an 'AI response spectrum.' No system is implemented, no model is evaluated, and no dataset or benchmark is introduced. Matters only as a position/framework paper articulating ethical motivations for defense work; it contributes neither a named attack technique nor a validated defense to this registry.</t>
         </is>
       </c>
       <c r="F267" s="5" t="n"/>
@@ -11548,7 +11556,7 @@
       <c r="H267" s="5" t="n"/>
       <c r="I267" s="5" t="inlineStr">
         <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
+          <t>1f1aefa3ae39eb0ef7285a2a075acfbf06b66e03</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11566,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -11581,7 +11589,7 @@
       <c r="H268" s="5" t="n"/>
       <c r="I268" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11591,7 +11599,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11606,7 +11614,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F269" s="5" t="n"/>
@@ -11614,7 +11622,7 @@
       <c r="H269" s="5" t="n"/>
       <c r="I269" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11632,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -11647,7 +11655,7 @@
       <c r="H270" s="5" t="n"/>
       <c r="I270" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11657,7 +11665,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -11672,7 +11680,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F271" s="5" t="n"/>
@@ -11680,7 +11688,7 @@
       <c r="H271" s="5" t="n"/>
       <c r="I271" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11698,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -11705,7 +11713,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F272" s="5" t="n"/>
@@ -11713,7 +11721,7 @@
       <c r="H272" s="5" t="n"/>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11731,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -11738,7 +11746,7 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F273" s="5" t="n"/>
@@ -11746,7 +11754,7 @@
       <c r="H273" s="5" t="n"/>
       <c r="I273" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11764,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -11771,7 +11779,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F274" s="5" t="n"/>
@@ -11779,7 +11787,7 @@
       <c r="H274" s="5" t="n"/>
       <c r="I274" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11797,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -11804,7 +11812,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F275" s="5" t="n"/>
@@ -11812,7 +11820,7 @@
       <c r="H275" s="5" t="n"/>
       <c r="I275" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11822,7 +11830,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -11837,7 +11845,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F276" s="5" t="n"/>
@@ -11845,7 +11853,7 @@
       <c r="H276" s="5" t="n"/>
       <c r="I276" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11863,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -11878,7 +11886,7 @@
       <c r="H277" s="5" t="n"/>
       <c r="I277" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11896,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -11903,7 +11911,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F278" s="5" t="n"/>
@@ -11911,7 +11919,7 @@
       <c r="H278" s="5" t="n"/>
       <c r="I278" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11921,7 +11929,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -11936,7 +11944,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>Y - dataset/code released at github.com/vladutdinu/dmattack</t>
+          <t>All code, data, and pre-computed results required to reproduce the experiments and figures are publicly available: 'All code, data, and pre-computed results required to reproduce the experiments and figures in this paper are publicly available at https://github.com/MatthiasHBusch/BlindingLLMs.'</t>
         </is>
       </c>
       <c r="F279" s="5" t="n"/>
@@ -11944,7 +11952,7 @@
       <c r="H279" s="5" t="n"/>
       <c r="I279" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11962,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -11969,7 +11977,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Llama3.1:8b; Llama3.2:3b; Llama3.2:1b; Mistral-Nemo:12b; Mistral:7b-instruct; SmolLM:1.7b; Qwen2:7b; Qwen2:1.5b; Qwen2.5:1.5b; Granite3-MoE:3b; Gemini 2.0-Flash; GPT-4o-Mini; filters: Meta Prompt-Guard, ProtectAI DeBERTaV3-prompt-injection-v2</t>
+          <t>Nine LLM variants across three families: GPT-4.1, GPT-5, and Gemini 2.5 (including Gemini 2.5 Flash and Flash-Lite variants, which show notably different memorization/interference behavior from the other models).</t>
         </is>
       </c>
       <c r="F280" s="5" t="n"/>
@@ -11977,7 +11985,7 @@
       <c r="H280" s="5" t="n"/>
       <c r="I280" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11995,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -12002,7 +12010,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>Self-constructed "DisruptiveMessages" (DM-10, DM-15, DM-20) dataset: 500 HTML pages sampled from an open-source corpus, with 10/15/20 randomly placed hidden prompt injections per page</t>
+          <t>Three MoleculeNet benchmark datasets: ESOL/Delaney (aqueous solubility, using the experimentally measured log-solubility column as target, explicitly excluding Delaney's own calculated regression-equation output), Lipophilicity, and QM7 (atomization energy). Three control datasets are also used: a 2025 ASAP Discovery antiviral potency dataset (post-knowledge-cutoff negative control for retrieval/memorization), and two additional positive-control datasets (including IUPAC atomic weights and boiling points from Wikipedia) drawn from sources guaranteed to be in training data. In-context sample sizes of 0-, 60-, and 1000-shot are used as a controlled variable.</t>
         </is>
       </c>
       <c r="F281" s="5" t="n"/>
@@ -12010,7 +12018,7 @@
       <c r="H281" s="5" t="n"/>
       <c r="I281" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -12020,7 +12028,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -12035,7 +12043,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>Baseline ASR on the DM-X dataset ranges from 0% (SmolLM:1.7b) to 60.7% average (Mistral-Nemo:12b); the proposed 128/64-token windowed pre-processing filter using PromptGuard or DeBERTaV3 reduces ASR on DM-20 to roughly 7-28% depending on model and tokenizer, a substantial reduction versus unfiltered baselines.</t>
+          <t>Across a 0-shot performance comparison, a post-knowledge-cutoff dataset shows LLMs generalize to unseen samples via genuine learned structure-property relationships rather than verbatim retrieval, and the pre-2018 legacy datasets (Delaney, Lipophilicity, QM7) behave similarly -- indicating no evidence of direct dataset-specific memorization for those benchmarks -- whereas a control test with IUPAC/Wikipedia values shows LLMs do retrieve some numbers verbatim when present in training corpora. Under the six-level information-blinding framework, in-context-learning reliance varies sharply by property: Lipophilicity performance collapses from ~72% to ~35% under blinding (consistent across 8/9 models, sign-test p=0.02), Delaney/solubility drops only modestly (~96% to ~92%), and QM7 shows no degradation. Prior knowledge acts as a 'double-edged sword': performance with 60 in-context examples was lower than 0-shot in 19/27 model x dataset cases (sign-test p=0.026), an effect mostly resolved by 1000 samples (better than 60-shot in 21/27 cases, p=0.003), and in the most extreme case (Gemini 2.5 Flash on QM7), suppressing the property-name prior via blinding raised correlation by +38 percentage points (from ~6% to ~44%, bootstrap CI [+17,+54] excluding zero) -- evidence that strong but misleading priors can actively interfere with in-context learning rather than support it.</t>
         </is>
       </c>
       <c r="F282" s="5" t="n"/>
@@ -12043,7 +12051,7 @@
       <c r="H282" s="5" t="n"/>
       <c r="I282" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -12053,7 +12061,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -12068,7 +12076,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>Unfiltered LLM responses (raw ASR per model) vs. filtered responses using DeBERTaV3-based chunk filtering and PromptGuard-based chunk filtering, at 128-token and 64-token window sizes</t>
+          <t>The paper's comparative structure is internal (across blinding levels, shot counts, models, and datasets) rather than against external prior systems; it uses a positive-control dataset (known IUPAC/Wikipedia values) and a negative-control post-cutoff dataset (2025 ASAP antiviral potency) as calibration baselines for its memorization diagnostics, and compares 0-shot vs. 60-shot vs. 1000-shot performance and Level-1 (full context) vs. Level-6 (maximally blinded) performance as the core experimental contrasts.</t>
         </is>
       </c>
       <c r="F283" s="5" t="n"/>
@@ -12076,7 +12084,7 @@
       <c r="H283" s="5" t="n"/>
       <c r="I283" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -12086,7 +12094,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -12101,7 +12109,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>An attacker embeds hidden prompt injection instructions (e.g., in invisible HTML spans) at random locations within web pages that an LLM-based web-content-extraction/browsing system retrieves and processes, aiming to hijack the response (e.g., force a specific keyword or terminate generation).</t>
+          <t>N/A - non-adversarial. This is a scientific-capability/evaluation-methodology paper, not a security paper; the incidental failure mode of interest is a form of context-vs-parametric-knowledge conflict -- specifically, benchmark contamination and memorization masquerading as genuine in-context learning, and cases where an LLM's strong pre-trained (parametric) prior about a molecular property actively conflicts with and degrades performance relative to what could be learned from the provided in-context examples alone, particularly when the in-context sample count is small.</t>
         </is>
       </c>
       <c r="F284" s="5" t="n"/>
@@ -12109,7 +12117,7 @@
       <c r="H284" s="5" t="n"/>
       <c r="I284" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12127,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -12134,7 +12142,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>Authors note the filtering pipeline's computational overhead requires balancing security and efficiency for retrieval applications, that filtering performance is highly dependent on the choice of LLM and token-window size, and that aggressive filtering risks removing legitimate content while lenient filtering risks letting malicious prompts through.</t>
+          <t>The paper contains an explicit '5.5 Limitations and Future Work' section with three named points, quoted/paraphrased directly: (1) the study uses only SMILES string representations, while many molecular property prediction methods leverage 3D coordinates or molecular graphs -- reflecting the text-based nature of LLMs but potentially underestimating their potential with richer input formats; (2) statistical power is limited by computational cost, with only 2 runs per configuration, though uncertainty is quantified via bootstrapping over the test set and model-to-model comparisons are softened accordingly, with additional runs noted as a natural extension to tighten confidence intervals; (3) using an LLM with an openly available (rather than proprietary/closed) training corpus would allow definitively proving the extent of memorization of specific numbers and datasets, which the closed frontier models studied here do not permit.</t>
         </is>
       </c>
       <c r="F285" s="5" t="n"/>
@@ -12142,7 +12150,7 @@
       <c r="H285" s="5" t="n"/>
       <c r="I285" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12160,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
+          <t>In-Context Molecular Property Prediction with LLMs: A Blinding Study on Memorization and Knowledge Conflicts</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -12167,7 +12175,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>Constructs a benchmark dataset (DisruptiveMessages / DM-10/15/20) of HTML pages containing randomly placed hidden prompt injections designed to hijack an LLM's response to a fixed keyword, and evaluates attack success rate across 12 open- and closed-source LLMs. Proposes a pre-processing defense that chunks retrieved HTML into fixed-size (128- or 64-token) windows, classifies each chunk with off-the-shelf detectors (Meta Prompt-Guard or ProtectAI's DeBERTaV3-prompt-injection-v2), and filters out flagged chunks before re-feeding the cleaned content to the LLM. Shows the filtering substantially reduces ASR relative to unfiltered baselines across models and window sizes. Releases the dataset and experiment code on GitHub.</t>
+          <t>This paper investigates whether LLMs performing molecular property prediction via in-context learning (ICL) are doing genuine numerical/structural regression or are instead relying on memorized values from widely-used, long-public benchmark datasets (ESOL/Delaney, Lipophilicity, QM7) that may have leaked into pre-training corpora -- a benchmark contamination concern the authors argue is especially acute given the small number of standard datasets dominating the molecular property prediction literature. The core methodological contribution is a systematic six-level information-blinding framework that progressively strips contextual information from the prediction task (ranging from Level 1, full chemical context with the property explicitly named, to Level 6, where both the property name is hidden and both input SMILES strings and target values are transformed via a consistent, invertible mathematical transformation to prevent verbatim value/pattern recognition), allowing the authors to selectively deactivate specific capabilities (verbatim memorization, generalized domain knowledge, chemical in-context learning, general in-context learning) and isolate their individual contributions by comparing performance across blinding levels. This blinding approach is combined with variation in in-context sample size (0-, 60-, and 1000-shot) as an additional, independent control on information access, and is validated using a memorization-diagnostic methodology that pairs an exact-match-rate metric (first three significant digits) with precision-scaling retention analysis across positive-control datasets (known verbatim-memorized values, e.g. IUPAC/Wikipedia atomic weights) and a negative-control post-knowledge-cutoff dataset (2025 ASAP Discovery antiviral potency data) to calibrate what genuine verbatim memorization looks like versus learned generalization. Applied across nine LLM variants (GPT-4.1, GPT-5, Gemini 2.5 family) and three MoleculeNet datasets, the framework reveals that apparent benchmark success reflects a mixture of genuine learned structure-property relationships, general and chemical in-context learning, and (for some model families and datasets) prior knowledge that actively conflicts with and can degrade in-context-learning performance, motivating the paper's broader methodological recommendation that molecular-property benchmarks intended to test pure in-context generalization should incorporate blinding protocols rather than relying on standard, potentially-contaminated evaluation sets.</t>
         </is>
       </c>
       <c r="F286" s="5" t="n"/>
@@ -12175,7 +12183,7 @@
       <c r="H286" s="5" t="n"/>
       <c r="I286" s="5" t="inlineStr">
         <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
+          <t>179acbd9f0287369c32a5ddef4660801af0590bd</t>
         </is>
       </c>
     </row>
@@ -12185,7 +12193,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -12208,7 +12216,7 @@
       <c r="H287" s="5" t="n"/>
       <c r="I287" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12218,7 +12226,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -12241,7 +12249,7 @@
       <c r="H288" s="5" t="n"/>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12251,7 +12259,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -12274,7 +12282,7 @@
       <c r="H289" s="5" t="n"/>
       <c r="I289" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12292,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -12299,7 +12307,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F290" s="5" t="n"/>
@@ -12307,7 +12315,7 @@
       <c r="H290" s="5" t="n"/>
       <c r="I290" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12325,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -12340,7 +12348,7 @@
       <c r="H291" s="5" t="n"/>
       <c r="I291" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12350,7 +12358,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -12365,7 +12373,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F292" s="5" t="n"/>
@@ -12373,7 +12381,7 @@
       <c r="H292" s="5" t="n"/>
       <c r="I292" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12383,7 +12391,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -12406,7 +12414,7 @@
       <c r="H293" s="5" t="n"/>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12424,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -12431,7 +12439,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F294" s="5" t="n"/>
@@ -12439,7 +12447,7 @@
       <c r="H294" s="5" t="n"/>
       <c r="I294" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12449,7 +12457,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -12472,7 +12480,7 @@
       <c r="H295" s="5" t="n"/>
       <c r="I295" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12490,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -12505,7 +12513,7 @@
       <c r="H296" s="5" t="n"/>
       <c r="I296" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12515,7 +12523,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -12538,7 +12546,7 @@
       <c r="H297" s="5" t="n"/>
       <c r="I297" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12556,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -12563,7 +12571,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>A GitHub link is present but explicitly anonymized for peer review: the Data Availability section states 'All code, evaluation datasets, and cross-model validation results are available at: https://github.com/[anonymized-for-review]/memory-evaluation,' listing contents as synthetic/realistic conversation datasets, the 120-query evaluation protocol with ground-truth annotations, and cross-model evaluation scripts for 6 LLMs x 2 architectures. The repository owner/name is deliberately withheld pending review rather than being a resolvable public link.</t>
+          <t>The code is available at https://github.com/ictnlp/unified-memory-agent.git, as stated in a footnote on the first page.</t>
         </is>
       </c>
       <c r="F298" s="5" t="n"/>
@@ -12571,7 +12579,7 @@
       <c r="H298" s="5" t="n"/>
       <c r="I298" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12581,7 +12589,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -12596,7 +12604,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Cross-model validation spans six LLMs across three provider families: OpenAI (GPT-4o, GPT-4o-mini, GPT-5), Anthropic (Claude-4.5-Sonnet), and Google (Gemini-2.5-Pro, Gemini-3-Pro). The consolidation model is primarily GPT-4o-mini, ablated against GPT-4o and a 'GPT-4o-mini-Structured' (JSON-schema extraction) variant.</t>
+          <t>The Unified Memory Agent (UMA) policy is initialized from Qwen/Qwen3-4B-Instruct(-2507) and optimized via Task-Stratified Group Relative Policy Optimization (GRPO) on a cluster of 32 NVIDIA H200 GPUs. Qwen/Qwen3-30B-A3B-Instruct-2507 is used as an LLM-as-a-Judge evaluator. Baseline agentic methods (Mem1, MemAlpha) are reimplemented on the Qwen/Qwen3-4B-Instruct-2507 backbone for fair comparison; Mem1 additionally uses a Mem-Lab/Qwen2.5-7B-RL-finetuned specialist variant in some configurations.</t>
         </is>
       </c>
       <c r="F299" s="5" t="n"/>
@@ -12604,7 +12612,7 @@
       <c r="H299" s="5" t="n"/>
       <c r="I299" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12614,7 +12622,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -12629,7 +12637,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>Custom synthetic capacity-scaling tests up to 100,000 messages with a single embedded fact placed at beginning/middle/end (Lost-in-the-Middle probe); a realistic biomedical-research simulation benchmark spanning 15,000 messages across 10 scales (N=100 to N=15,000, 20 measurement points per scale); a 30-query pronoun/reference-resolution ablation set; a 120-query, 6-query-type cross-model evaluation protocol run across 6 models x 2 architectures = 1,440 total evaluations; and 15 realistic biomedical conversations (28-43 messages) for the consolidation-strategy ablation.</t>
+          <t>Evaluated across 13 datasets spanning three categories: (1) Ledger-QA, a newly introduced diagnostic benchmark for continuous state tracking where answers are latent values derived from accumulated updates (evaluated across varying session counts N in {2,5,...,50}); (2) Test-Time Learning datasets (Banking77, Clinic, NLU, TREC-Coarse, TREC-Fine); (3) Accurate Retrieval datasets (PubMed-RCT, ConvoMem, LoCoMo, LongMemEval, MSC, PerLTQA, SQuAD, and others). Detailed dataset statistics are given in Appendix D/Table 3-4.</t>
         </is>
       </c>
       <c r="F300" s="5" t="n"/>
@@ -12637,7 +12645,7 @@
       <c r="H300" s="5" t="n"/>
       <c r="I300" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12647,7 +12655,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -12662,7 +12670,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>The Dual-Process architecture sustains 70-85% accuracy at 15,000 messages using only 45,434 tokens versus a 120,000+ token Full-Context limit (a 62% token reduction), while Full Context crashes outright (0% accuracy, context-length-exceeded) at 10,000+ messages. A 'cognitive event horizon' is identified at ~2,000 messages (~40,000 tokens), where Full-Context accuracy begins degrading well before the physical 128k-token limit. Cross-model validation (1,440 queries) shows a consistent architectural split across all six models: Dual Process wins on recent-state/numeric-temporal queries (65-90% accuracy) while RAG wins on historical retrieval (60-85%) but RAG scores 0% on recent-state queries. A consolidation-model ablation finds upgrading GPT-4o-mini to GPT-4o improves accuracy by only +0.07% (23.74%-&gt;23.81%, p=0.986, not significant), indicating the consolidation bottleneck is prompt design rather than model capacity.</t>
+          <t>On the main 13-benchmark evaluation (Table 1), UMA achieves the highest average accuracy overall, notably 87.00% on Banking77 and 91.00% on Clinic (both unseen during training, demonstrating generalization), versus MemAlpha's 83.00%/78.00%. On the Ledger-QA long-horizon state-tracking benchmark (Figure 4/Table 8), UMA maintains over 50% accuracy even at the most challenging N=50 sessions, while the best baseline (RAG or MemAlpha) struggles to reach 25%; RAG plummets below 20% at N=50 and MemAgent drops to roughly 20% due to context rot and error accumulation despite moderate mid-range performance. Ablations show memory-equipped agents even without RL (61.38% avg) substantially outperform a stateless retrieval-only baseline (45.26%), and the full UMA with RL and joint end-to-end optimization reaches 76.46% average accuracy on Ledger-QA, outperforming ablated variants that remove RL, remove the memory maintenance phase, use a single global advantage group ignoring task heterogeneity (73.58%), or train memory and QA in two separate non-joint stages (66.29%), confirming the necessity of unified end-to-end optimization.</t>
         </is>
       </c>
       <c r="F301" s="5" t="n"/>
@@ -12670,7 +12678,7 @@
       <c r="H301" s="5" t="n"/>
       <c r="I301" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12688,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -12695,7 +12703,7 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>Full Context (complete unpruned conversation history) and RAG Only (neocortical/semantic memory with vector retrieval, no episodic buffer) are directly benchmarked. MemGPT is discussed and positioned against at length architecturally (explicit vs. implicit memory management, paging granularity, episodic access) but is not empirically re-run on this paper's benchmark -- direct empirical comparison to MemGPT is explicitly deferred as the 'highest-priority future work.' MemoryBank and Park et al.'s Generative Agents are discussed as related work only, not benchmarked.</t>
+          <t>Compared against Concat (full context input to the backbone's native window), RAG (top-20 chunk retrieval via hybrid dense+BM25 Reciprocal Rank Fusion), MemAgent and MemAgent-woq (recurrent summarization models, with/without query-conditioning), Mem1 (interleaved chunk reading with dynamic retrieval maintaining an evolving internal state), and MemAlpha (RL-optimized policy managing a composite core/episodic/semantic memory system, described as the prior state-of-the-art in trainable memory agents).</t>
         </is>
       </c>
       <c r="F302" s="5" t="n"/>
@@ -12703,7 +12711,7 @@
       <c r="H302" s="5" t="n"/>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12721,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -12728,7 +12736,7 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a scientific-agent capability/scalability paper, not a security paper. The incidental failure mode of interest is unintentional information loss/distortion from lossy memory consolidation (measured at only 23.74% fact-retrieval accuracy in the ablation) combined with 'lost-in-the-middle'-style signal-to-noise degradation as raw conversation history grows, plus a temporal-recency confusion failure mode in RAG, where cosine-similarity retrieval cannot distinguish a current parameter value from a stale, superseded one (e.g., retrieving an outdated significance threshold of p&lt;0.05 instead of the current p&lt;0.001).</t>
+          <t>N/A - non-adversarial. This is a long-context/memory-agent capability paper, not a security paper. The incidental failure mode of interest is passive information processing in long-context and RAG systems causing 'context rot' (performance degradation as input length grows even when relevant information is present) and brittleness under ultra-long, frequently-updated information streams requiring state tracking, contradiction resolution, and evidence aggregation.</t>
         </is>
       </c>
       <c r="F303" s="5" t="n"/>
@@ -12736,7 +12744,7 @@
       <c r="H303" s="5" t="n"/>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12746,7 +12754,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -12761,7 +12769,7 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Limitations and Evaluation Gaps' subsection within the Discussion: (1) the 'realistic simulation' benchmark is synthetic (LLM-generated rather than collected from real scientist interactions), risking distribution shift in query patterns, contradiction types, and information density; deployment studies with actual scientists are needed for ecological validity; (2) the paper lacks a systematic failure-mode taxonomy for its reported 70-85% aggregate accuracy (no breakdown of omission vs distortion vs hallucination vs contradiction-mishandling); (3) the flat-text semantic profile scales to only ~14,000 facts (~125,000 tokens) before approaching the 128k context limit, with latency rising to 2-6 seconds, necessitating hierarchical or graph-based retrieval for sub-linear scaling; (4) the memory system does not yet support procedural knowledge (APIs, workflows) needed as agents move from chat interfaces to autonomous tool use; (5) despite 1,440 cross-model queries, the paper lacks formal statistical significance testing or confidence intervals for model-to-model architecture-trade-off comparisons.</t>
+          <t>The paper has an explicit 'Limitations' section (unnumbered, following the Conclusion) stating three limitations: (1) the current implementation enforces a hard context window limit (e.g., 16k tokens) via truncation, and while the memory bank mitigates information loss, managing memory over an infinite-horizon setting spanning millions of tokens without any raw-context fallback remains an open challenge; (2) the Ledger-QA benchmark, while rigorous, is synthetically generated, and real-world bookkeeping or state-tracking scenarios may involve more unstructured noise and ambiguity than the simulation covers; (3) training relies on a specific fixed tool set (CRUD + Retrieval), and extending the framework to multi-modal memory (e.g., images, audio) or more complex tool-use patterns requires further investigation.</t>
         </is>
       </c>
       <c r="F304" s="5" t="n"/>
@@ -12769,7 +12777,7 @@
       <c r="H304" s="5" t="n"/>
       <c r="I304" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12779,7 +12787,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -12794,7 +12802,7 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>The paper evaluates a 'Dual-Process Memory Architecture' for long-horizon scientific LLM agents (e.g., pharmaceutical/genomic research assistants) that maintains two concurrent memory representations at inference time: a fixed-size episodic buffer (a deterministic sliding window of exactly W=10 most-recent raw messages, preserving exact wording for pronoun/discourse resolution and providing constant-time, low-latency access to recent state) and a growing 'neocortical' semantic memory (a natural-language consolidated research profile built via asynchronous incremental consolidation triggered after every message, using GPT-4o-mini with a four-stage extraction protocol: new-fact extraction, contradiction detection against the existing profile, knowledge merger applying a temporal-precedence rule that lets recent values overwrite historical ones, and preservation of domain-specific technical precision). This design is explicitly contrasted with MemGPT's explicit, LLM-driven memory-paging control flow: the Dual-Process system instead decouples consolidation from the primary inference path entirely (every message triggers background consolidation automatically), trading MemGPT's adaptive flexibility for robustness against consolidation failures corrupting the inference path. The empirical program includes destructive synthetic capacity-scaling tests (up to 100,000 messages), a 15,000-message realistic biomedical simulation revealing linear (~3 tokens/message, R^2=0.998) semantic-profile growth versus the constant synthetic-test baseline (the 'Sim-to-Real gap'), a memory-component ablation isolating the episodic buffer's necessity, a consolidation-model ablation identifying prompt design (not model scale) as the primary accuracy bottleneck, and a 1,440-query, 6-model, 2-architecture cross-model validation establishing that the Dual-Process-vs-RAG accuracy trade-off (recent-state strength vs historical-retrieval strength) is a property of the architecture itself, generalizing across OpenAI, Anthropic, and Google model families.</t>
+          <t>This paper proposes the Unified Memory Agent (UMA), an end-to-end reinforcement learning framework that jointly optimizes memory management operations (create, update, delete, reorganize) and question-answering/task execution within a single policy, addressing the credit-assignment gap in prior decoupled architectures (e.g., Memory-R1, Mem-alpha) where memory decisions are trained independently of downstream task outcomes. UMA maintains a dual memory representation: a compact core summary (mcore) for global context and a structured key-value Memory Bank (B) supporting explicit CRUD operations, enabling proactive consolidation during streaming rather than deferring reasoning to query time. The system is formalized as a Markov Decision Process where the input is decomposed into a stream of chunks; an inner loop performs standard tool actions (Add/Update/Delete/Retrieve/List on the bank) without advancing the input stream, while an outer loop's UpdateCore action commits progress to the core summary and advances to the next chunk, and upon processing all chunks the system transitions to a QA phase where a sampled query is answered using hybrid BM25/embedding retrieval over raw chunks plus structured bank access. The policy is trained with Task-Stratified Group Relative Policy Optimization (GRPO), using per-task-category advantage normalization to handle heterogeneous reward scales across memory-maintenance and QA phases (motivating the paper's own 'Global Group' ablation showing this stratification is necessary). To diagnose proactive reasoning specifically, the authors introduce Ledger-QA, a benchmark requiring continuous state tracking where correct answers are latent values derived from accumulated updates rather than retrievable from any single local span, explicitly designed to penalize passive/reactive retrieval strategies that lack persistent structured state.</t>
         </is>
       </c>
       <c r="F305" s="5" t="n"/>
@@ -12802,7 +12810,7 @@
       <c r="H305" s="5" t="n"/>
       <c r="I305" s="5" t="inlineStr">
         <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
@@ -12822,7 +12830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12901,7 +12909,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Building Browser Agents: Architecture, Security, and Practical Solutions</t>
+          <t>Securing Autonomous AI Agents: A Context-Aware Interception Framework for Detecting and Mitigating Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -12911,7 +12919,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hybrid context management + deterministic programmatic safety checks / domain allowlisting / action restriction / least-privilege scoping (production browser-agent architecture)</t>
+          <t>UNNAMED: Context-Aware Interception Framework for PI detection/mitigation</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -12930,7 +12938,7 @@
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2511.19477</t>
+          <t>440cdee84fc943b8919bcc0fb2308b0729b949ff</t>
         </is>
       </c>
     </row>
@@ -12940,27 +12948,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Beware of Agentic Botnets: Scalable Untargeted Promptware Attacks via Universal and Transferable Adversarial HalluSquatting</t>
+          <t>Still: Amortized KV Cache Compaction in a Single Forward Pass</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Adversarial HalluSquatting</t>
+          <t>Still (amortized KV cache compaction, Perceiver-based)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -12969,7 +12977,7 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>3120e577687f1ea6217cc0b546739aaa0295acbe</t>
+          <t>40ea97427c4750b1dee547f6c7b433733a80c38c</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12987,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>PoisonedRAG: Knowledge Corruption Attacks to Retrieval-Augmented Generation of Large Language Models</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -12989,17 +12997,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>F2A (Feign Agent Attack)</t>
+          <t>PoisonedRAG</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -13008,7 +13016,7 @@
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>f4e06256ab07727ff4e0465deea83fcf45012354</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13026,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>F2A: An Innovative Approach for Prompt Injection by Utilizing Feign Security Detection Agents</t>
+          <t>ShadowPlay: Engineering Defenses Against Role-Based Prompt Injection and Dependency Hallucination in LLM-Powered Development</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -13028,12 +13036,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Defe-Prompt</t>
+          <t>ShadowPlay</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -13047,7 +13055,7 @@
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>0b708c14a822691047238cfc50dc15312ee8cef1</t>
+          <t>62cd3a8f6ca307517456320009962a71487666f2</t>
         </is>
       </c>
     </row>
@@ -13057,27 +13065,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>Why So Gullible? Enhancing the Robustness of Retrieval-Augmented Models against Counterfactual Noise</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>message history forging (direct prompt injection via forged system/assistant roles)</t>
+          <t>Discern-and-Answer</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -13086,7 +13094,7 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>66cca7a055ee9278d0439654f474cbfa4135aff0</t>
         </is>
       </c>
     </row>
@@ -13096,7 +13104,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>When AI Meets the Web: Prompt Injection Risks in Third-Party AI Chatbot Plugins</t>
+          <t>PromptGuard a structured framework for injection resilient language models</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -13106,12 +13114,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>UGCBuster</t>
+          <t>PromptGuard</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -13125,7 +13133,7 @@
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>0e3f35c9f300156346dd5ddd75b78f768a21deb8</t>
+          <t>c3cc8bd227eedf8986bab48779db0c9335d5b633</t>
         </is>
       </c>
     </row>
@@ -13135,7 +13143,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard: Defending Agents against Indirect Prompt Injection via Planning-based Consistency Verification</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -13145,7 +13153,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>PlanGuard</t>
+          <t>AprielGuard</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -13164,7 +13172,7 @@
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>60d1a692707848767aba41b5d83205478c191f4d</t>
+          <t>c8bbbde5345092e81bfd17ad60456cd1f1ca4fdc</t>
         </is>
       </c>
     </row>
@@ -13174,27 +13182,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
+          <t>PISmith: Reinforcement Learning-based Red Teaming for Prompt Injection Defenses</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ReMEmbR (Retrieval-augmented Memory for Embodied Robots)</t>
+          <t>PISmith</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -13203,7 +13211,7 @@
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+          <t>a93eb55526ee6d441f19bdd47b70974af990079c</t>
         </is>
       </c>
     </row>
@@ -13213,7 +13221,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>BenchOverflow: Measuring Overflow in Large Language Models via Plain-Text Prompts</t>
+          <t>ChainFuzzer: Greybox Fuzzing for Workflow-Level Multi-Tool Vulnerabilities in LLM Agents</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -13223,17 +13231,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Overflow</t>
+          <t>ChainFuzzer</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>resource-abuse</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -13242,7 +13250,7 @@
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>301b6d574aa1f16b8b0ded55ec0236cbd2066260</t>
+          <t>48c12080143be758aa764aeab6bc2a0edff4a6cc</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13260,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>LLMON: An LLM-native Markup Language to Leverage Structure and Semantics at the LLM Interface</t>
+          <t>Hacking Back the AI-Hacker: Prompt Injection as a Defense Against LLM-driven Cyberattacks</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -13262,17 +13270,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>LLMON (LLM Object Notation)</t>
+          <t>Mantis</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -13281,7 +13289,7 @@
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>6928b524b564275fc7855a953d78677d3e66f092</t>
+          <t>b67a6181fad5c5838945583ccdc7f39187e29332</t>
         </is>
       </c>
     </row>
@@ -13291,22 +13299,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
+          <t>Learning to Remember: End-to-End Training of Memory Agents for Long-Context Reasoning</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>context compliance (failure to track whether output was actually controlled by retrieved context vs. parametric prior vs. post-hoc rationalization)</t>
+          <t>UMA (Unified Memory Agent)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -13320,214 +13328,19 @@
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Does RAG Know When Retrieval Is Wrong? Diagnosing Context Compliance under Knowledge Conflict</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>CDD (Context-Driven Decomposition)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>silent-corruption</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>bac834b243ee47e83b60117d529a369dec67514e</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>attack / failure mechanism</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Semantic-Masquerading IPI; Cascading IPI; Isolation-Breach IPI</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>tool-output</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Disrupting Large Language Models with Hidden Prompt Injection Attacks Embedded in HTML Pages</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Windowed HTML content filtering (128/64-token chunking + PromptGuard/DeBERTaV3 classification)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>7d76841c36a85d550d2211b148d0c593e75f7419</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>attack / failure mechanism</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>UNNAMED: "cognitive event horizon" (context-saturation threshold beyond which accuracy collapses)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>reasoning-corruption</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Episodic-Semantic Memory Architecture for Long-Horizon Scientific Agents</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Dual-Process Memory Architecture (episodic-semantic memory for scientific agents)</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>reasoning-corruption</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>7a39d0ccffe0c30b98a3a4b2c1bb82bb0e8c6026</t>
+          <t>58f06a469e693919434151b1269a01b355cc2b61</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="G2:G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
   </dataValidations>
